--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F3C462-C88E-4EB2-8F83-512DD742BCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54967162-310F-405F-9650-B829E2051AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7411" uniqueCount="2455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7432" uniqueCount="2471">
   <si>
     <t>항목</t>
   </si>
@@ -9037,6 +9037,1577 @@
     <t>주말에도 저녁 제때</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>V-47</t>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rule_id</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> confirmation_label </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기준으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rule_id</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> confirmation_state</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>똑같이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rule_id</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <t>V-48</t>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> source_visit_date </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내림차순으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음씩</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날짜가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rule_id </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오름차순으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가른다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>순서를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현마다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달라지거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하루에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <t>CFG-066</t>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>표기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내림차순</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>동률은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오름차순</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+  </si>
+  <si>
+    <t>CONFIRMATION_QUEUE_ORDER</t>
+  </si>
+  <si>
+    <t>GROUP_BY=confirmation_label;ORDER=source_visit_date DESC,rule_id ASC;PER_DAY=1</t>
+  </si>
+  <si>
+    <r>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -9252,7 +10823,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="DietSettings" displayName="DietSettings" ref="A1:K64" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="DietSettings" displayName="DietSettings" ref="A1:K65" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="setting_group"/>
@@ -9271,7 +10842,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="DietSettingParameters" displayName="DietSettingParameters" ref="A1:H22" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="DietSettingParameters" displayName="DietSettingParameters" ref="A1:H23" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="parameter_key"/>
@@ -9452,7 +11023,7 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D46" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D48" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1600-000001000000}" name="규칙 ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1600-000002000000}" name="대상"/>
@@ -12034,7 +13605,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -13936,6 +15507,29 @@
         <v>64</v>
       </c>
     </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="12" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>2467</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13950,7 +15544,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -14480,6 +16074,28 @@
       </c>
       <c r="H22" t="s">
         <v>1482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="12" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>2470</v>
       </c>
     </row>
   </sheetData>
@@ -21101,7 +22717,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -21752,6 +23368,34 @@
       </c>
       <c r="D46" s="12" t="s">
         <v>2399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="12" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="12" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>2462</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54967162-310F-405F-9650-B829E2051AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A317B4B-B0A5-4A8D-A5FE-5F833C2AEFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7257,9 +7257,6 @@
     <t>denied</t>
   </si>
   <si>
-    <t>아니요</t>
-  </si>
-  <si>
     <t>unknown</t>
   </si>
   <si>
@@ -7272,1550 +7269,6 @@
   </si>
   <si>
     <t>V-46</t>
-  </si>
-  <si>
-    <r>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{질환명</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진단받고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중이신가요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>해당</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세션의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>첫째</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문으로만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>노출</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>해당</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진단받고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는지에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자기보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>임상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>여부</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>자가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답이므로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>임상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확진이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모르겠어요가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뜻하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으며</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>금지는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유지된다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>집계하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중이에요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모르겠어요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>question_role이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CONFIRMATION</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> score_value</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하며</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>집계와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계산에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
   </si>
   <si>
     <t>점심 · 저녁 챙기기</t>
@@ -10608,6 +9061,1291 @@
       <t>본다</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이신가요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세션의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>첫째</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문으로만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는지에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자기보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>임상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>여부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답이므로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>임상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확진이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모르겠어요가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뜻하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유지된다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>집계하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이에요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모르겠어요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>question_role</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CONFIRMATION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> score_value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>비어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>집계와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넣지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넣거나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건수로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -10616,7 +10354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10659,13 +10397,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Carlito"/>
@@ -10675,6 +10406,16 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -10719,7 +10460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -10750,11 +10491,12 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15508,26 +15250,26 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="12" t="s">
-        <v>2463</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>2464</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>2466</v>
-      </c>
-      <c r="E65" s="12" t="s">
+      <c r="A65" s="11" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E65" s="11" t="s">
         <v>1420</v>
       </c>
-      <c r="I65" s="12" t="s">
+      <c r="I65" s="11" t="s">
         <v>1204</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>2467</v>
+      <c r="J65" s="11" t="s">
+        <v>2456</v>
       </c>
     </row>
   </sheetData>
@@ -16077,25 +15819,25 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="12" t="s">
-        <v>2463</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>2468</v>
-      </c>
-      <c r="C23" s="12" t="s">
+      <c r="A23" s="11" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>1440</v>
       </c>
       <c r="D23" s="12"/>
-      <c r="E23" s="12" t="s">
-        <v>2469</v>
+      <c r="E23" s="11" t="s">
+        <v>2458</v>
       </c>
       <c r="F23" s="12"/>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>1478</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>2470</v>
+      <c r="H23" s="11" t="s">
+        <v>2459</v>
       </c>
     </row>
   </sheetData>
@@ -23358,44 +23100,44 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="12" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>2397</v>
+        <v>2468</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>2398</v>
+        <v>2469</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>2399</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="12" t="s">
-        <v>2455</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>2456</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>2457</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>2458</v>
+      <c r="A47" s="11" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>2447</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="12" t="s">
-        <v>2459</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>2460</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>2461</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>2462</v>
+      <c r="A48" s="11" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>2451</v>
       </c>
     </row>
   </sheetData>
@@ -23656,8 +23398,8 @@
       <c r="F2" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>2451</v>
+      <c r="G2" s="14" t="s">
+        <v>2440</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1968</v>
@@ -23734,8 +23476,8 @@
       <c r="F4" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>2400</v>
+      <c r="G4" s="14" t="s">
+        <v>2389</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>1976</v>
@@ -23773,7 +23515,7 @@
       <c r="F5" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="14" t="s">
         <v>2327</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -23810,7 +23552,7 @@
       <c r="F6" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="14" t="s">
         <v>2328</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -23849,7 +23591,7 @@
       <c r="F7" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="14" t="s">
         <v>2329</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -23925,7 +23667,7 @@
       <c r="F9" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="14" t="s">
         <v>2330</v>
       </c>
       <c r="H9" s="9" t="s">
@@ -23962,7 +23704,7 @@
       <c r="F10" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="14" t="s">
         <v>2331</v>
       </c>
       <c r="H10" s="9" t="s">
@@ -24001,8 +23743,8 @@
       <c r="F11" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>2401</v>
+      <c r="G11" s="14" t="s">
+        <v>2390</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1994</v>
@@ -24040,8 +23782,8 @@
       <c r="F12" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>2402</v>
+      <c r="G12" s="14" t="s">
+        <v>2391</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>1997</v>
@@ -24079,7 +23821,7 @@
       <c r="F13" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
         <v>2332</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -24194,7 +23936,7 @@
       <c r="F16" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="14" t="s">
         <v>2333</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -24231,8 +23973,8 @@
       <c r="F17" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>2403</v>
+      <c r="G17" s="14" t="s">
+        <v>2392</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>2010</v>
@@ -24268,7 +24010,7 @@
       <c r="F18" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="14" t="s">
         <v>2334</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -24305,7 +24047,7 @@
       <c r="F19" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="14" t="s">
         <v>2335</v>
       </c>
       <c r="H19" s="9" t="s">
@@ -24342,7 +24084,7 @@
       <c r="F20" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="14" t="s">
         <v>2336</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -24381,8 +24123,8 @@
       <c r="F21" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>2450</v>
+      <c r="G21" s="14" t="s">
+        <v>2439</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>2020</v>
@@ -24420,8 +24162,8 @@
       <c r="F22" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>2405</v>
+      <c r="G22" s="14" t="s">
+        <v>2394</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>2022</v>
@@ -24459,7 +24201,7 @@
       <c r="F23" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="14" t="s">
         <v>2337</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -24498,7 +24240,7 @@
       <c r="F24" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="14" t="s">
         <v>2338</v>
       </c>
       <c r="H24" s="9" t="s">
@@ -24537,8 +24279,8 @@
       <c r="F25" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>2406</v>
+      <c r="G25" s="14" t="s">
+        <v>2395</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>2028</v>
@@ -24576,8 +24318,8 @@
       <c r="F26" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>2452</v>
+      <c r="G26" s="14" t="s">
+        <v>2441</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>2030</v>
@@ -24609,8 +24351,8 @@
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="11" t="s">
-        <v>2407</v>
+      <c r="G27" s="14" t="s">
+        <v>2396</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>2034</v>
@@ -24644,8 +24386,8 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="11" t="s">
-        <v>2404</v>
+      <c r="G28" s="14" t="s">
+        <v>2393</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>2036</v>
@@ -24679,7 +24421,7 @@
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="14" t="s">
         <v>2339</v>
       </c>
       <c r="H29" s="9" t="s">
@@ -24714,8 +24456,8 @@
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="11" t="s">
-        <v>2408</v>
+      <c r="G30" s="14" t="s">
+        <v>2397</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>2041</v>
@@ -24747,8 +24489,8 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="11" t="s">
-        <v>2409</v>
+      <c r="G31" s="14" t="s">
+        <v>2398</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>2043</v>
@@ -24780,8 +24522,8 @@
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="11" t="s">
-        <v>2410</v>
+      <c r="G32" s="14" t="s">
+        <v>2399</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>2045</v>
@@ -24817,7 +24559,7 @@
       <c r="F33" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="14" t="s">
         <v>2340</v>
       </c>
       <c r="H33" s="9" t="s">
@@ -24856,8 +24598,8 @@
       <c r="F34" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>2411</v>
+      <c r="G34" s="14" t="s">
+        <v>2400</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>2050</v>
@@ -24893,7 +24635,7 @@
       <c r="F35" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="14" t="s">
         <v>2341</v>
       </c>
       <c r="H35" s="9" t="s">
@@ -24932,8 +24674,8 @@
       <c r="F36" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G36" s="11" t="s">
-        <v>2412</v>
+      <c r="G36" s="14" t="s">
+        <v>2401</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>2054</v>
@@ -24971,7 +24713,7 @@
       <c r="F37" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="14" t="s">
         <v>2342</v>
       </c>
       <c r="H37" s="9" t="s">
@@ -25008,7 +24750,7 @@
       <c r="F38" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="14" t="s">
         <v>2343</v>
       </c>
       <c r="H38" s="9" t="s">
@@ -25047,7 +24789,7 @@
       <c r="F39" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="14" t="s">
         <v>2344</v>
       </c>
       <c r="H39" s="9" t="s">
@@ -25086,7 +24828,7 @@
       <c r="F40" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="14" t="s">
         <v>2345</v>
       </c>
       <c r="H40" s="9" t="s">
@@ -25162,8 +24904,8 @@
       <c r="F42" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G42" s="11" t="s">
-        <v>2413</v>
+      <c r="G42" s="14" t="s">
+        <v>2402</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>2068</v>
@@ -25275,7 +25017,7 @@
       <c r="F45" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="14" t="s">
         <v>2346</v>
       </c>
       <c r="H45" s="9" t="s">
@@ -25353,8 +25095,8 @@
       <c r="F47" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G47" s="11" t="s">
-        <v>2414</v>
+      <c r="G47" s="14" t="s">
+        <v>2403</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>2081</v>
@@ -25390,7 +25132,7 @@
       <c r="F48" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="14" t="s">
         <v>2347</v>
       </c>
       <c r="H48" s="9" t="s">
@@ -25429,8 +25171,8 @@
       <c r="F49" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G49" s="11" t="s">
-        <v>2415</v>
+      <c r="G49" s="14" t="s">
+        <v>2404</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>2085</v>
@@ -25468,8 +25210,8 @@
       <c r="F50" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G50" s="11" t="s">
-        <v>2416</v>
+      <c r="G50" s="14" t="s">
+        <v>2405</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>2087</v>
@@ -25505,7 +25247,7 @@
       <c r="F51" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G51" s="14" t="s">
         <v>2348</v>
       </c>
       <c r="H51" s="9" t="s">
@@ -25544,8 +25286,8 @@
       <c r="F52" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G52" s="11" t="s">
-        <v>2417</v>
+      <c r="G52" s="14" t="s">
+        <v>2406</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>2091</v>
@@ -25620,7 +25362,7 @@
       <c r="F54" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="14" t="s">
         <v>2349</v>
       </c>
       <c r="H54" s="9" t="s">
@@ -25696,8 +25438,8 @@
       <c r="F56" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G56" s="11" t="s">
-        <v>2418</v>
+      <c r="G56" s="14" t="s">
+        <v>2407</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>2101</v>
@@ -25735,8 +25477,8 @@
       <c r="F57" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G57" s="11" t="s">
-        <v>2419</v>
+      <c r="G57" s="14" t="s">
+        <v>2408</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>2103</v>
@@ -25772,7 +25514,7 @@
       <c r="F58" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="14" t="s">
         <v>2350</v>
       </c>
       <c r="H58" s="9" t="s">
@@ -25811,8 +25553,8 @@
       <c r="F59" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G59" s="11" t="s">
-        <v>2420</v>
+      <c r="G59" s="14" t="s">
+        <v>2409</v>
       </c>
       <c r="H59" s="9" t="s">
         <v>2107</v>
@@ -25850,8 +25592,8 @@
       <c r="F60" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>2421</v>
+      <c r="G60" s="14" t="s">
+        <v>2410</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>2109</v>
@@ -25889,7 +25631,7 @@
       <c r="F61" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="14" t="s">
         <v>2351</v>
       </c>
       <c r="H61" s="9" t="s">
@@ -25961,8 +25703,8 @@
       </c>
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
-      <c r="G63" s="11" t="s">
-        <v>2422</v>
+      <c r="G63" s="14" t="s">
+        <v>2411</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>2116</v>
@@ -25996,7 +25738,7 @@
       </c>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="14" t="s">
         <v>2352</v>
       </c>
       <c r="H64" s="9" t="s">
@@ -26035,8 +25777,8 @@
       <c r="F65" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G65" s="11" t="s">
-        <v>2423</v>
+      <c r="G65" s="14" t="s">
+        <v>2412</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>2120</v>
@@ -26074,8 +25816,8 @@
       <c r="F66" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G66" s="11" t="s">
-        <v>2424</v>
+      <c r="G66" s="14" t="s">
+        <v>2413</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>2122</v>
@@ -26113,7 +25855,7 @@
       <c r="F67" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="14" t="s">
         <v>2353</v>
       </c>
       <c r="H67" s="9" t="s">
@@ -26150,7 +25892,7 @@
       <c r="F68" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="14" t="s">
         <v>2354</v>
       </c>
       <c r="H68" s="9" t="s">
@@ -26189,7 +25931,7 @@
       <c r="F69" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="14" t="s">
         <v>2355</v>
       </c>
       <c r="H69" s="9" t="s">
@@ -26228,8 +25970,8 @@
       <c r="F70" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G70" s="11" t="s">
-        <v>2425</v>
+      <c r="G70" s="14" t="s">
+        <v>2414</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>2130</v>
@@ -26304,8 +26046,8 @@
       <c r="F72" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G72" s="11" t="s">
-        <v>2426</v>
+      <c r="G72" s="14" t="s">
+        <v>2415</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>2135</v>
@@ -26382,7 +26124,7 @@
       <c r="F74" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="14" t="s">
         <v>2356</v>
       </c>
       <c r="H74" s="9" t="s">
@@ -26421,8 +26163,8 @@
       <c r="F75" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G75" s="11" t="s">
-        <v>2427</v>
+      <c r="G75" s="14" t="s">
+        <v>2416</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>2142</v>
@@ -26458,7 +26200,7 @@
       <c r="F76" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="14" t="s">
         <v>2357</v>
       </c>
       <c r="H76" s="9" t="s">
@@ -26573,7 +26315,7 @@
       <c r="F79" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="14" t="s">
         <v>2358</v>
       </c>
       <c r="H79" s="9" t="s">
@@ -26612,8 +26354,8 @@
       <c r="F80" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G80" s="11" t="s">
-        <v>2428</v>
+      <c r="G80" s="14" t="s">
+        <v>2417</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>2155</v>
@@ -26651,8 +26393,8 @@
       <c r="F81" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G81" s="11" t="s">
-        <v>2429</v>
+      <c r="G81" s="14" t="s">
+        <v>2418</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>2157</v>
@@ -26690,8 +26432,8 @@
       <c r="F82" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G82" s="11" t="s">
-        <v>2430</v>
+      <c r="G82" s="14" t="s">
+        <v>2419</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>2159</v>
@@ -26729,7 +26471,7 @@
       <c r="F83" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="14" t="s">
         <v>2359</v>
       </c>
       <c r="H83" s="9" t="s">
@@ -26768,8 +26510,8 @@
       <c r="F84" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G84" s="11" t="s">
-        <v>2431</v>
+      <c r="G84" s="14" t="s">
+        <v>2420</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>2163</v>
@@ -26805,7 +26547,7 @@
       <c r="F85" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="14" t="s">
         <v>2360</v>
       </c>
       <c r="H85" s="9" t="s">
@@ -26842,8 +26584,8 @@
       <c r="F86" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G86" s="11" t="s">
-        <v>2432</v>
+      <c r="G86" s="14" t="s">
+        <v>2421</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>2167</v>
@@ -26879,8 +26621,8 @@
       <c r="F87" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G87" s="11" t="s">
-        <v>2453</v>
+      <c r="G87" s="14" t="s">
+        <v>2442</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>2169</v>
@@ -26955,8 +26697,8 @@
       <c r="F89" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G89" s="11" t="s">
-        <v>2433</v>
+      <c r="G89" s="14" t="s">
+        <v>2422</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>2174</v>
@@ -26992,7 +26734,7 @@
       <c r="F90" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G90" s="11" t="s">
+      <c r="G90" s="14" t="s">
         <v>2361</v>
       </c>
       <c r="H90" s="9" t="s">
@@ -27031,8 +26773,8 @@
       <c r="F91" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G91" s="11" t="s">
-        <v>2434</v>
+      <c r="G91" s="14" t="s">
+        <v>2423</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>2179</v>
@@ -27070,8 +26812,8 @@
       <c r="F92" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G92" s="11" t="s">
-        <v>2435</v>
+      <c r="G92" s="14" t="s">
+        <v>2424</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>2181</v>
@@ -27109,8 +26851,8 @@
       <c r="F93" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G93" s="11" t="s">
-        <v>2436</v>
+      <c r="G93" s="14" t="s">
+        <v>2425</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>2183</v>
@@ -27183,8 +26925,8 @@
       <c r="F95" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G95" s="11" t="s">
-        <v>2437</v>
+      <c r="G95" s="14" t="s">
+        <v>2426</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>2188</v>
@@ -27261,8 +27003,8 @@
       <c r="F97" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G97" s="11" t="s">
-        <v>2438</v>
+      <c r="G97" s="14" t="s">
+        <v>2427</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>2193</v>
@@ -27298,8 +27040,8 @@
       <c r="F98" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G98" s="11" t="s">
-        <v>2454</v>
+      <c r="G98" s="14" t="s">
+        <v>2443</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>2195</v>
@@ -27335,7 +27077,7 @@
       <c r="F99" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G99" s="11" t="s">
+      <c r="G99" s="14" t="s">
         <v>2362</v>
       </c>
       <c r="H99" s="9" t="s">
@@ -27452,7 +27194,7 @@
       <c r="F102" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G102" s="11" t="s">
+      <c r="G102" s="14" t="s">
         <v>2363</v>
       </c>
       <c r="H102" s="9" t="s">
@@ -27489,8 +27231,8 @@
       <c r="F103" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G103" s="11" t="s">
-        <v>2439</v>
+      <c r="G103" s="14" t="s">
+        <v>2428</v>
       </c>
       <c r="H103" s="9" t="s">
         <v>2207</v>
@@ -27524,7 +27266,7 @@
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
-      <c r="G104" s="11" t="s">
+      <c r="G104" s="14" t="s">
         <v>2364</v>
       </c>
       <c r="H104" s="9" t="s">
@@ -27559,7 +27301,7 @@
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
-      <c r="G105" s="11" t="s">
+      <c r="G105" s="14" t="s">
         <v>2365</v>
       </c>
       <c r="H105" s="9" t="s">
@@ -27594,7 +27336,7 @@
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
-      <c r="G106" s="11" t="s">
+      <c r="G106" s="14" t="s">
         <v>2366</v>
       </c>
       <c r="H106" s="9" t="s">
@@ -27668,8 +27410,8 @@
       <c r="F108" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G108" s="11" t="s">
-        <v>2440</v>
+      <c r="G108" s="14" t="s">
+        <v>2429</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>2218</v>
@@ -27707,7 +27449,7 @@
       <c r="F109" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G109" s="11" t="s">
+      <c r="G109" s="14" t="s">
         <v>2367</v>
       </c>
       <c r="H109" s="9" t="s">
@@ -27822,8 +27564,8 @@
       <c r="F112" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G112" s="11" t="s">
-        <v>2441</v>
+      <c r="G112" s="14" t="s">
+        <v>2430</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>2228</v>
@@ -27861,7 +27603,7 @@
       <c r="F113" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G113" s="11" t="s">
+      <c r="G113" s="14" t="s">
         <v>2368</v>
       </c>
       <c r="H113" s="9" t="s">
@@ -27898,8 +27640,8 @@
       <c r="F114" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G114" s="11" t="s">
-        <v>2442</v>
+      <c r="G114" s="14" t="s">
+        <v>2431</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>2232</v>
@@ -27976,8 +27718,8 @@
       <c r="F116" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G116" s="11" t="s">
-        <v>2443</v>
+      <c r="G116" s="14" t="s">
+        <v>2432</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>2237</v>
@@ -28171,7 +27913,7 @@
       <c r="F121" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G121" s="11" t="s">
+      <c r="G121" s="14" t="s">
         <v>2369</v>
       </c>
       <c r="H121" s="9" t="s">
@@ -28249,8 +27991,8 @@
       <c r="F123" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G123" s="11" t="s">
-        <v>2444</v>
+      <c r="G123" s="14" t="s">
+        <v>2433</v>
       </c>
       <c r="H123" s="9" t="s">
         <v>2256</v>
@@ -28325,8 +28067,8 @@
       <c r="F125" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G125" s="11" t="s">
-        <v>2445</v>
+      <c r="G125" s="14" t="s">
+        <v>2434</v>
       </c>
       <c r="H125" s="9" t="s">
         <v>2261</v>
@@ -28438,7 +28180,7 @@
       <c r="F128" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G128" s="11" t="s">
+      <c r="G128" s="14" t="s">
         <v>2370</v>
       </c>
       <c r="H128" s="9" t="s">
@@ -28541,8 +28283,8 @@
       </c>
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
-      <c r="G131" s="11" t="s">
-        <v>2446</v>
+      <c r="G131" s="14" t="s">
+        <v>2435</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>2277</v>
@@ -28578,7 +28320,7 @@
       <c r="F132" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G132" s="11" t="s">
+      <c r="G132" s="14" t="s">
         <v>2371</v>
       </c>
       <c r="H132" s="9" t="s">
@@ -28615,7 +28357,7 @@
       <c r="F133" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G133" s="11" t="s">
+      <c r="G133" s="14" t="s">
         <v>2372</v>
       </c>
       <c r="H133" s="9" t="s">
@@ -28652,7 +28394,7 @@
       <c r="F134" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G134" s="11" t="s">
+      <c r="G134" s="14" t="s">
         <v>2373</v>
       </c>
       <c r="H134" s="9" t="s">
@@ -28689,8 +28431,8 @@
       <c r="F135" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G135" s="11" t="s">
-        <v>2447</v>
+      <c r="G135" s="14" t="s">
+        <v>2436</v>
       </c>
       <c r="H135" s="9" t="s">
         <v>2287</v>
@@ -28726,7 +28468,7 @@
       <c r="F136" s="9" t="s">
         <v>1978</v>
       </c>
-      <c r="G136" s="11" t="s">
+      <c r="G136" s="14" t="s">
         <v>2374</v>
       </c>
       <c r="H136" s="9" t="s">
@@ -28763,7 +28505,7 @@
       <c r="F137" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G137" s="11" t="s">
+      <c r="G137" s="14" t="s">
         <v>2375</v>
       </c>
       <c r="H137" s="9" t="s">
@@ -28800,7 +28542,7 @@
       <c r="F138" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G138" s="11" t="s">
+      <c r="G138" s="14" t="s">
         <v>2376</v>
       </c>
       <c r="H138" s="9" t="s">
@@ -28837,7 +28579,7 @@
       <c r="F139" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G139" s="11" t="s">
+      <c r="G139" s="14" t="s">
         <v>2377</v>
       </c>
       <c r="H139" s="9" t="s">
@@ -28874,8 +28616,8 @@
       <c r="F140" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G140" s="11" t="s">
-        <v>2448</v>
+      <c r="G140" s="14" t="s">
+        <v>2437</v>
       </c>
       <c r="H140" s="9" t="s">
         <v>2300</v>
@@ -28911,7 +28653,7 @@
       <c r="F141" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G141" s="11" t="s">
+      <c r="G141" s="14" t="s">
         <v>2378</v>
       </c>
       <c r="H141" s="9" t="s">
@@ -28948,7 +28690,7 @@
       <c r="F142" s="9" t="s">
         <v>1972</v>
       </c>
-      <c r="G142" s="11" t="s">
+      <c r="G142" s="14" t="s">
         <v>2379</v>
       </c>
       <c r="H142" s="9" t="s">
@@ -28985,7 +28727,7 @@
       <c r="F143" s="9" t="s">
         <v>1967</v>
       </c>
-      <c r="G143" s="11" t="s">
+      <c r="G143" s="14" t="s">
         <v>2380</v>
       </c>
       <c r="H143" s="9" t="s">
@@ -29018,8 +28760,8 @@
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
-      <c r="G144" s="11" t="s">
-        <v>2449</v>
+      <c r="G144" s="14" t="s">
+        <v>2438</v>
       </c>
       <c r="H144" s="9" t="s">
         <v>2309</v>
@@ -33626,7 +33368,7 @@
         <v>238</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
@@ -35646,7 +35388,7 @@
         <v>239</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="24" customHeight="1">
@@ -40616,22 +40358,22 @@
         <v>842</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2390</v>
+        <v>2460</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>2382</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2391</v>
+        <v>2461</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>2392</v>
+        <v>2462</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>2393</v>
+        <v>2463</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>2394</v>
+        <v>2464</v>
       </c>
     </row>
   </sheetData>
@@ -41242,7 +40984,7 @@
         <v>2383</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2395</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -41259,7 +41001,7 @@
         <v>2384</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>2385</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -41273,10 +41015,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2396</v>
+        <v>2467</v>
       </c>
     </row>
   </sheetData>
@@ -41532,7 +41274,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>941</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5BC99E-B362-405A-9D05-A8C8A66498C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5013ACD7-2F53-41F6-A374-93D4E1EC6439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10287,10 +10287,6 @@
     </r>
   </si>
   <si>
-    <t>거의 못 먹었어요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>절반 이하</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -10365,6 +10361,10 @@
       </rPr>
       <t>길이</t>
     </r>
+  </si>
+  <si>
+    <t>거의 못 먹거나 거름</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -10416,7 +10416,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 10</t>
+      <t xml:space="preserve"> 11</t>
     </r>
     <r>
       <rPr>
@@ -10501,7 +10501,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>버튼은</t>
+      <t>버튼</t>
     </r>
     <r>
       <rPr>
@@ -10520,7 +10520,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>한</t>
+      <t>폭이</t>
     </r>
     <r>
       <rPr>
@@ -10539,7 +10539,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>줄로</t>
+      <t>고정이라</t>
     </r>
     <r>
       <rPr>
@@ -10558,7 +10558,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>보이므로</t>
+      <t>그보다</t>
     </r>
     <r>
       <rPr>
@@ -10577,7 +10577,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>줄바꿈이나</t>
+      <t>길면</t>
     </r>
     <r>
       <rPr>
@@ -10596,7 +10596,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>말줄임이</t>
+      <t>버튼</t>
     </r>
     <r>
       <rPr>
@@ -10615,7 +10615,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>생기면</t>
+      <t>높이가</t>
     </r>
     <r>
       <rPr>
@@ -10634,7 +10634,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>안</t>
+      <t>혼자</t>
     </r>
     <r>
       <rPr>
@@ -10653,12 +10653,13 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>된다</t>
+      <t>늘어난다</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>10자를</t>
+      <t>11자를</t>
     </r>
     <r>
       <rPr>
@@ -10736,6 +10737,7 @@
       </rPr>
       <t>거부</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23540,10 +23542,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="11" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>2471</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>2472</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>2473</v>
@@ -40896,7 +40898,7 @@
         <v>891</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>2463</v>
+        <v>2472</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -41080,7 +41082,7 @@
         <v>904</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -41103,7 +41105,7 @@
         <v>905</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -41147,7 +41149,7 @@
         <v>899</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -41168,7 +41170,7 @@
         <v>901</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -41212,7 +41214,7 @@
         <v>908</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -41235,7 +41237,7 @@
         <v>909</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -41396,7 +41398,7 @@
         <v>2376</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="27" spans="1:7">

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5013ACD7-2F53-41F6-A374-93D4E1EC6439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C001D6-4AA1-45FE-8650-F70764074272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -6465,9 +6465,6 @@
     <t>DIET-P-0110</t>
   </si>
   <si>
-    <t>저녁 시각 어제와 같게</t>
-  </si>
-  <si>
     <t>생활 일정에 맞춰 저녁 시각을 계획해요.</t>
   </si>
   <si>
@@ -6672,9 +6669,6 @@
     <t>DIET-P-0183</t>
   </si>
   <si>
-    <t>늦은 저녁엔 국물 적게</t>
-  </si>
-  <si>
     <t>늦은 식사의 국물 양을 살펴봐요. 증상 개선을 보장하지 않아요.</t>
   </si>
   <si>
@@ -6816,9 +6810,6 @@
     <t>DIET-P-0218</t>
   </si>
   <si>
-    <t>더운 날 음료는 물부터</t>
-  </si>
-  <si>
     <t>갈증이 있을 때 개인 수분 계획에 맞춰 마셔요.</t>
   </si>
   <si>
@@ -7006,10 +6997,6 @@
   </si>
   <si>
     <t>PRE_MIDNIGHT</t>
-  </si>
-  <si>
-    <t>끼니 시각 어제처럼</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>한 끼에 채소 하나</t>
@@ -7032,10 +7019,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>한 끼는 간 싱겁게</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>식사 중 수저 내려놓기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7060,10 +7043,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>아침에 우유나 두유</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 세 끼 챙기기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7072,10 +7051,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>고기엔 쌈 채소 함께</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>외식에도 채소 하나 더</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7112,26 +7087,14 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>세 끼 시각 평소대로</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>국에 채소 한 줌</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>모든 끼니에 채소</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>짠 반찬은 한 가지만</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>김치는 작은 접시에</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>중간에 한 번 멈추기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7160,18 +7123,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>먹을 수 있는 것부터</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁에 익힌 채소 하나</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>약속 날에도 저녁 제때</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>혼자여도 상 차려 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7196,10 +7151,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>세 끼 모두 천천히</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>아침 먹을 자리 치우기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7254,10 +7205,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>단 음료는 무가당</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁 디저트 건너뛰기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7266,10 +7213,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>단백질 한 입이라도</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>단백질 반찬 하나</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7286,18 +7229,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 간단하게</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>점심은 평소 양으로</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>점심 늦지 않게</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>주말에도 아침 챙기기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7314,10 +7249,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>소스는 따로 달라고</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>휴대폰 끄고 식사</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7326,10 +7257,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 다른 단백질</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>삼겹살 대신 목살</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7342,18 +7269,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 가볍게라도</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>출근길에 아침 챙기기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>저녁 반찬 절반 채소</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>찌개는 건더기만</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7374,10 +7293,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 생선 · 두부</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>아침거리 꺼내 두기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7418,10 +7333,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>혼밥도 그릇에 덜어</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>혼밥에도 단백질 하나</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7446,27 +7357,11 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>내일 아침 간단하게</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금이라도 단백질</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>아침에 뭐라도 한 입</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고기 대신 생선으로</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>연휴에도 제시간에</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주말에도 저녁 제때</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -10739,6 +10634,114 @@
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>단 음료는 무가당으로</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 끼는 싱겁게 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금이라도 단백질 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단백질 한 입 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 간단하게 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심 늦지 않게 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>고기와 쌈 채소 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스는 따로 받기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 가볍게 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 끼니에 채소 넣기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 반찬 절반은 채소</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치는 접시에 덜기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 생선 · 두부로</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹을 수 있는 것 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 저녁 국물 줄이기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼밥도 그릇에 덜기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>더운 날 물부터 마시기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 끼 천천히 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 아침 미리 정하기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>어제처럼 제때 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침에 우유 마시기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니마다 단백질 바꾸기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 끼 제때 챙기기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 어제처럼 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>연휴에도 제때 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>주말에도 저녁 챙기기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>약속 날에도 저녁 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -10860,7 +10863,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -10899,6 +10902,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11536,13 +11542,13 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31.05" customHeight="1">
+    <row r="1" spans="1:2" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11669,7 +11675,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -11683,7 +11689,7 @@
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.05" customHeight="1">
+    <row r="1" spans="1:12" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -13750,7 +13756,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:K65"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -13764,7 +13770,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.05" customHeight="1">
+    <row r="1" spans="1:11" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -15653,16 +15659,16 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="11" t="s">
-        <v>2445</v>
+        <v>2418</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>2446</v>
+        <v>2419</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>2447</v>
+        <v>2420</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>2448</v>
+        <v>2421</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>1413</v>
@@ -15671,7 +15677,7 @@
         <v>1197</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>2449</v>
+        <v>2422</v>
       </c>
     </row>
   </sheetData>
@@ -15689,7 +15695,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -15699,7 +15705,7 @@
     <col min="8" max="8" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.05" customHeight="1">
+    <row r="1" spans="1:8" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>84</v>
       </c>
@@ -16222,22 +16228,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="11" t="s">
-        <v>2445</v>
+        <v>2418</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>2450</v>
+        <v>2423</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>1433</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>2451</v>
+        <v>2424</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>1471</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>2452</v>
+        <v>2425</v>
       </c>
     </row>
   </sheetData>
@@ -16255,7 +16261,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
@@ -16265,7 +16271,7 @@
     <col min="6" max="6" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>131</v>
       </c>
@@ -16453,7 +16459,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -16465,7 +16471,7 @@
     <col min="8" max="8" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.05" customHeight="1">
+    <row r="1" spans="1:8" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -16892,7 +16898,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -16902,7 +16908,7 @@
     <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -17255,7 +17261,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -17266,7 +17272,7 @@
     <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.05" customHeight="1">
+    <row r="1" spans="1:9" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>186</v>
       </c>
@@ -18847,7 +18853,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -18858,7 +18864,7 @@
     <col min="7" max="7" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.05" customHeight="1">
+    <row r="1" spans="1:7" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>186</v>
       </c>
@@ -20429,7 +20435,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
@@ -20437,7 +20443,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.05" customHeight="1">
+    <row r="1" spans="1:5" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -20520,7 +20526,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -20528,7 +20534,7 @@
     <col min="5" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>154</v>
       </c>
@@ -20743,7 +20749,7 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -20754,7 +20760,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.05" customHeight="1">
+    <row r="1" spans="1:7" ht="31" customHeight="1">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -21643,7 +21649,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -21654,7 +21660,7 @@
     <col min="8" max="8" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.05" customHeight="1">
+    <row r="1" spans="1:8" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>160</v>
       </c>
@@ -22501,7 +22507,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -22514,7 +22520,7 @@
     <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.05" customHeight="1">
+    <row r="1" spans="1:9" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -22665,7 +22671,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -22675,7 +22681,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>154</v>
       </c>
@@ -22860,7 +22866,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -22868,7 +22874,7 @@
     <col min="4" max="4" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.05" customHeight="1">
+    <row r="1" spans="1:4" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
@@ -23500,58 +23506,58 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2381</v>
+        <v>2368</v>
       </c>
       <c r="B46" t="s">
-        <v>2460</v>
+        <v>2433</v>
       </c>
       <c r="C46" t="s">
-        <v>2461</v>
+        <v>2434</v>
       </c>
       <c r="D46" t="s">
-        <v>2462</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="11" t="s">
-        <v>2437</v>
+        <v>2410</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>2438</v>
+        <v>2411</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>2439</v>
+        <v>2412</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>2440</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="11" t="s">
-        <v>2441</v>
+        <v>2414</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>2442</v>
+        <v>2415</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>2443</v>
+        <v>2416</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>2444</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="11" t="s">
-        <v>2470</v>
+        <v>2443</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>2471</v>
+        <v>2444</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>2473</v>
+        <v>2446</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>2474</v>
+        <v>2447</v>
       </c>
     </row>
   </sheetData>
@@ -23566,7 +23572,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -23688,7 +23694,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -23719,7 +23725,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="34.049999999999997" customHeight="1">
+    <row r="2" spans="1:6" ht="34" customHeight="1">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -23736,7 +23742,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:M144"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -23813,7 +23819,7 @@
         <v>1960</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>2433</v>
+        <v>2408</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1961</v>
@@ -23891,7 +23897,7 @@
         <v>1965</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>2382</v>
+        <v>2369</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>1969</v>
@@ -23929,8 +23935,8 @@
       <c r="F5" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>2320</v>
+      <c r="G5" s="15" t="s">
+        <v>2467</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1972</v>
@@ -23967,7 +23973,7 @@
         <v>1960</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2321</v>
+        <v>2317</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>1974</v>
@@ -24006,7 +24012,7 @@
         <v>1965</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>1977</v>
@@ -24082,7 +24088,7 @@
         <v>1971</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>2323</v>
+        <v>2319</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>1982</v>
@@ -24119,7 +24125,7 @@
         <v>1960</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>1984</v>
@@ -24157,8 +24163,8 @@
       <c r="F11" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>2383</v>
+      <c r="G11" s="15" t="s">
+        <v>2448</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1987</v>
@@ -24197,7 +24203,7 @@
         <v>1965</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>2384</v>
+        <v>2370</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>1990</v>
@@ -24236,7 +24242,7 @@
         <v>1971</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>1993</v>
@@ -24350,8 +24356,8 @@
       <c r="F16" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>2326</v>
+      <c r="G16" s="15" t="s">
+        <v>2449</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>2001</v>
@@ -24388,7 +24394,7 @@
         <v>1971</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>2385</v>
+        <v>2371</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>2003</v>
@@ -24425,7 +24431,7 @@
         <v>1960</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>2327</v>
+        <v>2322</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>2006</v>
@@ -24462,7 +24468,7 @@
         <v>1965</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>2328</v>
+        <v>2323</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>2009</v>
@@ -24499,7 +24505,7 @@
         <v>1971</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>2329</v>
+        <v>2324</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>2011</v>
@@ -24537,8 +24543,8 @@
       <c r="F21" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>2432</v>
+      <c r="G21" s="15" t="s">
+        <v>2450</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>2013</v>
@@ -24577,7 +24583,7 @@
         <v>1965</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>2387</v>
+        <v>2372</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>2015</v>
@@ -24616,7 +24622,7 @@
         <v>1971</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>2330</v>
+        <v>2325</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>2017</v>
@@ -24655,7 +24661,7 @@
         <v>1960</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2331</v>
+        <v>2326</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>2019</v>
@@ -24694,7 +24700,7 @@
         <v>1965</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2388</v>
+        <v>2373</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>2021</v>
@@ -24733,7 +24739,7 @@
         <v>1971</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2434</v>
+        <v>2409</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>2023</v>
@@ -24766,7 +24772,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="13" t="s">
-        <v>2389</v>
+        <v>2374</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>2027</v>
@@ -24800,8 +24806,8 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="13" t="s">
-        <v>2386</v>
+      <c r="G28" s="15" t="s">
+        <v>2451</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>2029</v>
@@ -24836,7 +24842,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>2031</v>
@@ -24871,7 +24877,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="13" t="s">
-        <v>2390</v>
+        <v>2375</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>2034</v>
@@ -24903,8 +24909,8 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="13" t="s">
-        <v>2391</v>
+      <c r="G31" s="15" t="s">
+        <v>2452</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>2036</v>
@@ -24937,7 +24943,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="13" t="s">
-        <v>2392</v>
+        <v>2376</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>2038</v>
@@ -24973,8 +24979,8 @@
       <c r="F33" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>2333</v>
+      <c r="G33" s="15" t="s">
+        <v>2468</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>2040</v>
@@ -25012,8 +25018,8 @@
       <c r="F34" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G34" s="13" t="s">
-        <v>2393</v>
+      <c r="G34" s="15" t="s">
+        <v>2453</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>2043</v>
@@ -25050,7 +25056,7 @@
         <v>1971</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>2334</v>
+        <v>2328</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>2045</v>
@@ -25089,7 +25095,7 @@
         <v>1971</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>2394</v>
+        <v>2377</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>2047</v>
@@ -25128,7 +25134,7 @@
         <v>1960</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>2335</v>
+        <v>2329</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>2049</v>
@@ -25164,8 +25170,8 @@
       <c r="F38" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G38" s="13" t="s">
-        <v>2336</v>
+      <c r="G38" s="15" t="s">
+        <v>2454</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>2051</v>
@@ -25204,7 +25210,7 @@
         <v>1965</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>2337</v>
+        <v>2330</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>2054</v>
@@ -25243,7 +25249,7 @@
         <v>1971</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>2338</v>
+        <v>2331</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>2056</v>
@@ -25319,7 +25325,7 @@
         <v>1960</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>2395</v>
+        <v>2378</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>2061</v>
@@ -25432,7 +25438,7 @@
         <v>1971</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>2339</v>
+        <v>2332</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>2069</v>
@@ -25510,7 +25516,7 @@
         <v>1960</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>2396</v>
+        <v>2379</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>2074</v>
@@ -25547,7 +25553,7 @@
         <v>1965</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>2340</v>
+        <v>2333</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>2076</v>
@@ -25586,7 +25592,7 @@
         <v>1965</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>2397</v>
+        <v>2380</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>2078</v>
@@ -25624,8 +25630,8 @@
       <c r="F50" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G50" s="13" t="s">
-        <v>2398</v>
+      <c r="G50" s="15" t="s">
+        <v>2455</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>2080</v>
@@ -25662,7 +25668,7 @@
         <v>1971</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>2341</v>
+        <v>2334</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>2082</v>
@@ -25701,7 +25707,7 @@
         <v>1960</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>2399</v>
+        <v>2381</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>2084</v>
@@ -25777,7 +25783,7 @@
         <v>1960</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>2342</v>
+        <v>2335</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>2089</v>
@@ -25853,7 +25859,7 @@
         <v>1965</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>2400</v>
+        <v>2382</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>2094</v>
@@ -25891,8 +25897,8 @@
       <c r="F57" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G57" s="13" t="s">
-        <v>2401</v>
+      <c r="G57" s="15" t="s">
+        <v>2469</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>2096</v>
@@ -25929,7 +25935,7 @@
         <v>1960</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>2343</v>
+        <v>2336</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>2098</v>
@@ -25968,7 +25974,7 @@
         <v>1960</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>2402</v>
+        <v>2383</v>
       </c>
       <c r="H59" s="9" t="s">
         <v>2100</v>
@@ -26007,7 +26013,7 @@
         <v>1965</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>2403</v>
+        <v>2384</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>2102</v>
@@ -26046,7 +26052,7 @@
         <v>1965</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>2344</v>
+        <v>2337</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>2104</v>
@@ -26118,7 +26124,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="13" t="s">
-        <v>2404</v>
+        <v>2385</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>2109</v>
@@ -26153,7 +26159,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="13" t="s">
-        <v>2345</v>
+        <v>2338</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>2111</v>
@@ -26191,8 +26197,8 @@
       <c r="F65" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G65" s="13" t="s">
-        <v>2405</v>
+      <c r="G65" s="15" t="s">
+        <v>2456</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>2113</v>
@@ -26231,7 +26237,7 @@
         <v>1971</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>2406</v>
+        <v>2386</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>2115</v>
@@ -26269,8 +26275,8 @@
       <c r="F67" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G67" s="13" t="s">
-        <v>2346</v>
+      <c r="G67" s="15" t="s">
+        <v>2470</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>2117</v>
@@ -26307,7 +26313,7 @@
         <v>1965</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>2119</v>
@@ -26345,8 +26351,8 @@
       <c r="F69" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G69" s="13" t="s">
-        <v>2348</v>
+      <c r="G69" s="15" t="s">
+        <v>2457</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>2121</v>
@@ -26384,8 +26390,8 @@
       <c r="F70" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G70" s="13" t="s">
-        <v>2407</v>
+      <c r="G70" s="15" t="s">
+        <v>2458</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>2123</v>
@@ -26461,7 +26467,7 @@
         <v>1960</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>2408</v>
+        <v>2387</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>2128</v>
@@ -26539,7 +26545,7 @@
         <v>1965</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>2349</v>
+        <v>2340</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>2133</v>
@@ -26578,7 +26584,7 @@
         <v>1965</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>2409</v>
+        <v>2388</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>2135</v>
@@ -26614,8 +26620,8 @@
       <c r="F76" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G76" s="13" t="s">
-        <v>2350</v>
+      <c r="G76" s="15" t="s">
+        <v>2459</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>2137</v>
@@ -26653,11 +26659,11 @@
       <c r="F77" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="G77" s="15" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>2139</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>2140</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="9"/>
@@ -26673,7 +26679,7 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="9" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>842</v>
@@ -26691,17 +26697,17 @@
         <v>1960</v>
       </c>
       <c r="G78" s="9" t="s">
+        <v>2141</v>
+      </c>
+      <c r="H78" s="9" t="s">
         <v>2142</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>2143</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J78" s="9"/>
       <c r="K78" s="9" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>1963</v>
@@ -26712,7 +26718,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="9" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>842</v>
@@ -26730,17 +26736,17 @@
         <v>1965</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>2351</v>
+        <v>2341</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J79" s="9"/>
       <c r="K79" s="9" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="L79" s="9" t="s">
         <v>2052</v>
@@ -26751,7 +26757,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="9" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>842</v>
@@ -26769,10 +26775,10 @@
         <v>1971</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>2410</v>
+        <v>2389</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>956</v>
@@ -26790,7 +26796,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="9" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>842</v>
@@ -26808,10 +26814,10 @@
         <v>1960</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>2411</v>
+        <v>2390</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>957</v>
@@ -26829,7 +26835,7 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="9" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>842</v>
@@ -26847,10 +26853,10 @@
         <v>1965</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>2412</v>
+        <v>2391</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>959</v>
@@ -26868,7 +26874,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="9" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>842</v>
@@ -26886,10 +26892,10 @@
         <v>1965</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>2352</v>
+        <v>2342</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="I83" s="9" t="s">
         <v>957</v>
@@ -26907,7 +26913,7 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="9" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>842</v>
@@ -26924,11 +26930,11 @@
       <c r="F84" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G84" s="13" t="s">
-        <v>2413</v>
+      <c r="G84" s="15" t="s">
+        <v>2460</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="9"/>
@@ -26944,7 +26950,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="9" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>842</v>
@@ -26962,10 +26968,10 @@
         <v>1960</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>2353</v>
+        <v>2343</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
@@ -26981,7 +26987,7 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="9" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>842</v>
@@ -26999,10 +27005,10 @@
         <v>1960</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>2414</v>
+        <v>2392</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="9"/>
@@ -27018,7 +27024,7 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="9" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>842</v>
@@ -27035,11 +27041,11 @@
       <c r="F87" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G87" s="13" t="s">
-        <v>2435</v>
+      <c r="G87" s="15" t="s">
+        <v>2472</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="9"/>
@@ -27055,7 +27061,7 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="9" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>842</v>
@@ -27073,10 +27079,10 @@
         <v>1965</v>
       </c>
       <c r="G88" s="9" t="s">
+        <v>2163</v>
+      </c>
+      <c r="H88" s="9" t="s">
         <v>2164</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>2165</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>957</v>
@@ -27094,7 +27100,7 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="9" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>842</v>
@@ -27112,10 +27118,10 @@
         <v>1971</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="9"/>
@@ -27131,7 +27137,7 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="9" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>842</v>
@@ -27149,10 +27155,10 @@
         <v>1965</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>2354</v>
+        <v>2344</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>958</v>
@@ -27162,7 +27168,7 @@
         <v>1985</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="M90" s="9">
         <v>112</v>
@@ -27170,7 +27176,7 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>842</v>
@@ -27188,10 +27194,10 @@
         <v>1971</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>2416</v>
+        <v>2394</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="I91" s="9" t="s">
         <v>955</v>
@@ -27209,7 +27215,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="9" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>842</v>
@@ -27227,10 +27233,10 @@
         <v>1971</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>2417</v>
+        <v>2395</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>955</v>
@@ -27248,7 +27254,7 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="9" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>842</v>
@@ -27266,10 +27272,10 @@
         <v>1960</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>2418</v>
+        <v>2396</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
@@ -27285,7 +27291,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="9" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>842</v>
@@ -27303,10 +27309,10 @@
         <v>1960</v>
       </c>
       <c r="G94" s="9" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H94" s="9" t="s">
         <v>2178</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>2179</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="9"/>
@@ -27322,7 +27328,7 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="9" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>842</v>
@@ -27340,10 +27346,10 @@
         <v>1971</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="I95" s="9" t="s">
         <v>955</v>
@@ -27361,7 +27367,7 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="9" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>842</v>
@@ -27379,10 +27385,10 @@
         <v>1971</v>
       </c>
       <c r="G96" s="9" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H96" s="9" t="s">
         <v>2183</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>2184</v>
       </c>
       <c r="I96" s="9" t="s">
         <v>955</v>
@@ -27400,7 +27406,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="9" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>842</v>
@@ -27418,10 +27424,10 @@
         <v>1960</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>2420</v>
+        <v>2398</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="9"/>
@@ -27437,7 +27443,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="9" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>842</v>
@@ -27454,11 +27460,11 @@
       <c r="F98" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G98" s="13" t="s">
-        <v>2436</v>
+      <c r="G98" s="15" t="s">
+        <v>2473</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="9"/>
@@ -27474,7 +27480,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="9" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>842</v>
@@ -27492,20 +27498,20 @@
         <v>1960</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>2355</v>
+        <v>2345</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="9" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="L99" s="9" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="M99" s="9">
         <v>125</v>
@@ -27513,7 +27519,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="9" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>842</v>
@@ -27531,10 +27537,10 @@
         <v>1960</v>
       </c>
       <c r="G100" s="9" t="s">
+        <v>2191</v>
+      </c>
+      <c r="H100" s="9" t="s">
         <v>2192</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>2193</v>
       </c>
       <c r="I100" s="9" t="s">
         <v>957</v>
@@ -27552,7 +27558,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="9" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>842</v>
@@ -27570,10 +27576,10 @@
         <v>1971</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>2195</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>2196</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>957</v>
@@ -27591,7 +27597,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="9" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>842</v>
@@ -27609,10 +27615,10 @@
         <v>1965</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>2356</v>
+        <v>2346</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="I102" s="9"/>
       <c r="J102" s="9"/>
@@ -27628,7 +27634,7 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="9" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>842</v>
@@ -27646,10 +27652,10 @@
         <v>1965</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>2421</v>
+        <v>2399</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="I103" s="9" t="s">
         <v>956</v>
@@ -27667,7 +27673,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="9" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>842</v>
@@ -27681,10 +27687,10 @@
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
       <c r="G104" s="13" t="s">
-        <v>2357</v>
+        <v>2347</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>957</v>
@@ -27702,7 +27708,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="9" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>842</v>
@@ -27715,11 +27721,11 @@
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
-      <c r="G105" s="13" t="s">
-        <v>2358</v>
+      <c r="G105" s="15" t="s">
+        <v>2461</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="I105" s="9" t="s">
         <v>957</v>
@@ -27737,7 +27743,7 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="9" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>842</v>
@@ -27751,10 +27757,10 @@
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="13" t="s">
-        <v>2359</v>
+        <v>2348</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>957</v>
@@ -27772,7 +27778,7 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="9" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>842</v>
@@ -27785,11 +27791,11 @@
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
-      <c r="G107" s="9" t="s">
-        <v>2208</v>
+      <c r="G107" s="15" t="s">
+        <v>2462</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>956</v>
@@ -27807,7 +27813,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="9" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>842</v>
@@ -27825,10 +27831,10 @@
         <v>1971</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>2422</v>
+        <v>2400</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>955</v>
@@ -27846,7 +27852,7 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="9" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>842</v>
@@ -27863,11 +27869,11 @@
       <c r="F109" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G109" s="13" t="s">
-        <v>2360</v>
+      <c r="G109" s="15" t="s">
+        <v>2474</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="9"/>
@@ -27883,7 +27889,7 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="9" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>842</v>
@@ -27901,10 +27907,10 @@
         <v>1971</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>957</v>
@@ -27922,7 +27928,7 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="9" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>842</v>
@@ -27940,10 +27946,10 @@
         <v>1971</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>955</v>
@@ -27961,7 +27967,7 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="9" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>842</v>
@@ -27979,10 +27985,10 @@
         <v>1971</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>2423</v>
+        <v>2401</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>959</v>
@@ -28000,7 +28006,7 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="9" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>842</v>
@@ -28018,10 +28024,10 @@
         <v>1960</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>2361</v>
+        <v>2349</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="9"/>
@@ -28037,7 +28043,7 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="9" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>842</v>
@@ -28054,18 +28060,18 @@
       <c r="F114" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G114" s="13" t="s">
-        <v>2424</v>
+      <c r="G114" s="15" t="s">
+        <v>2463</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="I114" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J114" s="9"/>
       <c r="K114" s="9" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="L114" s="9" t="s">
         <v>2052</v>
@@ -28076,7 +28082,7 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="9" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>842</v>
@@ -28094,10 +28100,10 @@
         <v>1960</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="I115" s="9" t="s">
         <v>957</v>
@@ -28115,7 +28121,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="9" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>842</v>
@@ -28133,10 +28139,10 @@
         <v>1960</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>2425</v>
+        <v>2402</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="I116" s="9" t="s">
         <v>957</v>
@@ -28154,7 +28160,7 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="9" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>842</v>
@@ -28172,10 +28178,10 @@
         <v>1960</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="I117" s="9" t="s">
         <v>957</v>
@@ -28193,7 +28199,7 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="9" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>842</v>
@@ -28211,10 +28217,10 @@
         <v>1960</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="I118" s="9" t="s">
         <v>957</v>
@@ -28232,7 +28238,7 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="9" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>842</v>
@@ -28250,10 +28256,10 @@
         <v>1965</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="I119" s="9" t="s">
         <v>955</v>
@@ -28271,7 +28277,7 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="9" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>842</v>
@@ -28289,10 +28295,10 @@
         <v>1965</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="I120" s="9" t="s">
         <v>959</v>
@@ -28310,7 +28316,7 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="9" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>842</v>
@@ -28328,10 +28334,10 @@
         <v>1965</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>2362</v>
+        <v>2350</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="I121" s="9" t="s">
         <v>957</v>
@@ -28349,7 +28355,7 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="9" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>842</v>
@@ -28367,10 +28373,10 @@
         <v>1965</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="I122" s="9" t="s">
         <v>956</v>
@@ -28388,7 +28394,7 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="9" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>842</v>
@@ -28406,10 +28412,10 @@
         <v>1965</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>2426</v>
+        <v>2403</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="9"/>
@@ -28425,7 +28431,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="9" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>842</v>
@@ -28443,10 +28449,10 @@
         <v>1960</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="I124" s="9" t="s">
         <v>956</v>
@@ -28464,7 +28470,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="9" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>842</v>
@@ -28482,10 +28488,10 @@
         <v>1960</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>2427</v>
+        <v>2404</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="9"/>
@@ -28501,7 +28507,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="9" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>842</v>
@@ -28518,11 +28524,11 @@
       <c r="F126" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G126" s="9" t="s">
-        <v>2256</v>
+      <c r="G126" s="15" t="s">
+        <v>2464</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="I126" s="9" t="s">
         <v>958</v>
@@ -28540,7 +28546,7 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="9" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>842</v>
@@ -28558,10 +28564,10 @@
         <v>1960</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="9"/>
@@ -28577,7 +28583,7 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="9" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>842</v>
@@ -28595,10 +28601,10 @@
         <v>1960</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>2363</v>
+        <v>2351</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="I128" s="9" t="s">
         <v>958</v>
@@ -28616,7 +28622,7 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="9" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>842</v>
@@ -28630,10 +28636,10 @@
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
       <c r="G129" s="9" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="I129" s="9" t="s">
         <v>957</v>
@@ -28651,7 +28657,7 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="9" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>842</v>
@@ -28665,10 +28671,10 @@
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
       <c r="G130" s="9" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="I130" s="9"/>
       <c r="J130" s="9"/>
@@ -28684,7 +28690,7 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="9" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>842</v>
@@ -28698,10 +28704,10 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="13" t="s">
-        <v>2428</v>
+        <v>2405</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="9"/>
@@ -28717,7 +28723,7 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>842</v>
@@ -28735,18 +28741,18 @@
         <v>1971</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>2364</v>
+        <v>2352</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="9"/>
       <c r="K132" s="9" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="L132" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="M132" s="9">
         <v>173</v>
@@ -28754,7 +28760,7 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="9" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>842</v>
@@ -28772,18 +28778,18 @@
         <v>1971</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>2365</v>
+        <v>2353</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="9"/>
       <c r="K133" s="9" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="M133" s="9">
         <v>174</v>
@@ -28791,7 +28797,7 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="9" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>842</v>
@@ -28809,18 +28815,18 @@
         <v>1971</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>2366</v>
+        <v>2354</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="I134" s="9"/>
       <c r="J134" s="9"/>
       <c r="K134" s="9" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="M134" s="9">
         <v>175</v>
@@ -28828,7 +28834,7 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="9" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>842</v>
@@ -28846,18 +28852,18 @@
         <v>1971</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>2429</v>
+        <v>2406</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="M135" s="9">
         <v>176</v>
@@ -28865,7 +28871,7 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="9" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>842</v>
@@ -28882,19 +28888,19 @@
       <c r="F136" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G136" s="13" t="s">
-        <v>2367</v>
+      <c r="G136" s="15" t="s">
+        <v>2465</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="I136" s="9"/>
       <c r="J136" s="9"/>
       <c r="K136" s="9" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="L136" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="M136" s="9">
         <v>177</v>
@@ -28902,7 +28908,7 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="9" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>842</v>
@@ -28920,10 +28926,10 @@
         <v>1960</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>2368</v>
+        <v>2355</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="9"/>
@@ -28931,7 +28937,7 @@
         <v>1962</v>
       </c>
       <c r="L137" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M137" s="9">
         <v>165</v>
@@ -28939,7 +28945,7 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="9" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>842</v>
@@ -28957,10 +28963,10 @@
         <v>1965</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>2369</v>
+        <v>2356</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="I138" s="9"/>
       <c r="J138" s="9"/>
@@ -28968,7 +28974,7 @@
         <v>1962</v>
       </c>
       <c r="L138" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M138" s="9">
         <v>166</v>
@@ -28976,7 +28982,7 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="9" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="B139" s="9" t="s">
         <v>842</v>
@@ -28994,18 +29000,18 @@
         <v>1960</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>2370</v>
+        <v>2357</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="9"/>
       <c r="K139" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="L139" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M139" s="9">
         <v>167</v>
@@ -29013,7 +29019,7 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="9" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>842</v>
@@ -29031,18 +29037,18 @@
         <v>1965</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>2430</v>
+        <v>2407</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="I140" s="9"/>
       <c r="J140" s="9"/>
       <c r="K140" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="L140" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M140" s="9">
         <v>168</v>
@@ -29050,7 +29056,7 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="9" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>842</v>
@@ -29068,18 +29074,18 @@
         <v>1960</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>2371</v>
+        <v>2358</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="9"/>
       <c r="K141" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="L141" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M141" s="9">
         <v>169</v>
@@ -29087,7 +29093,7 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="9" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>842</v>
@@ -29105,18 +29111,18 @@
         <v>1965</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>2372</v>
+        <v>2359</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="I142" s="9"/>
       <c r="J142" s="9"/>
       <c r="K142" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="L142" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M142" s="9">
         <v>170</v>
@@ -29124,7 +29130,7 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="9" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>842</v>
@@ -29142,18 +29148,18 @@
         <v>1960</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>2373</v>
+        <v>2360</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="9"/>
       <c r="K143" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="L143" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M143" s="9">
         <v>171</v>
@@ -29161,7 +29167,7 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>842</v>
@@ -29174,11 +29180,11 @@
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
-      <c r="G144" s="13" t="s">
-        <v>2431</v>
+      <c r="G144" s="15" t="s">
+        <v>2466</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="I144" s="9"/>
       <c r="J144" s="9"/>
@@ -29186,7 +29192,7 @@
         <v>1962</v>
       </c>
       <c r="L144" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="M144" s="9">
         <v>172</v>
@@ -29204,7 +29210,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:K144"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -29261,10 +29267,10 @@
         <v>842</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>326</v>
@@ -29292,10 +29298,10 @@
         <v>842</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>326</v>
@@ -29439,10 +29445,10 @@
         <v>842</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>326</v>
@@ -29557,10 +29563,10 @@
         <v>842</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>326</v>
@@ -29994,10 +30000,10 @@
         <v>842</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>326</v>
@@ -30054,10 +30060,10 @@
         <v>842</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>326</v>
@@ -30114,10 +30120,10 @@
         <v>842</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>326</v>
@@ -30145,10 +30151,10 @@
         <v>842</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>326</v>
@@ -30176,10 +30182,10 @@
         <v>842</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>326</v>
@@ -30207,7 +30213,7 @@
         <v>842</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>326</v>
@@ -30238,7 +30244,7 @@
         <v>842</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>326</v>
@@ -30269,13 +30275,13 @@
         <v>842</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>326</v>
@@ -30300,7 +30306,7 @@
         <v>842</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>326</v>
@@ -30331,7 +30337,7 @@
         <v>842</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>326</v>
@@ -30362,7 +30368,7 @@
         <v>842</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>326</v>
@@ -30393,7 +30399,7 @@
         <v>842</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>326</v>
@@ -30424,7 +30430,7 @@
         <v>842</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>326</v>
@@ -30455,7 +30461,7 @@
         <v>842</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>326</v>
@@ -30486,7 +30492,7 @@
         <v>842</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>326</v>
@@ -30517,7 +30523,7 @@
         <v>842</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>326</v>
@@ -30548,7 +30554,7 @@
         <v>842</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>326</v>
@@ -30579,7 +30585,7 @@
         <v>842</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>326</v>
@@ -30610,7 +30616,7 @@
         <v>842</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>326</v>
@@ -30641,7 +30647,7 @@
         <v>842</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>326</v>
@@ -30672,7 +30678,7 @@
         <v>842</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>326</v>
@@ -30703,7 +30709,7 @@
         <v>842</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>326</v>
@@ -30734,7 +30740,7 @@
         <v>842</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>326</v>
@@ -30765,7 +30771,7 @@
         <v>842</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>326</v>
@@ -30796,10 +30802,10 @@
         <v>842</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>326</v>
@@ -30827,7 +30833,7 @@
         <v>842</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>326</v>
@@ -30858,7 +30864,7 @@
         <v>842</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>326</v>
@@ -30889,7 +30895,7 @@
         <v>842</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>326</v>
@@ -30920,7 +30926,7 @@
         <v>842</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>326</v>
@@ -30951,7 +30957,7 @@
         <v>842</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>326</v>
@@ -30982,7 +30988,7 @@
         <v>842</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>326</v>
@@ -31013,7 +31019,7 @@
         <v>842</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>326</v>
@@ -31044,7 +31050,7 @@
         <v>842</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>326</v>
@@ -31075,7 +31081,7 @@
         <v>842</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>326</v>
@@ -31106,10 +31112,10 @@
         <v>842</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>326</v>
@@ -31137,7 +31143,7 @@
         <v>842</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>326</v>
@@ -31168,10 +31174,10 @@
         <v>842</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>326</v>
@@ -31199,13 +31205,13 @@
         <v>842</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>326</v>
@@ -31230,7 +31236,7 @@
         <v>842</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>326</v>
@@ -31261,7 +31267,7 @@
         <v>842</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>326</v>
@@ -31292,7 +31298,7 @@
         <v>842</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>326</v>
@@ -31323,10 +31329,10 @@
         <v>842</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>326</v>
@@ -31354,7 +31360,7 @@
         <v>842</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>326</v>
@@ -31385,7 +31391,7 @@
         <v>842</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>326</v>
@@ -31416,7 +31422,7 @@
         <v>842</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>326</v>
@@ -31447,7 +31453,7 @@
         <v>842</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>326</v>
@@ -31478,7 +31484,7 @@
         <v>842</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>326</v>
@@ -31509,7 +31515,7 @@
         <v>842</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>326</v>
@@ -31540,10 +31546,10 @@
         <v>842</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>326</v>
@@ -31565,13 +31571,13 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="9" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>326</v>
@@ -31596,13 +31602,13 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="9" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D79" s="9" t="s">
         <v>326</v>
@@ -31627,13 +31633,13 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="9" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D80" s="9" t="s">
         <v>326</v>
@@ -31658,13 +31664,13 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="9" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>326</v>
@@ -31689,13 +31695,13 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="9" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>326</v>
@@ -31720,13 +31726,13 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="9" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>326</v>
@@ -31751,16 +31757,16 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="9" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>326</v>
@@ -31782,13 +31788,13 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="9" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>326</v>
@@ -31813,16 +31819,16 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="9" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>326</v>
@@ -31844,19 +31850,19 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="9" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>326</v>
@@ -31875,16 +31881,16 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="9" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>326</v>
@@ -31906,19 +31912,19 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="9" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>326</v>
@@ -31937,19 +31943,19 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="9" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>326</v>
@@ -31968,16 +31974,16 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="9" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>326</v>
@@ -31999,13 +32005,13 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="9" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>326</v>
@@ -32030,13 +32036,13 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="9" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>326</v>
@@ -32061,13 +32067,13 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="9" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>326</v>
@@ -32092,13 +32098,13 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="9" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>326</v>
@@ -32123,19 +32129,19 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="9" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>326</v>
@@ -32154,16 +32160,16 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="9" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>326</v>
@@ -32185,19 +32191,19 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="9" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>326</v>
@@ -32216,19 +32222,19 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="9" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>326</v>
@@ -32247,16 +32253,16 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="9" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>326</v>
@@ -32278,16 +32284,16 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="9" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>326</v>
@@ -32309,13 +32315,13 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="9" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>326</v>
@@ -32340,19 +32346,19 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="9" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>326</v>
@@ -32371,13 +32377,13 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="9" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>326</v>
@@ -32402,13 +32408,13 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="9" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>326</v>
@@ -32433,16 +32439,16 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="9" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>326</v>
@@ -32464,16 +32470,16 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="9" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>326</v>
@@ -32495,16 +32501,16 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="9" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>326</v>
@@ -32526,16 +32532,16 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="9" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>326</v>
@@ -32557,13 +32563,13 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="9" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>326</v>
@@ -32588,13 +32594,13 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="9" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>326</v>
@@ -32619,13 +32625,13 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="9" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>326</v>
@@ -32650,13 +32656,13 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="9" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>326</v>
@@ -32681,13 +32687,13 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="9" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>326</v>
@@ -32712,13 +32718,13 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="9" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>326</v>
@@ -32743,13 +32749,13 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="9" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>326</v>
@@ -32774,13 +32780,13 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="9" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>326</v>
@@ -32805,13 +32811,13 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="9" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>326</v>
@@ -32836,13 +32842,13 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="9" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>326</v>
@@ -32867,13 +32873,13 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="9" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D120" s="9" t="s">
         <v>326</v>
@@ -32898,13 +32904,13 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="9" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>326</v>
@@ -32929,13 +32935,13 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="9" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>326</v>
@@ -32960,13 +32966,13 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="9" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>326</v>
@@ -32991,13 +32997,13 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="9" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>326</v>
@@ -33022,13 +33028,13 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="9" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>326</v>
@@ -33053,13 +33059,13 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="9" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>326</v>
@@ -33084,13 +33090,13 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="9" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>326</v>
@@ -33115,13 +33121,13 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="9" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>326</v>
@@ -33146,13 +33152,13 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="9" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>326</v>
@@ -33177,13 +33183,13 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="9" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>326</v>
@@ -33208,16 +33214,16 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="9" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>326</v>
@@ -33239,13 +33245,13 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>326</v>
@@ -33270,13 +33276,13 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="9" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>326</v>
@@ -33301,13 +33307,13 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="9" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>326</v>
@@ -33332,13 +33338,13 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="9" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>326</v>
@@ -33363,13 +33369,13 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="9" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>326</v>
@@ -33394,16 +33400,16 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="9" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>326</v>
@@ -33425,16 +33431,16 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="9" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>326</v>
@@ -33456,16 +33462,16 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="9" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="B139" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>326</v>
@@ -33487,16 +33493,16 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="9" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>326</v>
@@ -33518,16 +33524,16 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="9" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>326</v>
@@ -33549,16 +33555,16 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="9" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>326</v>
@@ -33580,16 +33586,16 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="9" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>326</v>
@@ -33611,16 +33617,16 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>326</v>
@@ -33655,7 +33661,7 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:I295"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -33667,7 +33673,7 @@
     <col min="9" max="9" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.05" customHeight="1">
+    <row r="1" spans="1:9" ht="31" customHeight="1">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -33782,7 +33788,7 @@
         <v>238</v>
       </c>
       <c r="H5" t="s">
-        <v>2380</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
@@ -35802,7 +35808,7 @@
         <v>239</v>
       </c>
       <c r="H97" t="s">
-        <v>2380</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="24" customHeight="1">
@@ -40257,7 +40263,7 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -40268,7 +40274,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.05" customHeight="1">
+    <row r="1" spans="1:7" ht="31" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>90</v>
       </c>
@@ -40360,7 +40366,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="13.95" customHeight="1">
+    <row r="5" spans="1:7" ht="14" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>818</v>
       </c>
@@ -40429,7 +40435,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.95" customHeight="1">
+    <row r="8" spans="1:7" ht="14" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>832</v>
       </c>
@@ -40452,7 +40458,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="39.450000000000003" customHeight="1">
+    <row r="9" spans="1:7" ht="39.5" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>836</v>
       </c>
@@ -40490,7 +40496,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -40503,7 +40509,7 @@
     <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.05" customHeight="1">
+    <row r="1" spans="1:9" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>235</v>
       </c>
@@ -40766,28 +40772,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>2374</v>
+        <v>2361</v>
       </c>
       <c r="B10" t="s">
         <v>842</v>
       </c>
       <c r="C10" t="s">
-        <v>2453</v>
+        <v>2426</v>
       </c>
       <c r="D10" t="s">
-        <v>2375</v>
+        <v>2362</v>
       </c>
       <c r="E10" t="s">
-        <v>2454</v>
+        <v>2427</v>
       </c>
       <c r="F10" t="s">
-        <v>2455</v>
+        <v>2428</v>
       </c>
       <c r="G10" t="s">
-        <v>2456</v>
+        <v>2429</v>
       </c>
       <c r="H10" t="s">
-        <v>2457</v>
+        <v>2430</v>
       </c>
     </row>
   </sheetData>
@@ -40805,7 +40811,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -40815,7 +40821,7 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.05" customHeight="1">
+    <row r="1" spans="1:7" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>235</v>
       </c>
@@ -40898,7 +40904,7 @@
         <v>891</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>2472</v>
+        <v>2445</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -41082,7 +41088,7 @@
         <v>904</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>2463</v>
+        <v>2436</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -41105,7 +41111,7 @@
         <v>905</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>2464</v>
+        <v>2437</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -41149,7 +41155,7 @@
         <v>899</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>2465</v>
+        <v>2438</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -41170,7 +41176,7 @@
         <v>901</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>2466</v>
+        <v>2439</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -41214,7 +41220,7 @@
         <v>908</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>2467</v>
+        <v>2440</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -41237,7 +41243,7 @@
         <v>909</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>2468</v>
+        <v>2441</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -41386,7 +41392,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>2374</v>
+        <v>2361</v>
       </c>
       <c r="B26" t="s">
         <v>842</v>
@@ -41395,15 +41401,15 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>2376</v>
+        <v>2363</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2469</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>2374</v>
+        <v>2361</v>
       </c>
       <c r="B27" t="s">
         <v>842</v>
@@ -41412,15 +41418,15 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>2377</v>
+        <v>2364</v>
       </c>
       <c r="E27" t="s">
-        <v>2458</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>2374</v>
+        <v>2361</v>
       </c>
       <c r="B28" t="s">
         <v>842</v>
@@ -41429,10 +41435,10 @@
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>2378</v>
+        <v>2365</v>
       </c>
       <c r="E28" t="s">
-        <v>2459</v>
+        <v>2432</v>
       </c>
     </row>
   </sheetData>
@@ -41450,7 +41456,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -41464,7 +41470,7 @@
     <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.05" customHeight="1">
+    <row r="1" spans="1:11" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -41688,7 +41694,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>2379</v>
+        <v>2366</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>934</v>
@@ -41982,14 +41988,14 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.05" customHeight="1">
+    <row r="1" spans="1:3" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -42191,14 +42197,14 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="31.05" customHeight="1">
+    <row r="1" spans="1:3" ht="31" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C001D6-4AA1-45FE-8650-F70764074272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496149F0-0278-42B9-86BF-5EA09F3E1772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45260" yWindow="3530" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -8936,1252 +8936,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진단받고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중이신가요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>해당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세션의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>첫째</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문으로만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>노출</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>해당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진단받고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는지에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자기보고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>임상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>여부</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답이므로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>임상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확진이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모르겠어요가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뜻하지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>금지는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유지된다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>집계하지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모르겠어요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>question_role</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CONFIRMATION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> score_value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>집계와</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계산에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣거나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
-  </si>
-  <si>
     <t>절반 이하</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -10742,6 +9496,1510 @@
     <t>약속 날에도 저녁 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{질환명</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이신가요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세션의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>첫째</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문으로만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>해당</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는지에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자기보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>임상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>여부</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>자가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답이므로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>임상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확진이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모르겠어요가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뜻하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유지된다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>집계하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <t>아니요</t>
+  </si>
+  <si>
+    <r>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모르겠어요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>question_role이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CONFIRMATION</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> score_value</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>비어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어야</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>집계와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넣지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넣거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건수로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -10750,7 +11008,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10805,16 +11063,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -10863,7 +11111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -10895,16 +11143,10 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -23505,17 +23747,17 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" t="s">
+      <c r="A46" s="11" t="s">
         <v>2368</v>
       </c>
-      <c r="B46" t="s">
-        <v>2433</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2434</v>
-      </c>
-      <c r="D46" t="s">
-        <v>2435</v>
+      <c r="B46" s="11" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>2473</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>2474</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -23548,16 +23790,16 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="11" t="s">
-        <v>2443</v>
+        <v>2433</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>2444</v>
+        <v>2434</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>2446</v>
+        <v>2436</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>2447</v>
+        <v>2437</v>
       </c>
     </row>
   </sheetData>
@@ -23935,8 +24177,8 @@
       <c r="F5" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>2467</v>
+      <c r="G5" s="13" t="s">
+        <v>2457</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1972</v>
@@ -24163,8 +24405,8 @@
       <c r="F11" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>2448</v>
+      <c r="G11" s="13" t="s">
+        <v>2438</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1987</v>
@@ -24356,8 +24598,8 @@
       <c r="F16" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>2449</v>
+      <c r="G16" s="13" t="s">
+        <v>2439</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>2001</v>
@@ -24543,8 +24785,8 @@
       <c r="F21" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G21" s="15" t="s">
-        <v>2450</v>
+      <c r="G21" s="13" t="s">
+        <v>2440</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>2013</v>
@@ -24806,8 +25048,8 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="15" t="s">
-        <v>2451</v>
+      <c r="G28" s="13" t="s">
+        <v>2441</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>2029</v>
@@ -24909,8 +25151,8 @@
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="15" t="s">
-        <v>2452</v>
+      <c r="G31" s="13" t="s">
+        <v>2442</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>2036</v>
@@ -24979,8 +25221,8 @@
       <c r="F33" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>2468</v>
+      <c r="G33" s="13" t="s">
+        <v>2458</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>2040</v>
@@ -25018,8 +25260,8 @@
       <c r="F34" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>2453</v>
+      <c r="G34" s="13" t="s">
+        <v>2443</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>2043</v>
@@ -25170,8 +25412,8 @@
       <c r="F38" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G38" s="15" t="s">
-        <v>2454</v>
+      <c r="G38" s="13" t="s">
+        <v>2444</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>2051</v>
@@ -25630,8 +25872,8 @@
       <c r="F50" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G50" s="15" t="s">
-        <v>2455</v>
+      <c r="G50" s="13" t="s">
+        <v>2445</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>2080</v>
@@ -25897,8 +26139,8 @@
       <c r="F57" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G57" s="15" t="s">
-        <v>2469</v>
+      <c r="G57" s="13" t="s">
+        <v>2459</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>2096</v>
@@ -26197,8 +26439,8 @@
       <c r="F65" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>2456</v>
+      <c r="G65" s="13" t="s">
+        <v>2446</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>2113</v>
@@ -26275,8 +26517,8 @@
       <c r="F67" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G67" s="15" t="s">
-        <v>2470</v>
+      <c r="G67" s="13" t="s">
+        <v>2460</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>2117</v>
@@ -26351,8 +26593,8 @@
       <c r="F69" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G69" s="15" t="s">
-        <v>2457</v>
+      <c r="G69" s="13" t="s">
+        <v>2447</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>2121</v>
@@ -26390,8 +26632,8 @@
       <c r="F70" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G70" s="15" t="s">
-        <v>2458</v>
+      <c r="G70" s="13" t="s">
+        <v>2448</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>2123</v>
@@ -26620,8 +26862,8 @@
       <c r="F76" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>2459</v>
+      <c r="G76" s="13" t="s">
+        <v>2449</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>2137</v>
@@ -26659,8 +26901,8 @@
       <c r="F77" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G77" s="15" t="s">
-        <v>2471</v>
+      <c r="G77" s="13" t="s">
+        <v>2461</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>2139</v>
@@ -26930,8 +27172,8 @@
       <c r="F84" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G84" s="15" t="s">
-        <v>2460</v>
+      <c r="G84" s="13" t="s">
+        <v>2450</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>2155</v>
@@ -27041,8 +27283,8 @@
       <c r="F87" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G87" s="15" t="s">
-        <v>2472</v>
+      <c r="G87" s="13" t="s">
+        <v>2462</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>2161</v>
@@ -27460,8 +27702,8 @@
       <c r="F98" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G98" s="15" t="s">
-        <v>2473</v>
+      <c r="G98" s="13" t="s">
+        <v>2463</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>2187</v>
@@ -27721,8 +27963,8 @@
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
-      <c r="G105" s="15" t="s">
-        <v>2461</v>
+      <c r="G105" s="13" t="s">
+        <v>2451</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>2203</v>
@@ -27791,8 +28033,8 @@
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
-      <c r="G107" s="15" t="s">
-        <v>2462</v>
+      <c r="G107" s="13" t="s">
+        <v>2452</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>2207</v>
@@ -27869,8 +28111,8 @@
       <c r="F109" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>2474</v>
+      <c r="G109" s="13" t="s">
+        <v>2464</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>2211</v>
@@ -28060,8 +28302,8 @@
       <c r="F114" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G114" s="15" t="s">
-        <v>2463</v>
+      <c r="G114" s="13" t="s">
+        <v>2453</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>2223</v>
@@ -28524,8 +28766,8 @@
       <c r="F126" s="9" t="s">
         <v>1960</v>
       </c>
-      <c r="G126" s="15" t="s">
-        <v>2464</v>
+      <c r="G126" s="13" t="s">
+        <v>2454</v>
       </c>
       <c r="H126" s="9" t="s">
         <v>2254</v>
@@ -28888,8 +29130,8 @@
       <c r="F136" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G136" s="15" t="s">
-        <v>2465</v>
+      <c r="G136" s="13" t="s">
+        <v>2455</v>
       </c>
       <c r="H136" s="9" t="s">
         <v>2280</v>
@@ -29180,8 +29422,8 @@
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
-      <c r="G144" s="15" t="s">
-        <v>2466</v>
+      <c r="G144" s="13" t="s">
+        <v>2456</v>
       </c>
       <c r="H144" s="9" t="s">
         <v>2299</v>
@@ -33787,7 +34029,7 @@
       <c r="F5" t="s">
         <v>238</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="11" t="s">
         <v>2367</v>
       </c>
     </row>
@@ -35807,7 +36049,7 @@
       <c r="G97" t="s">
         <v>239</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="11" t="s">
         <v>2367</v>
       </c>
     </row>
@@ -40771,29 +41013,29 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" t="s">
+      <c r="A10" s="11" t="s">
         <v>2361</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="C10" t="s">
-        <v>2426</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="11" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>2362</v>
       </c>
-      <c r="E10" t="s">
-        <v>2427</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2428</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2429</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2430</v>
+      <c r="E10" s="11" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>2467</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>2468</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>2469</v>
       </c>
     </row>
   </sheetData>
@@ -40903,8 +41145,8 @@
       <c r="D4" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>2445</v>
+      <c r="E4" s="12" t="s">
+        <v>2435</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -41087,8 +41329,8 @@
       <c r="D12" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>2436</v>
+      <c r="E12" s="12" t="s">
+        <v>2426</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -41110,8 +41352,8 @@
       <c r="D13" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>2437</v>
+      <c r="E13" s="12" t="s">
+        <v>2427</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -41154,8 +41396,8 @@
       <c r="D15" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>2438</v>
+      <c r="E15" s="12" t="s">
+        <v>2428</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -41175,8 +41417,8 @@
       <c r="D16" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>2439</v>
+      <c r="E16" s="12" t="s">
+        <v>2429</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -41219,8 +41461,8 @@
       <c r="D18" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>2440</v>
+      <c r="E18" s="12" t="s">
+        <v>2430</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -41242,8 +41484,8 @@
       <c r="D19" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>2441</v>
+      <c r="E19" s="12" t="s">
+        <v>2431</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -41391,54 +41633,54 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" t="s">
+      <c r="A26" s="11" t="s">
         <v>2361</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="11">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="11" t="s">
         <v>2363</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2442</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" t="s">
+      <c r="A27" s="11" t="s">
         <v>2361</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="11">
         <v>2</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="11" t="s">
         <v>2364</v>
       </c>
-      <c r="E27" t="s">
-        <v>2431</v>
+      <c r="E27" s="11" t="s">
+        <v>2470</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" t="s">
+      <c r="A28" s="11" t="s">
         <v>2361</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="11" t="s">
         <v>842</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="11">
         <v>3</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="11" t="s">
         <v>2365</v>
       </c>
-      <c r="E28" t="s">
-        <v>2432</v>
+      <c r="E28" s="11" t="s">
+        <v>2471</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496149F0-0278-42B9-86BF-5EA09F3E1772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6805286C-64E5-45C4-B85B-56B121437A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45260" yWindow="3530" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -5985,9 +5985,6 @@
     <t>DIET-P-0007</t>
   </si>
   <si>
-    <t>저녁은 채소부터 먼저</t>
-  </si>
-  <si>
     <t>채소 반찬부터 먹어 보는 행동이에요.</t>
   </si>
   <si>
@@ -6222,9 +6219,6 @@
     <t>DIET-P-0048</t>
   </si>
   <si>
-    <t>점심도 채소부터 먼저</t>
-  </si>
-  <si>
     <t>저녁뿐 아니라 점심에도 순서를 바꿔 보는 단계예요.</t>
   </si>
   <si>
@@ -6592,9 +6586,6 @@
   </si>
   <si>
     <t>DIET-P-0154</t>
-  </si>
-  <si>
-    <t>명절 음식은 국물 없이</t>
   </si>
   <si>
     <t>명절 식사에서도 국물 섭취량을 살펴봐요.</t>
@@ -7007,18 +6998,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 채소부터 먼저</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>한 잔은 물로 바꾸기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 단 음료 없이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>식사 중 수저 내려놓기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7039,10 +7022,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>간식으로 빈 끼 채우기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 세 끼 챙기기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7059,18 +7038,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 단 간식 없이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>김치는 먹을 만큼만</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>오늘 국물 없이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>우유 · 두유 한 잔</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7135,10 +7106,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>목마르면 물 먼저</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>마신 음료 적어 보기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7241,10 +7208,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>소스에 찍지 않기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>젓갈 · 장아찌 빼기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7257,10 +7220,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>삼겹살 대신 목살</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>드레싱은 반만</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7297,26 +7256,14 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>명절 상에도 나물 먼저</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>달달한 커피 쉬기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>후식 · 디저트 없이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>식탁에 소금 안 두기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>라면 · 즉석식품 없이</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁 후 부엌 정리</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7337,15 +7284,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>내 속도로 먹기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>국물 기름 걷어내기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁은 쉬운 것으로</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -9389,10 +9328,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>단 음료는 무가당으로</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>한 끼는 싱겁게 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -9405,10 +9340,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 간단하게 먹기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>점심 늦지 않게 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -9465,35 +9396,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>어제처럼 제때 먹기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침에 우유 마시기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>끼니마다 단백질 바꾸기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>세 끼 제때 챙기기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁 어제처럼 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>연휴에도 제때 먹기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주말에도 저녁 챙기기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>약속 날에도 저녁 먹기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -10999,6 +10910,98 @@
       </rPr>
       <t>거부</t>
     </r>
+  </si>
+  <si>
+    <t>세 끼 어제처럼 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침에 우유 곁들이기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 끼 평소대로 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>주말 저녁도 제때 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>약속 날도 제때 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>단 음료는 물로 바꾸기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식이라도 챙겨 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>부담 없는 저녁 차리기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스 없이 먹어보기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘은 국물 없이 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>후식 없이 식사 마치기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉석식품 오늘은 쉬기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>명절엔 국물 덜 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 간단한 것으로</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘은 단 음료 없이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 속도에 맞춰 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 채소부터 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니마다 채소부터 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심도 채소부터 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름 적은 부위로 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>명절에도 나물부터 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>목마르면 물부터 마시기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘은 단 간식 없이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15901,16 +15904,16 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="11" t="s">
-        <v>2418</v>
+        <v>2402</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>2419</v>
+        <v>2403</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>2420</v>
+        <v>2404</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>2421</v>
+        <v>2405</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>1413</v>
@@ -15919,7 +15922,7 @@
         <v>1197</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>2422</v>
+        <v>2406</v>
       </c>
     </row>
   </sheetData>
@@ -16470,22 +16473,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="11" t="s">
-        <v>2418</v>
+        <v>2402</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>2423</v>
+        <v>2407</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>1433</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>2424</v>
+        <v>2408</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>1471</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>2425</v>
+        <v>2409</v>
       </c>
     </row>
   </sheetData>
@@ -23748,58 +23751,58 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="11" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>2472</v>
+        <v>2449</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>2473</v>
+        <v>2450</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>2474</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="11" t="s">
-        <v>2410</v>
+        <v>2394</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>2411</v>
+        <v>2395</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>2412</v>
+        <v>2396</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>2413</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="11" t="s">
-        <v>2414</v>
+        <v>2398</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>2415</v>
+        <v>2399</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>2416</v>
+        <v>2400</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>2417</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="11" t="s">
-        <v>2433</v>
+        <v>2417</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>2434</v>
+        <v>2418</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>2436</v>
+        <v>2420</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>2437</v>
+        <v>2421</v>
       </c>
     </row>
   </sheetData>
@@ -24061,7 +24064,7 @@
         <v>1960</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>2408</v>
+        <v>2392</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1961</v>
@@ -24139,7 +24142,7 @@
         <v>1965</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>2369</v>
+        <v>2360</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>1969</v>
@@ -24178,7 +24181,7 @@
         <v>1971</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>2457</v>
+        <v>2452</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1972</v>
@@ -24215,7 +24218,7 @@
         <v>1960</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>1974</v>
@@ -24254,7 +24257,7 @@
         <v>1965</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>1977</v>
@@ -24292,11 +24295,11 @@
       <c r="F8" s="9" t="s">
         <v>1965</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="13" t="s">
+        <v>2468</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>1979</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>1980</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -24312,7 +24315,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="9" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>842</v>
@@ -24330,10 +24333,10 @@
         <v>1971</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>2319</v>
+        <v>2469</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -24349,7 +24352,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>842</v>
@@ -24367,17 +24370,17 @@
         <v>1960</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>2320</v>
+        <v>2316</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>1963</v>
@@ -24388,7 +24391,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>842</v>
@@ -24406,17 +24409,17 @@
         <v>1965</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>2438</v>
+        <v>2457</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>1963</v>
@@ -24427,7 +24430,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>842</v>
@@ -24445,17 +24448,17 @@
         <v>1965</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>2370</v>
+        <v>2361</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J12" s="9"/>
       <c r="K12" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>1963</v>
@@ -24466,7 +24469,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>842</v>
@@ -24484,17 +24487,17 @@
         <v>1971</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>2321</v>
+        <v>2466</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>1963</v>
@@ -24505,7 +24508,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="9" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>842</v>
@@ -24523,17 +24526,17 @@
         <v>1960</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>1995</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>1996</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>1963</v>
@@ -24544,7 +24547,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>842</v>
@@ -24562,15 +24565,15 @@
         <v>1965</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>1998</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>1999</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>1963</v>
@@ -24581,7 +24584,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="9" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>842</v>
@@ -24599,15 +24602,15 @@
         <v>1965</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>2439</v>
+        <v>2422</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>1963</v>
@@ -24618,7 +24621,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="9" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>842</v>
@@ -24636,10 +24639,10 @@
         <v>1971</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>2371</v>
+        <v>2362</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -24647,7 +24650,7 @@
         <v>1962</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M17" s="9">
         <v>17</v>
@@ -24655,7 +24658,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>842</v>
@@ -24673,15 +24676,15 @@
         <v>1960</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>2322</v>
+        <v>2317</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>1963</v>
@@ -24692,7 +24695,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>842</v>
@@ -24710,18 +24713,18 @@
         <v>1965</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>2323</v>
+        <v>2318</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M19" s="9">
         <v>19</v>
@@ -24729,7 +24732,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="9" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>842</v>
@@ -24747,20 +24750,20 @@
         <v>1971</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>2324</v>
+        <v>2319</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M20" s="9">
         <v>20</v>
@@ -24768,7 +24771,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="9" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>842</v>
@@ -24786,10 +24789,10 @@
         <v>1960</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>2440</v>
+        <v>2423</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>957</v>
@@ -24807,7 +24810,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="9" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>842</v>
@@ -24825,10 +24828,10 @@
         <v>1965</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>2372</v>
+        <v>2363</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>957</v>
@@ -24846,7 +24849,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="9" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>842</v>
@@ -24864,10 +24867,10 @@
         <v>1971</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>2325</v>
+        <v>2320</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>957</v>
@@ -24885,7 +24888,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="9" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>842</v>
@@ -24903,10 +24906,10 @@
         <v>1960</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2326</v>
+        <v>2321</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>956</v>
@@ -24924,7 +24927,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="9" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>842</v>
@@ -24942,10 +24945,10 @@
         <v>1965</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2373</v>
+        <v>2364</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>959</v>
@@ -24963,7 +24966,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="9" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>842</v>
@@ -24981,15 +24984,15 @@
         <v>1971</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2409</v>
+        <v>2393</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>1963</v>
@@ -25000,7 +25003,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="9" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>842</v>
@@ -25009,15 +25012,15 @@
         <v>1958</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="13" t="s">
-        <v>2374</v>
+        <v>2365</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>957</v>
@@ -25027,7 +25030,7 @@
         <v>1962</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M27" s="9">
         <v>27</v>
@@ -25035,7 +25038,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="9" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>842</v>
@@ -25044,15 +25047,15 @@
         <v>1958</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="13" t="s">
-        <v>2441</v>
+        <v>2424</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>957</v>
@@ -25070,7 +25073,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="9" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>842</v>
@@ -25079,15 +25082,15 @@
         <v>1958</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>2327</v>
+        <v>2458</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>957</v>
@@ -25105,7 +25108,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="9" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>842</v>
@@ -25114,23 +25117,23 @@
         <v>1958</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="13" t="s">
-        <v>2375</v>
+        <v>2366</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M30" s="9">
         <v>30</v>
@@ -25138,7 +25141,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="9" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>842</v>
@@ -25147,15 +25150,15 @@
         <v>1958</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="13" t="s">
-        <v>2442</v>
+        <v>2459</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -25163,7 +25166,7 @@
         <v>1962</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M31" s="9">
         <v>31</v>
@@ -25171,7 +25174,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="9" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>842</v>
@@ -25180,20 +25183,20 @@
         <v>1958</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="13" t="s">
-        <v>2376</v>
+        <v>2367</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>1963</v>
@@ -25204,7 +25207,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="9" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>842</v>
@@ -25222,20 +25225,20 @@
         <v>1960</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2458</v>
+        <v>2453</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>957</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M33" s="9">
         <v>33</v>
@@ -25243,7 +25246,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="9" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>842</v>
@@ -25261,10 +25264,10 @@
         <v>1965</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>2443</v>
+        <v>2425</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
@@ -25280,7 +25283,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="9" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>842</v>
@@ -25298,10 +25301,10 @@
         <v>1971</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>957</v>
@@ -25319,7 +25322,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="9" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>842</v>
@@ -25337,10 +25340,10 @@
         <v>1971</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>2377</v>
+        <v>2368</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>957</v>
@@ -25358,7 +25361,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="9" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>842</v>
@@ -25376,15 +25379,15 @@
         <v>1960</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>2329</v>
+        <v>2323</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L37" s="9" t="s">
         <v>1963</v>
@@ -25395,7 +25398,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="9" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>842</v>
@@ -25413,10 +25416,10 @@
         <v>1960</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>2444</v>
+        <v>2426</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>957</v>
@@ -25426,7 +25429,7 @@
         <v>1975</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M38" s="9">
         <v>38</v>
@@ -25434,7 +25437,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="9" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>842</v>
@@ -25452,10 +25455,10 @@
         <v>1965</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>2330</v>
+        <v>2324</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>957</v>
@@ -25473,7 +25476,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="9" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>842</v>
@@ -25491,10 +25494,10 @@
         <v>1971</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>2331</v>
+        <v>2325</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>957</v>
@@ -25512,7 +25515,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="9" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>842</v>
@@ -25529,11 +25532,11 @@
       <c r="F41" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>2058</v>
+      <c r="G41" s="13" t="s">
+        <v>2470</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
@@ -25541,7 +25544,7 @@
         <v>1975</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M41" s="9">
         <v>41</v>
@@ -25549,7 +25552,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="9" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>842</v>
@@ -25567,15 +25570,15 @@
         <v>1960</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>2378</v>
+        <v>2369</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
       <c r="K42" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L42" s="9" t="s">
         <v>1963</v>
@@ -25586,7 +25589,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="9" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>842</v>
@@ -25604,17 +25607,17 @@
         <v>1960</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J43" s="9"/>
       <c r="K43" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>1963</v>
@@ -25625,7 +25628,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="9" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>842</v>
@@ -25643,10 +25646,10 @@
         <v>1965</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
@@ -25662,7 +25665,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="9" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>842</v>
@@ -25680,17 +25683,17 @@
         <v>1971</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>2332</v>
+        <v>2474</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>1963</v>
@@ -25701,7 +25704,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="9" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>842</v>
@@ -25719,17 +25722,17 @@
         <v>1960</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J46" s="9"/>
       <c r="K46" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>1963</v>
@@ -25740,7 +25743,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="9" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>842</v>
@@ -25758,10 +25761,10 @@
         <v>1960</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>2379</v>
+        <v>2460</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="9"/>
@@ -25777,7 +25780,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="9" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>842</v>
@@ -25795,20 +25798,20 @@
         <v>1965</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>2333</v>
+        <v>2326</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M48" s="9">
         <v>48</v>
@@ -25816,7 +25819,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="9" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>842</v>
@@ -25834,17 +25837,17 @@
         <v>1965</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>1963</v>
@@ -25855,7 +25858,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="9" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>842</v>
@@ -25873,10 +25876,10 @@
         <v>1971</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>2445</v>
+        <v>2427</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
@@ -25884,7 +25887,7 @@
         <v>1962</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M50" s="9">
         <v>50</v>
@@ -25892,7 +25895,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="9" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>842</v>
@@ -25910,17 +25913,17 @@
         <v>1971</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>2334</v>
+        <v>2461</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J51" s="9"/>
       <c r="K51" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>1963</v>
@@ -25931,7 +25934,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="9" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>842</v>
@@ -25949,15 +25952,15 @@
         <v>1960</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>2381</v>
+        <v>2371</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
       <c r="K52" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>1963</v>
@@ -25968,7 +25971,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="9" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>842</v>
@@ -25986,10 +25989,10 @@
         <v>1960</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>957</v>
@@ -26007,7 +26010,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="9" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>842</v>
@@ -26025,20 +26028,20 @@
         <v>1960</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>2335</v>
+        <v>2327</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>957</v>
       </c>
       <c r="J54" s="9"/>
       <c r="K54" s="9" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M54" s="9">
         <v>54</v>
@@ -26046,7 +26049,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="9" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>842</v>
@@ -26064,10 +26067,10 @@
         <v>1965</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
@@ -26075,7 +26078,7 @@
         <v>1975</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M55" s="9">
         <v>55</v>
@@ -26083,7 +26086,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="9" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>842</v>
@@ -26101,10 +26104,10 @@
         <v>1965</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>2382</v>
+        <v>2372</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>957</v>
@@ -26114,7 +26117,7 @@
         <v>1975</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M56" s="9">
         <v>56</v>
@@ -26122,7 +26125,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="9" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>842</v>
@@ -26140,10 +26143,10 @@
         <v>1971</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>2459</v>
+        <v>2439</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
@@ -26159,7 +26162,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="9" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>842</v>
@@ -26177,17 +26180,17 @@
         <v>1960</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>2336</v>
+        <v>2328</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="I58" s="9" t="s">
         <v>959</v>
       </c>
       <c r="J58" s="9"/>
       <c r="K58" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L58" s="9" t="s">
         <v>1963</v>
@@ -26198,7 +26201,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="9" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>842</v>
@@ -26216,17 +26219,17 @@
         <v>1960</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>2383</v>
+        <v>2471</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="I59" s="9" t="s">
         <v>959</v>
       </c>
       <c r="J59" s="9"/>
       <c r="K59" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L59" s="9" t="s">
         <v>1963</v>
@@ -26237,7 +26240,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="9" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>842</v>
@@ -26255,17 +26258,17 @@
         <v>1965</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>2384</v>
+        <v>2373</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J60" s="9"/>
       <c r="K60" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>1963</v>
@@ -26276,7 +26279,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="9" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>842</v>
@@ -26294,15 +26297,15 @@
         <v>1965</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>2337</v>
+        <v>2329</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
       <c r="K61" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L61" s="9" t="s">
         <v>1963</v>
@@ -26313,7 +26316,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="9" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>842</v>
@@ -26331,10 +26334,10 @@
         <v>1971</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="I62" s="9" t="s">
         <v>955</v>
@@ -26352,7 +26355,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="9" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>842</v>
@@ -26361,25 +26364,25 @@
         <v>1958</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="13" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="I63" s="9" t="s">
         <v>957</v>
       </c>
       <c r="J63" s="9"/>
       <c r="K63" s="9" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M63" s="9">
         <v>63</v>
@@ -26387,7 +26390,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="9" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>842</v>
@@ -26396,25 +26399,25 @@
         <v>1958</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="13" t="s">
-        <v>2338</v>
+        <v>2330</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="I64" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J64" s="9"/>
       <c r="K64" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M64" s="9">
         <v>64</v>
@@ -26422,7 +26425,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="9" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>842</v>
@@ -26440,10 +26443,10 @@
         <v>1965</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>2446</v>
+        <v>2428</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>957</v>
@@ -26461,7 +26464,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="9" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>842</v>
@@ -26479,10 +26482,10 @@
         <v>1971</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>2386</v>
+        <v>2375</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>957</v>
@@ -26492,7 +26495,7 @@
         <v>1962</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M66" s="9">
         <v>67</v>
@@ -26500,7 +26503,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="9" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>842</v>
@@ -26518,10 +26521,10 @@
         <v>1971</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>2460</v>
+        <v>2454</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="9"/>
@@ -26537,7 +26540,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="9" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>842</v>
@@ -26555,10 +26558,10 @@
         <v>1965</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>2339</v>
+        <v>2331</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>957</v>
@@ -26576,7 +26579,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="9" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>842</v>
@@ -26594,17 +26597,17 @@
         <v>1971</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>2447</v>
+        <v>2429</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="I69" s="9" t="s">
         <v>957</v>
       </c>
       <c r="J69" s="9"/>
       <c r="K69" s="9" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L69" s="9" t="s">
         <v>1963</v>
@@ -26615,7 +26618,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="9" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>842</v>
@@ -26633,10 +26636,10 @@
         <v>1971</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>2448</v>
+        <v>2430</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="9"/>
@@ -26652,7 +26655,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="9" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>842</v>
@@ -26670,17 +26673,17 @@
         <v>1971</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="I71" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J71" s="9"/>
       <c r="K71" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L71" s="9" t="s">
         <v>1963</v>
@@ -26691,7 +26694,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="9" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>842</v>
@@ -26709,10 +26712,10 @@
         <v>1960</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>2387</v>
+        <v>2376</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="I72" s="9" t="s">
         <v>956</v>
@@ -26722,7 +26725,7 @@
         <v>1962</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M72" s="9">
         <v>79</v>
@@ -26730,7 +26733,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="9" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>842</v>
@@ -26748,10 +26751,10 @@
         <v>1960</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>956</v>
@@ -26761,7 +26764,7 @@
         <v>1962</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M73" s="9">
         <v>80</v>
@@ -26769,7 +26772,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="9" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>842</v>
@@ -26787,10 +26790,10 @@
         <v>1965</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>2340</v>
+        <v>2332</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="I74" s="9" t="s">
         <v>956</v>
@@ -26808,7 +26811,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="9" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>842</v>
@@ -26826,15 +26829,15 @@
         <v>1965</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>2388</v>
+        <v>2377</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L75" s="9" t="s">
         <v>1963</v>
@@ -26845,7 +26848,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="9" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>842</v>
@@ -26863,20 +26866,20 @@
         <v>1971</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>2449</v>
+        <v>2431</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J76" s="9"/>
       <c r="K76" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M76" s="9">
         <v>84</v>
@@ -26884,7 +26887,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="9" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>842</v>
@@ -26902,15 +26905,15 @@
         <v>1965</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>2461</v>
+        <v>2440</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="9"/>
       <c r="K77" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>1963</v>
@@ -26921,7 +26924,7 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="9" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>842</v>
@@ -26939,17 +26942,17 @@
         <v>1960</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J78" s="9"/>
       <c r="K78" s="9" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>1963</v>
@@ -26960,7 +26963,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="9" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>842</v>
@@ -26978,20 +26981,20 @@
         <v>1965</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>2341</v>
+        <v>2333</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J79" s="9"/>
       <c r="K79" s="9" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M79" s="9">
         <v>88</v>
@@ -26999,7 +27002,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="9" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>842</v>
@@ -27017,20 +27020,20 @@
         <v>1971</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>2389</v>
+        <v>2378</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J80" s="9"/>
       <c r="K80" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M80" s="9">
         <v>90</v>
@@ -27038,7 +27041,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="9" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>842</v>
@@ -27056,10 +27059,10 @@
         <v>1960</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>2390</v>
+        <v>2379</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>957</v>
@@ -27077,7 +27080,7 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="9" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>842</v>
@@ -27095,10 +27098,10 @@
         <v>1965</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>2391</v>
+        <v>2380</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>959</v>
@@ -27116,7 +27119,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="9" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>842</v>
@@ -27134,10 +27137,10 @@
         <v>1965</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>2342</v>
+        <v>2334</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="I83" s="9" t="s">
         <v>957</v>
@@ -27147,7 +27150,7 @@
         <v>1975</v>
       </c>
       <c r="L83" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M83" s="9">
         <v>94</v>
@@ -27155,7 +27158,7 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="9" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>842</v>
@@ -27173,10 +27176,10 @@
         <v>1971</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>2450</v>
+        <v>2432</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="9"/>
@@ -27192,7 +27195,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="9" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>842</v>
@@ -27210,18 +27213,18 @@
         <v>1960</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>2343</v>
+        <v>2335</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
       <c r="K85" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L85" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M85" s="9">
         <v>97</v>
@@ -27229,7 +27232,7 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="9" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>842</v>
@@ -27247,10 +27250,10 @@
         <v>1960</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>2392</v>
+        <v>2381</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="9"/>
@@ -27258,7 +27261,7 @@
         <v>1962</v>
       </c>
       <c r="L86" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M86" s="9">
         <v>98</v>
@@ -27266,7 +27269,7 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="9" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>842</v>
@@ -27284,10 +27287,10 @@
         <v>1971</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>2462</v>
+        <v>2441</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="9"/>
@@ -27303,7 +27306,7 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="9" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>842</v>
@@ -27321,10 +27324,10 @@
         <v>1965</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>957</v>
@@ -27342,7 +27345,7 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="9" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>842</v>
@@ -27360,18 +27363,18 @@
         <v>1971</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>2393</v>
+        <v>2472</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="9"/>
       <c r="K89" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M89" s="9">
         <v>108</v>
@@ -27379,7 +27382,7 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="9" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>842</v>
@@ -27397,20 +27400,20 @@
         <v>1965</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>2344</v>
+        <v>2336</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J90" s="9"/>
       <c r="K90" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="M90" s="9">
         <v>112</v>
@@ -27418,7 +27421,7 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="9" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>842</v>
@@ -27436,20 +27439,20 @@
         <v>1971</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>2394</v>
+        <v>2382</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I91" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J91" s="9"/>
       <c r="K91" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M91" s="9">
         <v>113</v>
@@ -27457,7 +27460,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="9" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>842</v>
@@ -27475,17 +27478,17 @@
         <v>1971</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>2395</v>
+        <v>2462</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I92" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J92" s="9"/>
       <c r="K92" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L92" s="9" t="s">
         <v>1963</v>
@@ -27496,7 +27499,7 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="9" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>842</v>
@@ -27514,10 +27517,10 @@
         <v>1960</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>2396</v>
+        <v>2383</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
@@ -27525,7 +27528,7 @@
         <v>1962</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M93" s="9">
         <v>115</v>
@@ -27533,7 +27536,7 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="9" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>842</v>
@@ -27551,10 +27554,10 @@
         <v>1960</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="I94" s="9"/>
       <c r="J94" s="9"/>
@@ -27570,7 +27573,7 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="9" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>842</v>
@@ -27588,17 +27591,17 @@
         <v>1971</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>2397</v>
+        <v>2463</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="I95" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L95" s="9" t="s">
         <v>1963</v>
@@ -27609,7 +27612,7 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="9" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>842</v>
@@ -27626,18 +27629,18 @@
       <c r="F96" s="9" t="s">
         <v>1971</v>
       </c>
-      <c r="G96" s="9" t="s">
-        <v>2182</v>
+      <c r="G96" s="13" t="s">
+        <v>2464</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="I96" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J96" s="9"/>
       <c r="K96" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L96" s="9" t="s">
         <v>1963</v>
@@ -27648,7 +27651,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="9" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>842</v>
@@ -27666,18 +27669,18 @@
         <v>1960</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>2398</v>
+        <v>2384</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="9"/>
       <c r="K97" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L97" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M97" s="9">
         <v>122</v>
@@ -27685,7 +27688,7 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="9" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>842</v>
@@ -27703,15 +27706,15 @@
         <v>1965</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>2463</v>
+        <v>2455</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="9"/>
       <c r="K98" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L98" s="9" t="s">
         <v>1963</v>
@@ -27722,7 +27725,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="9" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>842</v>
@@ -27740,20 +27743,20 @@
         <v>1960</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>2345</v>
+        <v>2337</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="I99" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="9" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="L99" s="9" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="M99" s="9">
         <v>125</v>
@@ -27761,7 +27764,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="9" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>842</v>
@@ -27779,10 +27782,10 @@
         <v>1960</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="I100" s="9" t="s">
         <v>957</v>
@@ -27792,7 +27795,7 @@
         <v>1975</v>
       </c>
       <c r="L100" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M100" s="9">
         <v>127</v>
@@ -27800,7 +27803,7 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="9" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>842</v>
@@ -27818,10 +27821,10 @@
         <v>1971</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>957</v>
@@ -27839,7 +27842,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="9" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>842</v>
@@ -27857,10 +27860,10 @@
         <v>1965</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>2346</v>
+        <v>2338</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="I102" s="9"/>
       <c r="J102" s="9"/>
@@ -27876,7 +27879,7 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="9" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>842</v>
@@ -27894,10 +27897,10 @@
         <v>1965</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>2399</v>
+        <v>2385</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="I103" s="9" t="s">
         <v>956</v>
@@ -27915,7 +27918,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="9" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>842</v>
@@ -27924,15 +27927,15 @@
         <v>1958</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
       <c r="G104" s="13" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>957</v>
@@ -27942,7 +27945,7 @@
         <v>1962</v>
       </c>
       <c r="L104" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M104" s="9">
         <v>137</v>
@@ -27950,7 +27953,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="9" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>842</v>
@@ -27959,15 +27962,15 @@
         <v>1958</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
       <c r="G105" s="13" t="s">
-        <v>2451</v>
+        <v>2433</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="I105" s="9" t="s">
         <v>957</v>
@@ -27977,7 +27980,7 @@
         <v>1962</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M105" s="9">
         <v>138</v>
@@ -27985,7 +27988,7 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="9" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>842</v>
@@ -27994,15 +27997,15 @@
         <v>1958</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="13" t="s">
-        <v>2348</v>
+        <v>2340</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>957</v>
@@ -28012,7 +28015,7 @@
         <v>1975</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M106" s="9">
         <v>139</v>
@@ -28020,7 +28023,7 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="9" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>842</v>
@@ -28029,22 +28032,22 @@
         <v>1958</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="13" t="s">
-        <v>2452</v>
+        <v>2434</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J107" s="9"/>
       <c r="K107" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L107" s="9" t="s">
         <v>1963</v>
@@ -28055,7 +28058,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="9" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>842</v>
@@ -28073,20 +28076,20 @@
         <v>1971</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>2400</v>
+        <v>2386</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J108" s="9"/>
       <c r="K108" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L108" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M108" s="9">
         <v>141</v>
@@ -28094,7 +28097,7 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="9" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>842</v>
@@ -28112,18 +28115,18 @@
         <v>1971</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>2464</v>
+        <v>2456</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L109" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M109" s="9">
         <v>142</v>
@@ -28131,7 +28134,7 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="9" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>842</v>
@@ -28149,10 +28152,10 @@
         <v>1971</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>957</v>
@@ -28170,7 +28173,7 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="9" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>842</v>
@@ -28188,10 +28191,10 @@
         <v>1971</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>955</v>
@@ -28209,7 +28212,7 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="9" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>842</v>
@@ -28227,10 +28230,10 @@
         <v>1971</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>2401</v>
+        <v>2387</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>959</v>
@@ -28240,7 +28243,7 @@
         <v>1962</v>
       </c>
       <c r="L112" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M112" s="9">
         <v>145</v>
@@ -28248,7 +28251,7 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="9" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>842</v>
@@ -28266,15 +28269,15 @@
         <v>1960</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>2349</v>
+        <v>2341</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="9"/>
       <c r="K113" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L113" s="9" t="s">
         <v>1963</v>
@@ -28285,7 +28288,7 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="9" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>842</v>
@@ -28303,20 +28306,20 @@
         <v>1960</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>2453</v>
+        <v>2435</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="I114" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J114" s="9"/>
       <c r="K114" s="9" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="L114" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M114" s="9">
         <v>147</v>
@@ -28324,7 +28327,7 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="9" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>842</v>
@@ -28342,10 +28345,10 @@
         <v>1960</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="I115" s="9" t="s">
         <v>957</v>
@@ -28363,7 +28366,7 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="9" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>842</v>
@@ -28381,10 +28384,10 @@
         <v>1960</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>2402</v>
+        <v>2388</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="I116" s="9" t="s">
         <v>957</v>
@@ -28402,7 +28405,7 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="9" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>842</v>
@@ -28420,10 +28423,10 @@
         <v>1960</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="I117" s="9" t="s">
         <v>957</v>
@@ -28433,7 +28436,7 @@
         <v>1975</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M117" s="9">
         <v>150</v>
@@ -28441,7 +28444,7 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="9" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>842</v>
@@ -28459,10 +28462,10 @@
         <v>1960</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="I118" s="9" t="s">
         <v>957</v>
@@ -28472,7 +28475,7 @@
         <v>1975</v>
       </c>
       <c r="L118" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M118" s="9">
         <v>151</v>
@@ -28480,7 +28483,7 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="9" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>842</v>
@@ -28498,17 +28501,17 @@
         <v>1965</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="I119" s="9" t="s">
         <v>955</v>
       </c>
       <c r="J119" s="9"/>
       <c r="K119" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L119" s="9" t="s">
         <v>1963</v>
@@ -28519,7 +28522,7 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="9" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>842</v>
@@ -28537,10 +28540,10 @@
         <v>1965</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="I120" s="9" t="s">
         <v>959</v>
@@ -28558,7 +28561,7 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="9" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>842</v>
@@ -28576,10 +28579,10 @@
         <v>1965</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>2350</v>
+        <v>2342</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="I121" s="9" t="s">
         <v>957</v>
@@ -28589,7 +28592,7 @@
         <v>1975</v>
       </c>
       <c r="L121" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M121" s="9">
         <v>154</v>
@@ -28597,7 +28600,7 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="9" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>842</v>
@@ -28615,17 +28618,17 @@
         <v>1965</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="I122" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J122" s="9"/>
       <c r="K122" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L122" s="9" t="s">
         <v>1963</v>
@@ -28636,7 +28639,7 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="9" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>842</v>
@@ -28654,18 +28657,18 @@
         <v>1965</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>2403</v>
+        <v>2467</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="9"/>
       <c r="K123" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="L123" s="9" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M123" s="9">
         <v>156</v>
@@ -28673,7 +28676,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="9" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>842</v>
@@ -28691,17 +28694,17 @@
         <v>1960</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="I124" s="9" t="s">
         <v>956</v>
       </c>
       <c r="J124" s="9"/>
       <c r="K124" s="9" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="L124" s="9" t="s">
         <v>1963</v>
@@ -28712,7 +28715,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="9" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>842</v>
@@ -28730,18 +28733,18 @@
         <v>1960</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>2404</v>
+        <v>2389</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="9"/>
       <c r="K125" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L125" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M125" s="9">
         <v>158</v>
@@ -28749,7 +28752,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="9" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>842</v>
@@ -28767,17 +28770,17 @@
         <v>1960</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>2454</v>
+        <v>2436</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="I126" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J126" s="9"/>
       <c r="K126" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L126" s="9" t="s">
         <v>1963</v>
@@ -28788,7 +28791,7 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="9" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>842</v>
@@ -28806,15 +28809,15 @@
         <v>1960</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="9"/>
       <c r="K127" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L127" s="9" t="s">
         <v>1963</v>
@@ -28825,7 +28828,7 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="9" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>842</v>
@@ -28843,17 +28846,17 @@
         <v>1960</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>2351</v>
+        <v>2473</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="I128" s="9" t="s">
         <v>958</v>
       </c>
       <c r="J128" s="9"/>
       <c r="K128" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L128" s="9" t="s">
         <v>1963</v>
@@ -28864,7 +28867,7 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="9" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>842</v>
@@ -28873,22 +28876,22 @@
         <v>1958</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
       <c r="G129" s="9" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="I129" s="9" t="s">
         <v>957</v>
       </c>
       <c r="J129" s="9"/>
       <c r="K129" s="9" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="L129" s="9" t="s">
         <v>1963</v>
@@ -28899,7 +28902,7 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="9" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>842</v>
@@ -28908,15 +28911,15 @@
         <v>1958</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
       <c r="G130" s="9" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="I130" s="9"/>
       <c r="J130" s="9"/>
@@ -28932,7 +28935,7 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="9" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>842</v>
@@ -28941,23 +28944,23 @@
         <v>1958</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="13" t="s">
-        <v>2405</v>
+        <v>2465</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="9"/>
       <c r="K131" s="9" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="L131" s="9" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="M131" s="9">
         <v>164</v>
@@ -28965,7 +28968,7 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="9" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>842</v>
@@ -28983,18 +28986,18 @@
         <v>1971</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>2352</v>
+        <v>2343</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="9"/>
       <c r="K132" s="9" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="L132" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="M132" s="9">
         <v>173</v>
@@ -29002,7 +29005,7 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="9" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>842</v>
@@ -29020,18 +29023,18 @@
         <v>1971</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>2353</v>
+        <v>2344</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="9"/>
       <c r="K133" s="9" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="M133" s="9">
         <v>174</v>
@@ -29039,7 +29042,7 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>842</v>
@@ -29057,18 +29060,18 @@
         <v>1971</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>2354</v>
+        <v>2345</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="I134" s="9"/>
       <c r="J134" s="9"/>
       <c r="K134" s="9" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="M134" s="9">
         <v>175</v>
@@ -29076,7 +29079,7 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="9" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>842</v>
@@ -29094,18 +29097,18 @@
         <v>1971</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>2406</v>
+        <v>2390</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="M135" s="9">
         <v>176</v>
@@ -29113,7 +29116,7 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="9" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>842</v>
@@ -29131,18 +29134,18 @@
         <v>1971</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>2455</v>
+        <v>2437</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="I136" s="9"/>
       <c r="J136" s="9"/>
       <c r="K136" s="9" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="L136" s="9" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="M136" s="9">
         <v>177</v>
@@ -29150,7 +29153,7 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="9" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>842</v>
@@ -29168,10 +29171,10 @@
         <v>1960</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>2355</v>
+        <v>2346</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="9"/>
@@ -29179,7 +29182,7 @@
         <v>1962</v>
       </c>
       <c r="L137" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M137" s="9">
         <v>165</v>
@@ -29187,7 +29190,7 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="9" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>842</v>
@@ -29205,10 +29208,10 @@
         <v>1965</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>2356</v>
+        <v>2347</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="I138" s="9"/>
       <c r="J138" s="9"/>
@@ -29216,7 +29219,7 @@
         <v>1962</v>
       </c>
       <c r="L138" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M138" s="9">
         <v>166</v>
@@ -29224,7 +29227,7 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="B139" s="9" t="s">
         <v>842</v>
@@ -29242,18 +29245,18 @@
         <v>1960</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>2357</v>
+        <v>2348</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="9"/>
       <c r="K139" s="9" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="L139" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M139" s="9">
         <v>167</v>
@@ -29261,7 +29264,7 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="9" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>842</v>
@@ -29279,18 +29282,18 @@
         <v>1965</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>2407</v>
+        <v>2391</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="I140" s="9"/>
       <c r="J140" s="9"/>
       <c r="K140" s="9" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="L140" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M140" s="9">
         <v>168</v>
@@ -29298,7 +29301,7 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>842</v>
@@ -29316,18 +29319,18 @@
         <v>1960</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>2358</v>
+        <v>2349</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="9"/>
       <c r="K141" s="9" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="L141" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M141" s="9">
         <v>169</v>
@@ -29335,7 +29338,7 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="9" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>842</v>
@@ -29353,18 +29356,18 @@
         <v>1965</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>2359</v>
+        <v>2350</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="I142" s="9"/>
       <c r="J142" s="9"/>
       <c r="K142" s="9" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="L142" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M142" s="9">
         <v>170</v>
@@ -29372,7 +29375,7 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="9" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>842</v>
@@ -29390,18 +29393,18 @@
         <v>1960</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>2360</v>
+        <v>2351</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="9"/>
       <c r="K143" s="9" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="L143" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M143" s="9">
         <v>171</v>
@@ -29409,7 +29412,7 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="9" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>842</v>
@@ -29418,15 +29421,15 @@
         <v>1958</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
       <c r="G144" s="13" t="s">
-        <v>2456</v>
+        <v>2438</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="I144" s="9"/>
       <c r="J144" s="9"/>
@@ -29434,7 +29437,7 @@
         <v>1962</v>
       </c>
       <c r="L144" s="9" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="M144" s="9">
         <v>172</v>
@@ -29509,10 +29512,10 @@
         <v>842</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>326</v>
@@ -29540,10 +29543,10 @@
         <v>842</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>326</v>
@@ -29687,10 +29690,10 @@
         <v>842</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>326</v>
@@ -29712,7 +29715,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="9" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>842</v>
@@ -29741,7 +29744,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="9" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>842</v>
@@ -29770,7 +29773,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="9" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>842</v>
@@ -29799,16 +29802,16 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="9" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>326</v>
@@ -29830,7 +29833,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>842</v>
@@ -29859,7 +29862,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="9" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>842</v>
@@ -29888,7 +29891,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="9" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>842</v>
@@ -29917,7 +29920,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="9" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>842</v>
@@ -29946,7 +29949,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="9" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>842</v>
@@ -29975,7 +29978,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>842</v>
@@ -30004,7 +30007,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>842</v>
@@ -30033,7 +30036,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="9" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>842</v>
@@ -30062,7 +30065,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="9" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>842</v>
@@ -30091,7 +30094,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="9" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>842</v>
@@ -30120,7 +30123,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="9" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>842</v>
@@ -30149,7 +30152,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>842</v>
@@ -30178,7 +30181,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="9" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>842</v>
@@ -30207,7 +30210,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="9" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>842</v>
@@ -30236,16 +30239,16 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="9" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>326</v>
@@ -30267,7 +30270,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="9" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>842</v>
@@ -30296,16 +30299,16 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="9" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>326</v>
@@ -30327,7 +30330,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="9" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>842</v>
@@ -30356,16 +30359,16 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="9" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>326</v>
@@ -30387,16 +30390,16 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="9" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>326</v>
@@ -30418,16 +30421,16 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="9" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>326</v>
@@ -30449,13 +30452,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="9" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>326</v>
@@ -30480,13 +30483,13 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="9" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>326</v>
@@ -30511,19 +30514,19 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="9" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>326</v>
@@ -30542,13 +30545,13 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="9" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>326</v>
@@ -30573,13 +30576,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="9" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>326</v>
@@ -30604,13 +30607,13 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="9" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>326</v>
@@ -30635,13 +30638,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="9" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>326</v>
@@ -30666,13 +30669,13 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="9" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>326</v>
@@ -30697,13 +30700,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="9" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>326</v>
@@ -30728,13 +30731,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="9" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>326</v>
@@ -30759,13 +30762,13 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="9" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>326</v>
@@ -30790,13 +30793,13 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="9" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>326</v>
@@ -30821,13 +30824,13 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="9" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>326</v>
@@ -30852,13 +30855,13 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="9" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>326</v>
@@ -30883,13 +30886,13 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="9" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>326</v>
@@ -30914,13 +30917,13 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="9" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>326</v>
@@ -30945,13 +30948,13 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="9" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>326</v>
@@ -30976,13 +30979,13 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="9" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>326</v>
@@ -31007,13 +31010,13 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="9" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>326</v>
@@ -31038,16 +31041,16 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="9" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>326</v>
@@ -31069,13 +31072,13 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="9" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>326</v>
@@ -31100,13 +31103,13 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="9" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>326</v>
@@ -31131,13 +31134,13 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="9" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>326</v>
@@ -31162,13 +31165,13 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="9" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>326</v>
@@ -31193,13 +31196,13 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="9" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>326</v>
@@ -31224,13 +31227,13 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="9" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>326</v>
@@ -31255,13 +31258,13 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="9" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>326</v>
@@ -31286,13 +31289,13 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="9" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>326</v>
@@ -31317,13 +31320,13 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="9" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>326</v>
@@ -31348,16 +31351,16 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="9" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>326</v>
@@ -31379,13 +31382,13 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="9" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>326</v>
@@ -31410,16 +31413,16 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="9" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>326</v>
@@ -31441,19 +31444,19 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="9" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>326</v>
@@ -31472,13 +31475,13 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="9" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>326</v>
@@ -31503,13 +31506,13 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="9" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>326</v>
@@ -31534,13 +31537,13 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="9" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>326</v>
@@ -31565,16 +31568,16 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="9" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>326</v>
@@ -31596,13 +31599,13 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="9" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>326</v>
@@ -31627,13 +31630,13 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="9" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>326</v>
@@ -31658,13 +31661,13 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="9" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>326</v>
@@ -31689,13 +31692,13 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="9" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>326</v>
@@ -31720,13 +31723,13 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="9" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>326</v>
@@ -31751,13 +31754,13 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="9" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>326</v>
@@ -31782,16 +31785,16 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="9" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>326</v>
@@ -31813,13 +31816,13 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="9" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>326</v>
@@ -31844,13 +31847,13 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="9" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D79" s="9" t="s">
         <v>326</v>
@@ -31875,13 +31878,13 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="9" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D80" s="9" t="s">
         <v>326</v>
@@ -31906,13 +31909,13 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="9" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>326</v>
@@ -31937,13 +31940,13 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="9" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>326</v>
@@ -31968,13 +31971,13 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="9" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>326</v>
@@ -31999,16 +32002,16 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="9" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>326</v>
@@ -32030,13 +32033,13 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="9" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>326</v>
@@ -32061,16 +32064,16 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="9" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>326</v>
@@ -32092,19 +32095,19 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="9" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>326</v>
@@ -32123,16 +32126,16 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="9" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B88" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>326</v>
@@ -32154,19 +32157,19 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="9" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="B89" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>326</v>
@@ -32185,19 +32188,19 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="9" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="B90" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>326</v>
@@ -32216,16 +32219,16 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="9" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="B91" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>326</v>
@@ -32247,13 +32250,13 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="9" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="B92" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>326</v>
@@ -32278,13 +32281,13 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="9" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="B93" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>326</v>
@@ -32309,13 +32312,13 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="9" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>326</v>
@@ -32340,13 +32343,13 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="9" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="B95" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>326</v>
@@ -32371,19 +32374,19 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="9" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>326</v>
@@ -32402,16 +32405,16 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="9" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>326</v>
@@ -32433,19 +32436,19 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="9" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>326</v>
@@ -32464,19 +32467,19 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="9" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>326</v>
@@ -32495,16 +32498,16 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="9" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>326</v>
@@ -32526,16 +32529,16 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="9" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>326</v>
@@ -32557,13 +32560,13 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="9" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>326</v>
@@ -32588,19 +32591,19 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="9" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>326</v>
@@ -32619,13 +32622,13 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="9" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>326</v>
@@ -32650,13 +32653,13 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="9" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="B105" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>326</v>
@@ -32681,16 +32684,16 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="9" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="B106" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>326</v>
@@ -32712,16 +32715,16 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="9" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B107" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>326</v>
@@ -32743,16 +32746,16 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="9" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="B108" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>326</v>
@@ -32774,16 +32777,16 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="9" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="B109" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>326</v>
@@ -32805,13 +32808,13 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="9" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>326</v>
@@ -32836,13 +32839,13 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="9" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="B111" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>326</v>
@@ -32867,13 +32870,13 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="9" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>326</v>
@@ -32898,13 +32901,13 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="9" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>326</v>
@@ -32929,13 +32932,13 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="9" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>326</v>
@@ -32960,13 +32963,13 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="9" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="B115" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>326</v>
@@ -32991,13 +32994,13 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="9" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="B116" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>326</v>
@@ -33022,13 +33025,13 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="9" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="B117" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>326</v>
@@ -33053,13 +33056,13 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="9" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>326</v>
@@ -33084,13 +33087,13 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="9" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>326</v>
@@ -33115,13 +33118,13 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="9" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B120" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D120" s="9" t="s">
         <v>326</v>
@@ -33146,13 +33149,13 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="9" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B121" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>326</v>
@@ -33177,13 +33180,13 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="9" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="B122" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>326</v>
@@ -33208,13 +33211,13 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="9" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="B123" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>326</v>
@@ -33239,13 +33242,13 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="9" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="B124" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>326</v>
@@ -33270,13 +33273,13 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="9" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="B125" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>326</v>
@@ -33301,13 +33304,13 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="9" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B126" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>326</v>
@@ -33332,13 +33335,13 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="9" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>326</v>
@@ -33363,13 +33366,13 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="9" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>326</v>
@@ -33394,13 +33397,13 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="9" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>326</v>
@@ -33425,13 +33428,13 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="9" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>326</v>
@@ -33456,16 +33459,16 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="9" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>326</v>
@@ -33487,13 +33490,13 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="9" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>326</v>
@@ -33518,13 +33521,13 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="9" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>326</v>
@@ -33549,13 +33552,13 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="9" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="B134" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>326</v>
@@ -33580,13 +33583,13 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="9" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>326</v>
@@ -33611,13 +33614,13 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="9" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>326</v>
@@ -33642,16 +33645,16 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="9" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="B137" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>326</v>
@@ -33673,16 +33676,16 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="9" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="B138" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>326</v>
@@ -33704,16 +33707,16 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="9" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="B139" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>326</v>
@@ -33735,16 +33738,16 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="9" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>326</v>
@@ -33766,16 +33769,16 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="9" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>326</v>
@@ -33797,16 +33800,16 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="9" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>326</v>
@@ -33828,16 +33831,16 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="9" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>326</v>
@@ -33859,16 +33862,16 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="9" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>842</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>326</v>
@@ -34030,7 +34033,7 @@
         <v>238</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>2367</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
@@ -36050,7 +36053,7 @@
         <v>239</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>2367</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="24" customHeight="1">
@@ -41014,28 +41017,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="11" t="s">
-        <v>2361</v>
+        <v>2352</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>842</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>2465</v>
+        <v>2442</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>2362</v>
+        <v>2353</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>2466</v>
+        <v>2443</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>2467</v>
+        <v>2444</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>2468</v>
+        <v>2445</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>2469</v>
+        <v>2446</v>
       </c>
     </row>
   </sheetData>
@@ -41146,7 +41149,7 @@
         <v>891</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2435</v>
+        <v>2419</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -41330,7 +41333,7 @@
         <v>904</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2426</v>
+        <v>2410</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -41353,7 +41356,7 @@
         <v>905</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2427</v>
+        <v>2411</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -41397,7 +41400,7 @@
         <v>899</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2428</v>
+        <v>2412</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -41418,7 +41421,7 @@
         <v>901</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2429</v>
+        <v>2413</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -41462,7 +41465,7 @@
         <v>908</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>2430</v>
+        <v>2414</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -41485,7 +41488,7 @@
         <v>909</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2431</v>
+        <v>2415</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -41634,7 +41637,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="11" t="s">
-        <v>2361</v>
+        <v>2352</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>842</v>
@@ -41643,15 +41646,15 @@
         <v>1</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>2363</v>
+        <v>2354</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2432</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="11" t="s">
-        <v>2361</v>
+        <v>2352</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>842</v>
@@ -41660,15 +41663,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>2364</v>
+        <v>2355</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>2470</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="11" t="s">
-        <v>2361</v>
+        <v>2352</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>842</v>
@@ -41677,10 +41680,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>2365</v>
+        <v>2356</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>2471</v>
+        <v>2448</v>
       </c>
     </row>
   </sheetData>
@@ -41936,7 +41939,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>2366</v>
+        <v>2357</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>934</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6805286C-64E5-45C4-B85B-56B121437A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0896807A-37C1-4C6A-9B29-15DFF00FC1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3410" yWindow="1540" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -7014,10 +7014,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 단백질 하나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>튀긴 반찬은 하나만</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7180,10 +7176,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>단백질 반찬 하나</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>간식은 견과류로</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7277,10 +7269,6 @@
   </si>
   <si>
     <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>혼밥에도 단백질 하나</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -9357,10 +9345,6 @@
   </si>
   <si>
     <t>모든 끼니에 채소 넣기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>저녁 반찬 절반은 채소</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -10992,15 +10976,31 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>명절에도 나물부터 먹기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>목마르면 물부터 마시기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>오늘은 단 간식 없이</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>반찬 하나는 단백질로</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니마다 단백질 챙기기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼밥에도 단백질 챙기기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>명절상 나물부터 먹기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁엔 채소 반찬 많이</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -15904,16 +15904,16 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="11" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D65" s="11" t="s">
         <v>2402</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>2403</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>2404</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>2405</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>1413</v>
@@ -15922,7 +15922,7 @@
         <v>1197</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>2406</v>
+        <v>2403</v>
       </c>
     </row>
   </sheetData>
@@ -16473,22 +16473,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="11" t="s">
-        <v>2402</v>
+        <v>2399</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>2407</v>
+        <v>2404</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>1433</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>1471</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
     </row>
   </sheetData>
@@ -23751,58 +23751,58 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="11" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>2449</v>
+        <v>2445</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>2450</v>
+        <v>2446</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="11" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>2394</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>2395</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>2396</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>2397</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="11" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>2398</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>2399</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>2400</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>2401</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="11" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C49" s="11" t="s">
         <v>2417</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>2418</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>2420</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>2421</v>
       </c>
     </row>
   </sheetData>
@@ -24064,7 +24064,7 @@
         <v>1960</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1961</v>
@@ -24142,7 +24142,7 @@
         <v>1965</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>1969</v>
@@ -24181,7 +24181,7 @@
         <v>1971</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1972</v>
@@ -24296,7 +24296,7 @@
         <v>1965</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>2468</v>
+        <v>2464</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>1979</v>
@@ -24333,7 +24333,7 @@
         <v>1971</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>2469</v>
+        <v>2465</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>1981</v>
@@ -24409,7 +24409,7 @@
         <v>1965</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>2457</v>
+        <v>2453</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1986</v>
@@ -24448,7 +24448,7 @@
         <v>1965</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>1989</v>
@@ -24487,7 +24487,7 @@
         <v>1971</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>1992</v>
@@ -24602,7 +24602,7 @@
         <v>1965</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>2422</v>
+        <v>2419</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>2000</v>
@@ -24639,7 +24639,7 @@
         <v>1971</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>2002</v>
@@ -24789,7 +24789,7 @@
         <v>1960</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>2423</v>
+        <v>2420</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>2012</v>
@@ -24828,7 +24828,7 @@
         <v>1965</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>2363</v>
+        <v>2470</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>2014</v>
@@ -24867,7 +24867,7 @@
         <v>1971</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>2320</v>
+        <v>2471</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>2016</v>
@@ -24906,7 +24906,7 @@
         <v>1960</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>2018</v>
@@ -24945,7 +24945,7 @@
         <v>1965</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>2020</v>
@@ -24984,7 +24984,7 @@
         <v>1971</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>2022</v>
@@ -25017,7 +25017,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="13" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>2026</v>
@@ -25052,7 +25052,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="13" t="s">
-        <v>2424</v>
+        <v>2421</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>2028</v>
@@ -25087,7 +25087,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="13" t="s">
-        <v>2458</v>
+        <v>2454</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>2030</v>
@@ -25122,7 +25122,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="13" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>2033</v>
@@ -25155,7 +25155,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="13" t="s">
-        <v>2459</v>
+        <v>2455</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>2035</v>
@@ -25188,7 +25188,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="13" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>2037</v>
@@ -25225,7 +25225,7 @@
         <v>1960</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2453</v>
+        <v>2449</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>2039</v>
@@ -25264,7 +25264,7 @@
         <v>1965</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>2042</v>
@@ -25301,7 +25301,7 @@
         <v>1971</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>2044</v>
@@ -25340,7 +25340,7 @@
         <v>1971</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>2046</v>
@@ -25379,7 +25379,7 @@
         <v>1960</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>2048</v>
@@ -25416,7 +25416,7 @@
         <v>1960</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>2050</v>
@@ -25455,7 +25455,7 @@
         <v>1965</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>2053</v>
@@ -25494,7 +25494,7 @@
         <v>1971</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>2055</v>
@@ -25533,7 +25533,7 @@
         <v>1971</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>2470</v>
+        <v>2466</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>2057</v>
@@ -25570,7 +25570,7 @@
         <v>1960</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>2059</v>
@@ -25683,7 +25683,7 @@
         <v>1971</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>2474</v>
+        <v>2469</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>2067</v>
@@ -25761,7 +25761,7 @@
         <v>1960</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>2460</v>
+        <v>2456</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>2072</v>
@@ -25798,7 +25798,7 @@
         <v>1965</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>2074</v>
@@ -25837,7 +25837,7 @@
         <v>1965</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>2076</v>
@@ -25876,7 +25876,7 @@
         <v>1971</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>2427</v>
+        <v>2424</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>2078</v>
@@ -25913,7 +25913,7 @@
         <v>1971</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>2080</v>
@@ -25952,7 +25952,7 @@
         <v>1960</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>2082</v>
@@ -26028,7 +26028,7 @@
         <v>1960</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>2087</v>
@@ -26104,7 +26104,7 @@
         <v>1965</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>2092</v>
@@ -26143,7 +26143,7 @@
         <v>1971</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>2094</v>
@@ -26180,7 +26180,7 @@
         <v>1960</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>2096</v>
@@ -26219,7 +26219,7 @@
         <v>1960</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
       <c r="H59" s="9" t="s">
         <v>2098</v>
@@ -26258,7 +26258,7 @@
         <v>1965</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>2100</v>
@@ -26297,7 +26297,7 @@
         <v>1965</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>2102</v>
@@ -26369,7 +26369,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="13" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>2107</v>
@@ -26404,7 +26404,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="13" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>2109</v>
@@ -26443,7 +26443,7 @@
         <v>1965</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>2428</v>
+        <v>2425</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>2111</v>
@@ -26482,7 +26482,7 @@
         <v>1971</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>2113</v>
@@ -26521,7 +26521,7 @@
         <v>1971</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>2454</v>
+        <v>2450</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>2115</v>
@@ -26558,7 +26558,7 @@
         <v>1965</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>2117</v>
@@ -26597,7 +26597,7 @@
         <v>1971</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>2119</v>
@@ -26636,7 +26636,7 @@
         <v>1971</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>2430</v>
+        <v>2474</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>2121</v>
@@ -26712,7 +26712,7 @@
         <v>1960</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>2126</v>
@@ -26790,7 +26790,7 @@
         <v>1965</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>2131</v>
@@ -26829,7 +26829,7 @@
         <v>1965</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>2133</v>
@@ -26866,7 +26866,7 @@
         <v>1971</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>2135</v>
@@ -26905,7 +26905,7 @@
         <v>1965</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>2440</v>
+        <v>2436</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>2137</v>
@@ -26981,7 +26981,7 @@
         <v>1965</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="H79" s="9" t="s">
         <v>2143</v>
@@ -27020,7 +27020,7 @@
         <v>1971</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>2145</v>
@@ -27059,7 +27059,7 @@
         <v>1960</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>2147</v>
@@ -27098,7 +27098,7 @@
         <v>1965</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>2149</v>
@@ -27137,7 +27137,7 @@
         <v>1965</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="H83" s="9" t="s">
         <v>2151</v>
@@ -27176,7 +27176,7 @@
         <v>1971</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>2432</v>
+        <v>2428</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>2153</v>
@@ -27213,7 +27213,7 @@
         <v>1960</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="H85" s="9" t="s">
         <v>2155</v>
@@ -27250,7 +27250,7 @@
         <v>1960</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>2157</v>
@@ -27287,7 +27287,7 @@
         <v>1971</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>2159</v>
@@ -27363,7 +27363,7 @@
         <v>1971</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>2164</v>
@@ -27400,7 +27400,7 @@
         <v>1965</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>2166</v>
@@ -27439,7 +27439,7 @@
         <v>1971</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>2169</v>
@@ -27478,7 +27478,7 @@
         <v>1971</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>2462</v>
+        <v>2458</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>2171</v>
@@ -27517,7 +27517,7 @@
         <v>1960</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>2173</v>
@@ -27591,7 +27591,7 @@
         <v>1971</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>2463</v>
+        <v>2459</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>2178</v>
@@ -27630,7 +27630,7 @@
         <v>1971</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>2464</v>
+        <v>2460</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>2180</v>
@@ -27669,7 +27669,7 @@
         <v>1960</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>2182</v>
@@ -27706,7 +27706,7 @@
         <v>1965</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>2455</v>
+        <v>2451</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>2184</v>
@@ -27743,7 +27743,7 @@
         <v>1960</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="H99" s="9" t="s">
         <v>2186</v>
@@ -27860,7 +27860,7 @@
         <v>1965</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>2194</v>
@@ -27897,7 +27897,7 @@
         <v>1965</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="H103" s="9" t="s">
         <v>2196</v>
@@ -27932,7 +27932,7 @@
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
       <c r="G104" s="13" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>2198</v>
@@ -27967,7 +27967,7 @@
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
       <c r="G105" s="13" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>2200</v>
@@ -28002,7 +28002,7 @@
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="13" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>2202</v>
@@ -28037,7 +28037,7 @@
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="13" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>2204</v>
@@ -28076,7 +28076,7 @@
         <v>1971</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>2206</v>
@@ -28115,7 +28115,7 @@
         <v>1971</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>2208</v>
@@ -28230,7 +28230,7 @@
         <v>1971</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>2216</v>
@@ -28269,7 +28269,7 @@
         <v>1960</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="H113" s="9" t="s">
         <v>2218</v>
@@ -28306,7 +28306,7 @@
         <v>1960</v>
       </c>
       <c r="G114" s="13" t="s">
-        <v>2435</v>
+        <v>2431</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>2220</v>
@@ -28384,7 +28384,7 @@
         <v>1960</v>
       </c>
       <c r="G116" s="13" t="s">
-        <v>2388</v>
+        <v>2472</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>2225</v>
@@ -28579,7 +28579,7 @@
         <v>1965</v>
       </c>
       <c r="G121" s="13" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="H121" s="9" t="s">
         <v>2239</v>
@@ -28657,7 +28657,7 @@
         <v>1965</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>2467</v>
+        <v>2463</v>
       </c>
       <c r="H123" s="9" t="s">
         <v>2244</v>
@@ -28733,7 +28733,7 @@
         <v>1960</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="H125" s="9" t="s">
         <v>2249</v>
@@ -28770,7 +28770,7 @@
         <v>1960</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="H126" s="9" t="s">
         <v>2251</v>
@@ -28846,7 +28846,7 @@
         <v>1960</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>2473</v>
+        <v>2468</v>
       </c>
       <c r="H128" s="9" t="s">
         <v>2256</v>
@@ -28949,7 +28949,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="13" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>2264</v>
@@ -28986,7 +28986,7 @@
         <v>1971</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="H132" s="9" t="s">
         <v>2266</v>
@@ -29023,7 +29023,7 @@
         <v>1971</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="H133" s="9" t="s">
         <v>2270</v>
@@ -29060,7 +29060,7 @@
         <v>1971</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="H134" s="9" t="s">
         <v>2272</v>
@@ -29097,7 +29097,7 @@
         <v>1971</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="H135" s="9" t="s">
         <v>2274</v>
@@ -29134,7 +29134,7 @@
         <v>1971</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>2437</v>
+        <v>2433</v>
       </c>
       <c r="H136" s="9" t="s">
         <v>2277</v>
@@ -29171,7 +29171,7 @@
         <v>1960</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="H137" s="9" t="s">
         <v>2279</v>
@@ -29208,7 +29208,7 @@
         <v>1965</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="H138" s="9" t="s">
         <v>2282</v>
@@ -29245,7 +29245,7 @@
         <v>1960</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="H139" s="9" t="s">
         <v>2284</v>
@@ -29282,7 +29282,7 @@
         <v>1965</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="H140" s="9" t="s">
         <v>2287</v>
@@ -29319,7 +29319,7 @@
         <v>1960</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H141" s="9" t="s">
         <v>2289</v>
@@ -29356,7 +29356,7 @@
         <v>1965</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="H142" s="9" t="s">
         <v>2291</v>
@@ -29393,7 +29393,7 @@
         <v>1960</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="H143" s="9" t="s">
         <v>2293</v>
@@ -29426,7 +29426,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
       <c r="G144" s="13" t="s">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="H144" s="9" t="s">
         <v>2296</v>
@@ -34033,7 +34033,7 @@
         <v>238</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
@@ -36053,7 +36053,7 @@
         <v>239</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="24" customHeight="1">
@@ -41017,28 +41017,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="11" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>842</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>2441</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>2442</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>2353</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>2444</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>2445</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>2446</v>
       </c>
     </row>
   </sheetData>
@@ -41149,7 +41149,7 @@
         <v>891</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2419</v>
+        <v>2416</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -41333,7 +41333,7 @@
         <v>904</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2410</v>
+        <v>2407</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -41356,7 +41356,7 @@
         <v>905</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -41400,7 +41400,7 @@
         <v>899</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -41421,7 +41421,7 @@
         <v>901</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -41465,7 +41465,7 @@
         <v>908</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -41488,7 +41488,7 @@
         <v>909</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -41637,7 +41637,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="11" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>842</v>
@@ -41646,15 +41646,15 @@
         <v>1</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="11" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>842</v>
@@ -41663,15 +41663,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>2447</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="11" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>842</v>
@@ -41680,10 +41680,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>2448</v>
+        <v>2444</v>
       </c>
     </row>
   </sheetData>
@@ -41939,7 +41939,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>934</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C841F91D-2A0A-48AA-BFE5-4837F0F5CDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A81B8-7665-4F33-84C5-965144D48750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7462" uniqueCount="2491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="2520">
   <si>
     <t>항목</t>
   </si>
@@ -11941,6 +11941,2258 @@
   <si>
     <t>목표 축 선정</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내용</t>
+    </r>
+  </si>
+  <si>
+    <t>최초 발행 2026-09-23 이후 바뀐 것을 최신순으로 적는다. 파일 이름의 v1.0.0은 바꾸지 않는다.</t>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+  </si>
+  <si>
+    <t>어디</t>
+  </si>
+  <si>
+    <r>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상승에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본까지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올린다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-42 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-068 · CFG-069</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사람의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번씩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-041 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상세기획</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환연결축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-39 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-03</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고치고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넷을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄임</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8개를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>길던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자였다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-49</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료일이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음부터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-47 · V-48 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신설</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{질환명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이신가요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>매기지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-90 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-46</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>타일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>109개를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>띄어쓰기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>말끝이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끊긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>심혈관질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞추려고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>괄호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>예시를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뺌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DX-06</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -11950,7 +14202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -12014,6 +14266,28 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -12056,7 +14330,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -12094,6 +14368,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -12728,11 +15005,13 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="1" max="1" width="82.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="146.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31" customHeight="1">
@@ -12845,6 +15124,156 @@
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="14" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="14" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="15">
+        <v>46297</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>2495</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="15">
+        <v>46297</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="15">
+        <v>46297</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="15">
+        <v>46296</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="15">
+        <v>46295</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="15">
+        <v>46295</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="15">
+        <v>46294</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="15">
+        <v>46294</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="15">
+        <v>46294</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>2517</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>2519</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A81B8-7665-4F33-84C5-965144D48750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43270FD8-546A-412D-BA0D-003C647185B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="2520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7504" uniqueCount="2524">
   <si>
     <t>항목</t>
   </si>
@@ -14193,6 +14193,18 @@
       </rPr>
       <t xml:space="preserve"> DX-06</t>
     </r>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
   </si>
 </sst>
 </file>
@@ -14369,8 +14381,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -15151,128 +15163,128 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="15">
-        <v>46297</v>
-      </c>
-      <c r="B20" s="16" t="s">
+      <c r="A20" s="16" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>2495</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>2496</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>2497</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="15">
-        <v>46297</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="A21" s="16" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>2498</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>2499</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>2500</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="15">
-        <v>46297</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="16" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>2501</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>2502</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>2503</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="15">
-        <v>46296</v>
-      </c>
-      <c r="B23" s="16" t="s">
+      <c r="A23" s="16" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>2504</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>2505</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="15">
-        <v>46295</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="16" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>2506</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>2507</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>2508</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="15">
-        <v>46295</v>
-      </c>
-      <c r="B25" s="16" t="s">
+      <c r="A25" s="16" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>2509</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>2510</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="15" t="s">
         <v>2511</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="15">
-        <v>46294</v>
-      </c>
-      <c r="B26" s="16" t="s">
+      <c r="A26" s="16" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>2512</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="15" t="s">
         <v>2513</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>2514</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="15">
-        <v>46294</v>
-      </c>
-      <c r="B27" s="16" t="s">
+      <c r="A27" s="16" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>2515</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>2516</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="15">
-        <v>46294</v>
-      </c>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="16" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>2517</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>2518</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="15" t="s">
         <v>2519</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9789AE9B-2047-4153-80CE-DF8D688C0C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F8C582-50B8-469B-AEC2-93294DA1F6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7501" uniqueCount="2526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7503" uniqueCount="2531">
   <si>
     <t>항목</t>
   </si>
@@ -17785,6 +17785,828 @@
         <family val="2"/>
       </rPr>
       <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>연결 축 없음. 금지만 적용한다(내정보질환매핑 SAFETY_ONLY와 맞춤)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>만성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환연결축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DX-05 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>짠맛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰였다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내정보질환매핑에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「새</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용」이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적혀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>곳이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어긋났다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없앴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. link_enabled</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> False</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환연결축에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지웠다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(INCREASE·REDUCE·FLUID)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둔다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DX-05 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환연결축</t>
     </r>
   </si>
 </sst>
@@ -18370,7 +19192,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="DietDiseaseAxes" displayName="DietDiseaseAxes" ref="A1:C17" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="DietDiseaseAxes" displayName="DietDiseaseAxes" ref="A1:C16" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="rule_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="question_id"/>
@@ -18589,7 +19411,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -18734,59 +19556,73 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="56">
+    <row r="20" spans="1:4" ht="42">
       <c r="A20" s="16" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="56">
+      <c r="A21" s="16" t="s">
         <v>2511</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B21" s="16" t="s">
         <v>2512</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C21" s="16" t="s">
         <v>2513</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D21" s="16" t="s">
         <v>2514</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="28">
-      <c r="A21" s="16" t="s">
-        <v>2515</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>2516</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>2517</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>2518</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28">
       <c r="A22" s="16" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>2521</v>
+        <v>2517</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28">
       <c r="A23" s="16" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="28">
+      <c r="A24" s="16" t="s">
         <v>2475</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B24" s="16" t="s">
         <v>2523</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>2524</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D24" s="16" t="s">
         <v>2525</v>
       </c>
     </row>
@@ -48922,8 +49758,8 @@
       <c r="C6" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="D6" s="1" t="b">
-        <v>1</v>
+      <c r="D6" s="14" t="b">
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
@@ -48940,8 +49776,8 @@
       <c r="I6" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>910</v>
+      <c r="J6" s="14" t="s">
+        <v>2526</v>
       </c>
       <c r="K6" s="1">
         <v>6</v>
@@ -49260,7 +50096,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -49390,44 +50226,44 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>919</v>
+      <c r="A12" s="14" t="s">
+        <v>922</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="C12" s="1">
-        <v>6</v>
+      <c r="C12" s="14">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="24" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>853</v>
+      <c r="B13" s="14" t="s">
+        <v>872</v>
       </c>
       <c r="C13" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="C14" s="1">
-        <v>7</v>
+      <c r="A14" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>849</v>
+      </c>
+      <c r="C14" s="14">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>849</v>
+      <c r="B15" s="14" t="s">
+        <v>872</v>
       </c>
       <c r="C15" s="1">
         <v>8</v>
@@ -49437,21 +50273,10 @@
       <c r="A16" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>872</v>
+      <c r="B16" s="14" t="s">
+        <v>864</v>
       </c>
       <c r="C16" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="24" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="C17" s="1">
         <v>8</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42546DCA-0079-44DD-AD1A-0909F522C51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5714B92B-58AD-42A8-B003-9E3EADD537BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -20647,12 +20647,6 @@
     <t>CFG-003,CFG-004</t>
   </si>
   <si>
-    <t>축 상태 경계값 구조화</t>
-  </si>
-  <si>
-    <t>CFG-002~005가 글로만 적혀 있어 개발이 바로 쓸 수 없었다</t>
-  </si>
-  <si>
     <r>
       <t>열</t>
     </r>
@@ -20684,7 +20678,207 @@
   </si>
   <si>
     <r>
-      <t>비율에</t>
+      <t>CFG-006과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-007. 이보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. 최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
     </r>
     <r>
       <rPr>
@@ -20705,15 +20899,673 @@
       </rPr>
       <t>분모</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. 7건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채우면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>결합</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경계값</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구조화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-002~005가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>글로만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적혀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>무엇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>비율인지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>알</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없었다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -20751,7 +21603,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>·28</t>
+      <t>·84</t>
     </r>
     <r>
       <rPr>
@@ -20779,102 +21631,64 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>창</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최소</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>붙여</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>숫자로</t>
+      <t>상한을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>붙였다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. CFG-005</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결합으로</t>
     </r>
     <r>
       <rPr>
@@ -20895,63 +21709,6 @@
       </rPr>
       <t>적었다</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. CFG-005</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AND </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>결합으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적었다</t>
-    </r>
   </si>
   <si>
     <r>
@@ -20975,531 +21732,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>설정파라미터</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-006과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>창에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-007. 이보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. 최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. 7건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채우면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. CFG-003과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. CFG-003과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>결합</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID</t>
     </r>
   </si>
 </sst>
@@ -21623,7 +21855,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -21673,9 +21905,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -21712,7 +21941,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DietGuide" displayName="DietGuide" ref="A1:D15" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DietGuide" displayName="DietGuide" ref="A1:D14" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="항목"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="내용"/>
@@ -22329,152 +22558,152 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2543</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="31" customHeight="1">
-      <c r="A2" s="18" t="s">
-        <v>2540</v>
-      </c>
-      <c r="B2" s="18" t="s">
         <v>2541</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>2544</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2545</v>
+    </row>
+    <row r="2" spans="1:4" ht="24" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>2482</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>2482</v>
+      <c r="A3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>4</v>
+      <c r="A4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>6</v>
+      <c r="A5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>8</v>
+      <c r="A6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>10</v>
+      <c r="A7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>12</v>
+      <c r="A8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>14</v>
+      <c r="A9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>16</v>
+      <c r="A10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>18</v>
+      <c r="A11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>20</v>
+      <c r="A12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>22</v>
+      <c r="A13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="24" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="13" t="s">
+        <v>2498</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="13" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="13" t="s">
         <v>2499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>2500</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>2496</v>
+        <v>2551</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>2497</v>
+        <v>2552</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2500</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28">
@@ -27259,7 +27488,7 @@
         <v>2529</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27282,7 +27511,7 @@
         <v>2529</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -27305,7 +27534,7 @@
         <v>2529</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -27328,7 +27557,7 @@
         <v>2529</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -27351,7 +27580,7 @@
         <v>2529</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -27374,7 +27603,7 @@
         <v>2529</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>2551</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27397,7 +27626,7 @@
         <v>2529</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>2552</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27420,7 +27649,7 @@
         <v>2529</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>2553</v>
+        <v>2549</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488916BF-D02A-4BC5-8A9A-E5144872371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57785249-EE9C-4A9F-9E7D-6B435A27A1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57785249-EE9C-4A9F-9E7D-6B435A27A1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F998C09D-9066-4232-99D9-F8371B4A3887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -7109,10 +7109,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>늦은 카페인 줄이기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>점심은 평소 양으로</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -7193,10 +7189,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>국물 기름 걷어내기</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -22449,6 +22441,14 @@
       </rPr>
       <t xml:space="preserve"> 66)</t>
     </r>
+  </si>
+  <si>
+    <t>튀김 대신 굽거나 찌기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 시간, 카페인 줄이기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -22571,7 +22571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -22620,6 +22620,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -23274,10 +23277,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
@@ -23285,7 +23288,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
@@ -23301,7 +23304,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
@@ -23309,7 +23312,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
@@ -23349,7 +23352,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -23381,17 +23384,17 @@
         <v>22</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="13" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="13" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -23399,111 +23402,111 @@
         <v>0</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>2555</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>2556</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>2557</v>
-      </c>
       <c r="D20" s="13" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="13" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>2546</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>2547</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>2548</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28">
       <c r="A22" s="16" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>2513</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="D22" s="16" t="s">
         <v>2514</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>2515</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>2516</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="42">
       <c r="A23" s="16" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>2509</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="D23" s="16" t="s">
         <v>2510</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>2511</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>2512</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="56">
       <c r="A24" s="16" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>2497</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="D24" s="16" t="s">
         <v>2498</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>2499</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>2500</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28">
       <c r="A25" s="16" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>2501</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>2502</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>2503</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>2504</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28">
       <c r="A26" s="16" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>2505</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>2506</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>2507</v>
       </c>
     </row>
   </sheetData>
@@ -25671,7 +25674,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="15" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>1169</v>
@@ -25700,7 +25703,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="15" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>1169</v>
@@ -25729,7 +25732,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="15" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>1169</v>
@@ -25758,7 +25761,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="15" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>1169</v>
@@ -26815,7 +26818,7 @@
         <v>1320</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>1167</v>
@@ -26824,7 +26827,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="15" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>1316</v>
@@ -27308,10 +27311,10 @@
         <v>1383</v>
       </c>
       <c r="B58" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C58" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="D58" t="s">
         <v>1385</v>
@@ -27326,7 +27329,7 @@
         <v>1183</v>
       </c>
       <c r="J58" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="K58">
         <v>58</v>
@@ -27337,10 +27340,10 @@
         <v>1387</v>
       </c>
       <c r="B59" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C59" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="D59" t="s">
         <v>1388</v>
@@ -27355,7 +27358,7 @@
         <v>1183</v>
       </c>
       <c r="J59" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="K59">
         <v>59</v>
@@ -27366,10 +27369,10 @@
         <v>1389</v>
       </c>
       <c r="B60" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C60" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="D60" t="s">
         <v>1187</v>
@@ -27384,7 +27387,7 @@
         <v>1183</v>
       </c>
       <c r="J60" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="K60">
         <v>60</v>
@@ -27395,10 +27398,10 @@
         <v>1390</v>
       </c>
       <c r="B61" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C61" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="D61" t="s">
         <v>770</v>
@@ -27413,7 +27416,7 @@
         <v>1183</v>
       </c>
       <c r="J61" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="K61">
         <v>61</v>
@@ -27505,16 +27508,16 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="B65" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D65" t="s">
         <v>2443</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2444</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2445</v>
       </c>
       <c r="E65" t="s">
         <v>1394</v>
@@ -27523,21 +27526,21 @@
         <v>1183</v>
       </c>
       <c r="J65" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="13" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>481</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>1394</v>
@@ -27546,21 +27549,21 @@
         <v>1183</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="13" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>481</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>1394</v>
@@ -27569,7 +27572,7 @@
         <v>1183</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
   </sheetData>
@@ -27641,10 +27644,10 @@
         <v>1408</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -27665,10 +27668,10 @@
         <v>1408</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -27689,10 +27692,10 @@
         <v>1408</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -28120,50 +28123,50 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="B23" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C23" t="s">
         <v>1413</v>
       </c>
       <c r="E23" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="G23" t="s">
         <v>1451</v>
       </c>
       <c r="H23" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="13" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>2463</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="G24" s="13" t="s">
         <v>2464</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>2465</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>2466</v>
-      </c>
       <c r="H24" s="13" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="13" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>1413</v>
@@ -28172,10 +28175,10 @@
         <v>1940</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -28183,19 +28186,19 @@
         <v>1319</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>1413</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -28203,7 +28206,7 @@
         <v>1163</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>1413</v>
@@ -28215,10 +28218,10 @@
         <v>1404</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -28226,7 +28229,7 @@
         <v>1163</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>1407</v>
@@ -28238,10 +28241,10 @@
         <v>1417</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -28249,7 +28252,7 @@
         <v>1170</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>1413</v>
@@ -28261,10 +28264,10 @@
         <v>1417</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -28272,7 +28275,7 @@
         <v>1170</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>1421</v>
@@ -28284,10 +28287,10 @@
         <v>1404</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -28295,7 +28298,7 @@
         <v>1173</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>1413</v>
@@ -28307,10 +28310,10 @@
         <v>1417</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -28318,7 +28321,7 @@
         <v>1173</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>1421</v>
@@ -28330,10 +28333,10 @@
         <v>1404</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -28341,7 +28344,7 @@
         <v>1176</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>1413</v>
@@ -28350,13 +28353,13 @@
         <v>705</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -28364,22 +28367,22 @@
         <v>1176</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>1413</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
     </row>
   </sheetData>
@@ -35547,13 +35550,13 @@
         <v>1899</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -35592,10 +35595,10 @@
         <v>1909</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -35645,69 +35648,69 @@
         <v>2333</v>
       </c>
       <c r="B46" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2447</v>
+      </c>
+      <c r="D46" t="s">
         <v>2448</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2449</v>
-      </c>
-      <c r="D46" t="s">
-        <v>2450</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="B47" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D47" t="s">
         <v>2451</v>
-      </c>
-      <c r="C47" t="s">
-        <v>2452</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2453</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="B48" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2453</v>
+      </c>
+      <c r="D48" t="s">
         <v>2454</v>
-      </c>
-      <c r="C48" t="s">
-        <v>2455</v>
-      </c>
-      <c r="D48" t="s">
-        <v>2456</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="B49" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D49" t="s">
         <v>2457</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2458</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2459</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="13" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>2522</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>2523</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>2524</v>
       </c>
     </row>
   </sheetData>
@@ -35969,7 +35972,7 @@
         <v>1935</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>1936</v>
@@ -36086,7 +36089,7 @@
         <v>1946</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>1947</v>
@@ -36201,7 +36204,7 @@
         <v>1940</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>1954</v>
@@ -36238,7 +36241,7 @@
         <v>1946</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>1956</v>
@@ -36314,7 +36317,7 @@
         <v>1940</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>1961</v>
@@ -36392,7 +36395,7 @@
         <v>1946</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>1967</v>
@@ -36507,7 +36510,7 @@
         <v>1940</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>1975</v>
@@ -36694,7 +36697,7 @@
         <v>1935</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>1987</v>
@@ -36733,7 +36736,7 @@
         <v>1940</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>1989</v>
@@ -36772,7 +36775,7 @@
         <v>1946</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>1991</v>
@@ -36889,7 +36892,7 @@
         <v>1946</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>1997</v>
@@ -36957,7 +36960,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="12" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>2003</v>
@@ -36992,7 +36995,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="12" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>2005</v>
@@ -37026,8 +37029,8 @@
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="12" t="s">
-        <v>2339</v>
+      <c r="G30" s="18" t="s">
+        <v>2557</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>2008</v>
@@ -37060,7 +37063,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="12" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>2010</v>
@@ -37093,7 +37096,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="12" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>2012</v>
@@ -37130,7 +37133,7 @@
         <v>1935</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>2014</v>
@@ -37169,7 +37172,7 @@
         <v>1940</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>2017</v>
@@ -37245,7 +37248,7 @@
         <v>1946</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>2021</v>
@@ -37321,7 +37324,7 @@
         <v>1935</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>2025</v>
@@ -37438,7 +37441,7 @@
         <v>1946</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>2032</v>
@@ -37475,7 +37478,7 @@
         <v>1935</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>2034</v>
@@ -37588,7 +37591,7 @@
         <v>1946</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>2042</v>
@@ -37666,7 +37669,7 @@
         <v>1935</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>2047</v>
@@ -37742,7 +37745,7 @@
         <v>1940</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>2051</v>
@@ -37781,7 +37784,7 @@
         <v>1946</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>2053</v>
@@ -37818,7 +37821,7 @@
         <v>1946</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>2055</v>
@@ -37857,7 +37860,7 @@
         <v>1935</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>2057</v>
@@ -38009,7 +38012,7 @@
         <v>1940</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>2067</v>
@@ -38048,7 +38051,7 @@
         <v>1946</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>2069</v>
@@ -38124,7 +38127,7 @@
         <v>1935</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="H59" s="9" t="s">
         <v>2073</v>
@@ -38163,7 +38166,7 @@
         <v>1940</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>2075</v>
@@ -38274,7 +38277,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="12" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>2082</v>
@@ -38348,7 +38351,7 @@
         <v>1940</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>2086</v>
@@ -38387,7 +38390,7 @@
         <v>1946</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>2088</v>
@@ -38426,7 +38429,7 @@
         <v>1946</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>2090</v>
@@ -38502,7 +38505,7 @@
         <v>1946</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>2094</v>
@@ -38541,7 +38544,7 @@
         <v>1946</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>2096</v>
@@ -38617,7 +38620,7 @@
         <v>1935</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>2101</v>
@@ -38734,7 +38737,7 @@
         <v>1940</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>2108</v>
@@ -38771,7 +38774,7 @@
         <v>1946</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>2110</v>
@@ -38810,7 +38813,7 @@
         <v>1940</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>2112</v>
@@ -38925,7 +38928,7 @@
         <v>1946</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>2120</v>
@@ -38964,7 +38967,7 @@
         <v>1935</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>2122</v>
@@ -39003,7 +39006,7 @@
         <v>1940</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>2124</v>
@@ -39081,7 +39084,7 @@
         <v>1946</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>2128</v>
@@ -39155,7 +39158,7 @@
         <v>1935</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>2132</v>
@@ -39192,7 +39195,7 @@
         <v>1946</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>2134</v>
@@ -39268,7 +39271,7 @@
         <v>1946</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>2139</v>
@@ -39344,7 +39347,7 @@
         <v>1946</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>2144</v>
@@ -39383,7 +39386,7 @@
         <v>1946</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>2146</v>
@@ -39422,7 +39425,7 @@
         <v>1935</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>2148</v>
@@ -39496,7 +39499,7 @@
         <v>1946</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>2153</v>
@@ -39535,7 +39538,7 @@
         <v>1946</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>2155</v>
@@ -39574,7 +39577,7 @@
         <v>1935</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>2157</v>
@@ -39611,7 +39614,7 @@
         <v>1940</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>2159</v>
@@ -39802,7 +39805,7 @@
         <v>1940</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="H103" s="9" t="s">
         <v>2171</v>
@@ -39872,7 +39875,7 @@
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
       <c r="G105" s="12" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>2175</v>
@@ -39942,7 +39945,7 @@
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="12" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>2179</v>
@@ -39981,7 +39984,7 @@
         <v>1946</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>2181</v>
@@ -40020,7 +40023,7 @@
         <v>1946</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>2183</v>
@@ -40134,8 +40137,8 @@
       <c r="F112" s="9" t="s">
         <v>1946</v>
       </c>
-      <c r="G112" s="12" t="s">
-        <v>2360</v>
+      <c r="G112" s="18" t="s">
+        <v>2556</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>2191</v>
@@ -40211,7 +40214,7 @@
         <v>1935</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>2195</v>
@@ -40289,7 +40292,7 @@
         <v>1935</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>2200</v>
@@ -40562,7 +40565,7 @@
         <v>1940</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="H123" s="9" t="s">
         <v>2219</v>
@@ -40638,7 +40641,7 @@
         <v>1935</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="H125" s="9" t="s">
         <v>2224</v>
@@ -40675,7 +40678,7 @@
         <v>1935</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="H126" s="9" t="s">
         <v>2226</v>
@@ -40751,7 +40754,7 @@
         <v>1935</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="H128" s="9" t="s">
         <v>2231</v>
@@ -40854,7 +40857,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="12" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="H131" s="9" t="s">
         <v>2239</v>
@@ -41002,7 +41005,7 @@
         <v>1946</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="H135" s="9" t="s">
         <v>2249</v>
@@ -41039,7 +41042,7 @@
         <v>1946</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="H136" s="9" t="s">
         <v>2252</v>
@@ -41187,7 +41190,7 @@
         <v>1940</v>
       </c>
       <c r="G140" s="12" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="H140" s="9" t="s">
         <v>2262</v>
@@ -41331,7 +41334,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
       <c r="G144" s="12" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="H144" s="9" t="s">
         <v>2271</v>
@@ -52498,19 +52501,19 @@
         <v>807</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>808</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>422</v>
@@ -52633,22 +52636,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>2487</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>2485</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>2488</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>2490</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>422</v>
@@ -52725,7 +52728,7 @@
         <v>835</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>836</v>
@@ -52754,7 +52757,7 @@
         <v>841</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>842</v>
@@ -52783,7 +52786,7 @@
         <v>841</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>842</v>
@@ -52870,7 +52873,7 @@
         <v>841</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>842</v>
@@ -52899,7 +52902,7 @@
         <v>841</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>842</v>
@@ -52951,22 +52954,22 @@
         <v>833</v>
       </c>
       <c r="C10" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="D10" t="s">
         <v>2327</v>
       </c>
       <c r="E10" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2435</v>
+      </c>
+      <c r="G10" t="s">
         <v>2436</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>2437</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2438</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2439</v>
       </c>
     </row>
   </sheetData>
@@ -53077,7 +53080,7 @@
         <v>877</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -53261,7 +53264,7 @@
         <v>890</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -53284,7 +53287,7 @@
         <v>891</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="F13" s="1">
         <v>-1</v>
@@ -53328,7 +53331,7 @@
         <v>885</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -53349,7 +53352,7 @@
         <v>887</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -53393,7 +53396,7 @@
         <v>894</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -53416,7 +53419,7 @@
         <v>895</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="F19" s="1">
         <v>-1</v>
@@ -53577,7 +53580,7 @@
         <v>2328</v>
       </c>
       <c r="E26" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -53594,7 +53597,7 @@
         <v>2329</v>
       </c>
       <c r="E27" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -53611,7 +53614,7 @@
         <v>2330</v>
       </c>
       <c r="E28" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
     </row>
   </sheetData>
@@ -53841,7 +53844,7 @@
         <v>905</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="K6" s="1">
         <v>6</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27C8C9C-86C6-4A52-AB0E-5A71BC835BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72E0828-661F-4946-AFD2-E414DBEAF0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19630,26 +19630,198 @@
   </si>
   <si>
     <r>
-      <t>덜</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>짠</t>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>콩</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>콩이나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간식도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>당류</t>
     </r>
     <r>
       <rPr>
@@ -19687,8 +19859,1060 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>확인하기</t>
-    </r>
+      <t>보기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간식의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>당류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표시를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>아침을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>야식도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그릇에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>봉지째</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그릇에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>마셔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반찬은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만큼만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만큼만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>담는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>나트륨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -19711,26 +20935,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>「덜</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>짠」</t>
+      <t>나트륨</t>
     </r>
     <r>
       <rPr>
@@ -19818,1248 +21023,7 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콩</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콩이나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간식도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>표시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간식의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>표시를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>세</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>아침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>아침을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그릇에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>봉지째</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그릇에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>물</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뒤에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>물을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>마셔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만큼만</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만큼만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>담는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -40122,10 +40086,10 @@
         <v>1940</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>2573</v>
+        <v>2587</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>2574</v>
+        <v>2588</v>
       </c>
       <c r="K151" s="13" t="s">
         <v>2539</v>
@@ -40157,10 +40121,10 @@
         <v>1940</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="K152" s="13" t="s">
         <v>2542</v>
@@ -40192,10 +40156,10 @@
         <v>1940</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="K153" s="13" t="s">
         <v>2544</v>
@@ -40227,10 +40191,10 @@
         <v>1935</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="K154" s="13" t="s">
         <v>2532</v>
@@ -40262,10 +40226,10 @@
         <v>1935</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="K155" s="13" t="s">
         <v>2530</v>
@@ -40297,10 +40261,10 @@
         <v>1940</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="K156" s="13" t="s">
         <v>2532</v>
@@ -40332,10 +40296,10 @@
         <v>1946</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>944</v>
@@ -40370,10 +40334,10 @@
         <v>1940</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="I158" s="13" t="s">
         <v>942</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBD82C7-BC06-46B0-AF56-A06664DE406F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3A296E-8500-4B6B-BD8A-3482883F47CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7958" uniqueCount="2623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8044" uniqueCount="2638">
   <si>
     <t>항목</t>
   </si>
@@ -20901,31 +20901,1971 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 9, 선택지 27, 목표문구 167, 노출조건 167, 질환규칙 14, 상병코드조건 61, 설정 66</t>
+    <r>
+      <t>식품</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>말해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>무엇으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸라는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것인지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>알기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어려웠다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>덜</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>짠</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제품</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르기</t>
+    </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>식품</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대체</t>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제품군에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나트륨이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>버터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리브유</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>버터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리브유를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>무침은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>들기름으로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>무침에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>들기름을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>마요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>머스터드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>마요네즈</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>머스터드를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>크림소스</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토마토</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>크림소스</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토마토소스를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>닭은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>껍질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>닭고기의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>껍질을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가공육</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>살코기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>햄</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>소시지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>살코기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식초</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>레몬</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식초나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>레몬으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>소금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후추</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>마늘</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>소금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>향신료로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시럽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계피</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가루</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시럽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계피</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가루로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>더하는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>드레싱은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금만</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>드레싱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIET-P-0264</t>
+  </si>
+  <si>
+    <t>DIET-P-0265</t>
+  </si>
+  <si>
+    <t>DIET-P-0266</t>
+  </si>
+  <si>
+    <t>DIET-P-0267</t>
+  </si>
+  <si>
+    <t>DIET-P-0268</t>
+  </si>
+  <si>
+    <t>질문 9, 선택지 27, 목표문구 172, 노출조건 172, 질환규칙 14, 상병코드조건 61, 설정 66</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> B</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>형태와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
     </r>
     <r>
       <rPr>
@@ -20954,169 +22894,791 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>말해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>무엇으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>바꾸라는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것인지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>알기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어려웠다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
+      <t xml:space="preserve"> 15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넣어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 172</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>됨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기름은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리브유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>들기름으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지정하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>카놀라유는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. DIET-P-0253~0268(0261 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>퇴근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>집에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미루지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>늦게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>오징어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>새우로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -21135,436 +23697,73 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> B</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>」</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>형태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 167</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>됨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카놀라유는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. DIET-P-0253~0263(0261 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>덜</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>짠</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제품</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르기</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제품군에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나트륨이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>해산물로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>차리는</t>
     </r>
     <r>
       <rPr>
@@ -21595,111 +23794,110 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
+  </si>
+  <si>
+    <r>
+      <t>생선은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구이로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>생선을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>튀기지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구워</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
     </r>
     <r>
       <rPr>
@@ -21730,1328 +23928,6 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>무침은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>무침에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>마요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>머스터드</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>마요네즈</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>머스터드를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>크림소스</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>토마토</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>크림소스</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>토마토소스를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>닭은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>껍질</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>빼고</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>닭고기의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>껍질을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>빼고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>가공육</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>살코기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>햄</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>소시지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>살코기를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식초</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>레몬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식초나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>레몬으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>소금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후추</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>마늘</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>소금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>향신료로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>시럽</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계피</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가루</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>시럽</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계피</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가루로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더하는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>드레싱은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조금만</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>드레싱</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄여</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -23518,7 +24394,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M168" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M173" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="phrase_version"/>
@@ -23539,7 +24415,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K168" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K173" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1900-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1900-000002000000}" name="phrase_version"/>
@@ -23952,7 +24828,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>2597</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -24013,13 +24889,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>2598</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>2599</v>
-      </c>
       <c r="C20" s="13" t="s">
-        <v>2600</v>
+        <v>2627</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>2552</v>
@@ -36438,7 +37314,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -42128,10 +43004,10 @@
         <v>1940</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="K151" s="13" t="s">
         <v>2537</v>
@@ -42414,10 +43290,10 @@
         <v>1946</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="K159" s="13" t="s">
         <v>2535</v>
@@ -42449,10 +43325,10 @@
         <v>1940</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="K160" s="13" t="s">
         <v>2586</v>
@@ -42484,10 +43360,10 @@
         <v>1940</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="K161" s="13" t="s">
         <v>1482</v>
@@ -42519,10 +43395,10 @@
         <v>1946</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="K162" s="13" t="s">
         <v>1482</v>
@@ -42554,10 +43430,10 @@
         <v>1935</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="K163" s="13" t="s">
         <v>1482</v>
@@ -42589,10 +43465,10 @@
         <v>1940</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="K164" s="13" t="s">
         <v>1937</v>
@@ -42624,10 +43500,10 @@
         <v>1940</v>
       </c>
       <c r="G165" s="13" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="K165" s="13" t="s">
         <v>2537</v>
@@ -42659,10 +43535,10 @@
         <v>1935</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="K166" s="13" t="s">
         <v>2537</v>
@@ -42694,10 +43570,10 @@
         <v>1940</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="K167" s="13" t="s">
         <v>2542</v>
@@ -42729,10 +43605,10 @@
         <v>1940</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="K168" s="13" t="s">
         <v>1482</v>
@@ -42742,6 +43618,184 @@
       </c>
       <c r="M168" s="13">
         <v>197</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" s="13" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="F169" s="13" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G169" s="13" t="s">
+        <v>2628</v>
+      </c>
+      <c r="H169" s="13" t="s">
+        <v>2629</v>
+      </c>
+      <c r="K169" s="13" t="s">
+        <v>2528</v>
+      </c>
+      <c r="L169" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M169" s="13">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" s="13" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C170" s="13" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G170" s="13" t="s">
+        <v>2630</v>
+      </c>
+      <c r="H170" s="13" t="s">
+        <v>2631</v>
+      </c>
+      <c r="K170" s="13" t="s">
+        <v>2530</v>
+      </c>
+      <c r="L170" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M170" s="13">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" s="13" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G171" s="13" t="s">
+        <v>2632</v>
+      </c>
+      <c r="H171" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I171" s="13" t="s">
+        <v>942</v>
+      </c>
+      <c r="K171" s="13" t="s">
+        <v>2530</v>
+      </c>
+      <c r="L171" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M171" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" s="13" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C172" s="13" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G172" s="13" t="s">
+        <v>2634</v>
+      </c>
+      <c r="H172" s="13" t="s">
+        <v>2635</v>
+      </c>
+      <c r="K172" s="13" t="s">
+        <v>1937</v>
+      </c>
+      <c r="L172" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M172" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>868</v>
+      </c>
+      <c r="F173" s="13" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G173" s="13" t="s">
+        <v>2636</v>
+      </c>
+      <c r="H173" s="13" t="s">
+        <v>2637</v>
+      </c>
+      <c r="K173" s="13" t="s">
+        <v>1482</v>
+      </c>
+      <c r="L173" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M173" s="13">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -42755,7 +43809,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -47886,6 +48940,151 @@
       </c>
       <c r="K168" s="13">
         <v>197</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" s="13" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F169" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G169" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H169" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K169" s="13">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" s="13" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C170" s="13" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G170" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H170" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K170" s="13">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" s="13" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G171" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H171" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K171" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" s="13" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C172" s="13" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G172" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H172" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K172" s="13">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F173" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G173" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H173" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="K173" s="13">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3A296E-8500-4B6B-BD8A-3482883F47CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED21C699-33DE-47CD-B78F-0581D316B1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17090,9 +17090,6 @@
     <t>DIET-P-0241</t>
   </si>
   <si>
-    <t>WHO-FAT-2023 / KDA-2023</t>
-  </si>
-  <si>
     <t>DIET-P-0242</t>
   </si>
   <si>
@@ -18392,216 +18389,6 @@
   </si>
   <si>
     <r>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>먹기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>국내외</t>
     </r>
     <r>
@@ -18736,407 +18523,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>대기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>입</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>씹어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>평소보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>씹어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>액체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>상온에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굳는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>액체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
     </r>
   </si>
   <si>
@@ -23928,6 +23314,475 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>KSoLA-2022 / WHO-FAT-2023</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정하기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>꼭꼭</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>평소보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>마가린</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쇼트닝</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>트랜스지방이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>많은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기름을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24828,7 +24683,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>2626</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -24865,7 +24720,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="13" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -24889,44 +24744,44 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
-        <v>2597</v>
+        <v>2590</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>2598</v>
+        <v>2591</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>2627</v>
+        <v>2620</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="13" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>2549</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="C21" s="13" t="s">
         <v>2550</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>2551</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2552</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="13" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>2553</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>2554</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
         <v>2555</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>2556</v>
       </c>
     </row>
   </sheetData>
@@ -37967,10 +37822,10 @@
         <v>1946</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>2595</v>
+        <v>2588</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>2596</v>
+        <v>2589</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -42791,10 +42646,10 @@
         <v>1940</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>2557</v>
+        <v>2632</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>2558</v>
+        <v>2633</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>942</v>
@@ -42803,7 +42658,7 @@
         <v>2528</v>
       </c>
       <c r="L145" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M145" s="13">
         <v>173</v>
@@ -42829,16 +42684,16 @@
         <v>1946</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>2560</v>
+        <v>2634</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>2561</v>
+        <v>2635</v>
       </c>
       <c r="K146" s="13" t="s">
         <v>2530</v>
       </c>
       <c r="L146" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M146" s="13">
         <v>174</v>
@@ -42864,16 +42719,16 @@
         <v>1946</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>2562</v>
+        <v>2636</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>2563</v>
+        <v>2637</v>
       </c>
       <c r="K147" s="13" t="s">
-        <v>2532</v>
+        <v>2631</v>
       </c>
       <c r="L147" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M147" s="13">
         <v>175</v>
@@ -42881,7 +42736,7 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="13" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B148" s="13" t="s">
         <v>833</v>
@@ -42899,16 +42754,16 @@
         <v>1946</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>2564</v>
+        <v>2557</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>2565</v>
+        <v>2558</v>
       </c>
       <c r="K148" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L148" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M148" s="13">
         <v>176</v>
@@ -42916,7 +42771,7 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="13" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>833</v>
@@ -42934,16 +42789,16 @@
         <v>1940</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>2566</v>
+        <v>2559</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>2567</v>
+        <v>2560</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L149" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M149" s="13">
         <v>177</v>
@@ -42951,7 +42806,7 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="13" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>833</v>
@@ -42969,16 +42824,16 @@
         <v>1940</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>2568</v>
+        <v>2561</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>2569</v>
+        <v>2562</v>
       </c>
       <c r="K150" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="L150" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M150" s="13">
         <v>178</v>
@@ -42986,7 +42841,7 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="13" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>833</v>
@@ -43004,16 +42859,16 @@
         <v>1940</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>2599</v>
+        <v>2592</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>2600</v>
+        <v>2593</v>
       </c>
       <c r="K151" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="L151" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M151" s="13">
         <v>179</v>
@@ -43021,7 +42876,7 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="13" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B152" s="13" t="s">
         <v>833</v>
@@ -43039,16 +42894,16 @@
         <v>1940</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>2570</v>
+        <v>2563</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>2571</v>
+        <v>2564</v>
       </c>
       <c r="K152" s="13" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="L152" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M152" s="13">
         <v>180</v>
@@ -43056,7 +42911,7 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="13" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>833</v>
@@ -43074,16 +42929,16 @@
         <v>1940</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>2572</v>
+        <v>2565</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>2573</v>
+        <v>2566</v>
       </c>
       <c r="K153" s="13" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="L153" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M153" s="13">
         <v>181</v>
@@ -43091,7 +42946,7 @@
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="13" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B154" s="13" t="s">
         <v>833</v>
@@ -43109,16 +42964,16 @@
         <v>1935</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>2574</v>
+        <v>2567</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>2575</v>
+        <v>2568</v>
       </c>
       <c r="K154" s="13" t="s">
         <v>2530</v>
       </c>
       <c r="L154" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M154" s="13">
         <v>182</v>
@@ -43126,7 +42981,7 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="13" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>833</v>
@@ -43144,16 +42999,16 @@
         <v>1935</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>2576</v>
+        <v>2569</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>2577</v>
+        <v>2570</v>
       </c>
       <c r="K155" s="13" t="s">
         <v>2528</v>
       </c>
       <c r="L155" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M155" s="13">
         <v>183</v>
@@ -43161,7 +43016,7 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="13" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B156" s="13" t="s">
         <v>833</v>
@@ -43179,16 +43034,16 @@
         <v>1940</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>2578</v>
+        <v>2571</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>2579</v>
+        <v>2572</v>
       </c>
       <c r="K156" s="13" t="s">
         <v>2530</v>
       </c>
       <c r="L156" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M156" s="13">
         <v>184</v>
@@ -43196,7 +43051,7 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="13" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>833</v>
@@ -43214,10 +43069,10 @@
         <v>1946</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>2580</v>
+        <v>2573</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>2581</v>
+        <v>2574</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>944</v>
@@ -43226,7 +43081,7 @@
         <v>2528</v>
       </c>
       <c r="L157" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M157" s="13">
         <v>185</v>
@@ -43234,7 +43089,7 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="13" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>833</v>
@@ -43252,10 +43107,10 @@
         <v>1940</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>2582</v>
+        <v>2575</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>2583</v>
+        <v>2576</v>
       </c>
       <c r="I158" s="13" t="s">
         <v>942</v>
@@ -43264,7 +43119,7 @@
         <v>2528</v>
       </c>
       <c r="L158" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M158" s="13">
         <v>186</v>
@@ -43272,7 +43127,7 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="13" t="s">
-        <v>2584</v>
+        <v>2577</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>833</v>
@@ -43290,16 +43145,16 @@
         <v>1946</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>2601</v>
+        <v>2594</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>2602</v>
+        <v>2595</v>
       </c>
       <c r="K159" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L159" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M159" s="13">
         <v>187</v>
@@ -43307,7 +43162,7 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="13" t="s">
-        <v>2585</v>
+        <v>2578</v>
       </c>
       <c r="B160" s="13" t="s">
         <v>833</v>
@@ -43325,16 +43180,16 @@
         <v>1940</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>2603</v>
+        <v>2596</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>2604</v>
+        <v>2597</v>
       </c>
       <c r="K160" s="13" t="s">
-        <v>2586</v>
+        <v>2579</v>
       </c>
       <c r="L160" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M160" s="13">
         <v>188</v>
@@ -43342,7 +43197,7 @@
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="13" t="s">
-        <v>2587</v>
+        <v>2580</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>833</v>
@@ -43360,16 +43215,16 @@
         <v>1940</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>2605</v>
+        <v>2598</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>2606</v>
+        <v>2599</v>
       </c>
       <c r="K161" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L161" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M161" s="13">
         <v>189</v>
@@ -43377,7 +43232,7 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="13" t="s">
-        <v>2588</v>
+        <v>2581</v>
       </c>
       <c r="B162" s="13" t="s">
         <v>833</v>
@@ -43395,16 +43250,16 @@
         <v>1946</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>2607</v>
+        <v>2600</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>2608</v>
+        <v>2601</v>
       </c>
       <c r="K162" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L162" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M162" s="13">
         <v>190</v>
@@ -43412,7 +43267,7 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="13" t="s">
-        <v>2589</v>
+        <v>2582</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>833</v>
@@ -43430,16 +43285,16 @@
         <v>1935</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>2609</v>
+        <v>2602</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>2610</v>
+        <v>2603</v>
       </c>
       <c r="K163" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L163" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M163" s="13">
         <v>191</v>
@@ -43447,7 +43302,7 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="13" t="s">
-        <v>2590</v>
+        <v>2583</v>
       </c>
       <c r="B164" s="13" t="s">
         <v>833</v>
@@ -43465,16 +43320,16 @@
         <v>1940</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>2611</v>
+        <v>2604</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>2612</v>
+        <v>2605</v>
       </c>
       <c r="K164" s="13" t="s">
         <v>1937</v>
       </c>
       <c r="L164" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M164" s="13">
         <v>192</v>
@@ -43482,7 +43337,7 @@
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="13" t="s">
-        <v>2591</v>
+        <v>2584</v>
       </c>
       <c r="B165" s="13" t="s">
         <v>833</v>
@@ -43500,16 +43355,16 @@
         <v>1940</v>
       </c>
       <c r="G165" s="13" t="s">
-        <v>2613</v>
+        <v>2606</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>2614</v>
+        <v>2607</v>
       </c>
       <c r="K165" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="L165" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M165" s="13">
         <v>193</v>
@@ -43517,7 +43372,7 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="13" t="s">
-        <v>2592</v>
+        <v>2585</v>
       </c>
       <c r="B166" s="13" t="s">
         <v>833</v>
@@ -43535,16 +43390,16 @@
         <v>1935</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>2615</v>
+        <v>2608</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>2616</v>
+        <v>2609</v>
       </c>
       <c r="K166" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="L166" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M166" s="13">
         <v>194</v>
@@ -43552,7 +43407,7 @@
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="13" t="s">
-        <v>2593</v>
+        <v>2586</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>833</v>
@@ -43570,16 +43425,16 @@
         <v>1940</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>2617</v>
+        <v>2610</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>2618</v>
+        <v>2611</v>
       </c>
       <c r="K167" s="13" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="L167" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M167" s="13">
         <v>196</v>
@@ -43587,7 +43442,7 @@
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="13" t="s">
-        <v>2594</v>
+        <v>2587</v>
       </c>
       <c r="B168" s="13" t="s">
         <v>833</v>
@@ -43605,16 +43460,16 @@
         <v>1940</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>2619</v>
+        <v>2612</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>2620</v>
+        <v>2613</v>
       </c>
       <c r="K168" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L168" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M168" s="13">
         <v>197</v>
@@ -43622,7 +43477,7 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="13" t="s">
-        <v>2621</v>
+        <v>2614</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>833</v>
@@ -43640,16 +43495,16 @@
         <v>1935</v>
       </c>
       <c r="G169" s="13" t="s">
-        <v>2628</v>
+        <v>2621</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>2629</v>
+        <v>2622</v>
       </c>
       <c r="K169" s="13" t="s">
         <v>2528</v>
       </c>
       <c r="L169" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M169" s="13">
         <v>198</v>
@@ -43657,7 +43512,7 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="13" t="s">
-        <v>2622</v>
+        <v>2615</v>
       </c>
       <c r="B170" s="13" t="s">
         <v>833</v>
@@ -43675,16 +43530,16 @@
         <v>1940</v>
       </c>
       <c r="G170" s="13" t="s">
-        <v>2630</v>
+        <v>2623</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>2631</v>
+        <v>2624</v>
       </c>
       <c r="K170" s="13" t="s">
         <v>2530</v>
       </c>
       <c r="L170" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M170" s="13">
         <v>199</v>
@@ -43692,7 +43547,7 @@
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="13" t="s">
-        <v>2623</v>
+        <v>2616</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>833</v>
@@ -43710,10 +43565,10 @@
         <v>1940</v>
       </c>
       <c r="G171" s="13" t="s">
-        <v>2632</v>
+        <v>2625</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>2633</v>
+        <v>2626</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>942</v>
@@ -43722,7 +43577,7 @@
         <v>2530</v>
       </c>
       <c r="L171" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M171" s="13">
         <v>200</v>
@@ -43730,7 +43585,7 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="13" t="s">
-        <v>2624</v>
+        <v>2617</v>
       </c>
       <c r="B172" s="13" t="s">
         <v>833</v>
@@ -43748,16 +43603,16 @@
         <v>1946</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>2634</v>
+        <v>2627</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>2635</v>
+        <v>2628</v>
       </c>
       <c r="K172" s="13" t="s">
         <v>1937</v>
       </c>
       <c r="L172" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M172" s="13">
         <v>201</v>
@@ -43765,7 +43620,7 @@
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="13" t="s">
-        <v>2625</v>
+        <v>2618</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>833</v>
@@ -43783,16 +43638,16 @@
         <v>1935</v>
       </c>
       <c r="G173" s="13" t="s">
-        <v>2636</v>
+        <v>2629</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>2637</v>
+        <v>2630</v>
       </c>
       <c r="K173" s="13" t="s">
         <v>1482</v>
       </c>
       <c r="L173" s="13" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="M173" s="13">
         <v>202</v>
@@ -48335,7 +48190,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="13" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B148" s="13" t="s">
         <v>833</v>
@@ -48364,7 +48219,7 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="13" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>833</v>
@@ -48393,7 +48248,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="13" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>833</v>
@@ -48422,7 +48277,7 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="13" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>833</v>
@@ -48451,7 +48306,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="13" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B152" s="13" t="s">
         <v>833</v>
@@ -48480,7 +48335,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="13" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>833</v>
@@ -48509,7 +48364,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="13" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B154" s="13" t="s">
         <v>833</v>
@@ -48538,7 +48393,7 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="13" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>833</v>
@@ -48567,7 +48422,7 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="13" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B156" s="13" t="s">
         <v>833</v>
@@ -48596,7 +48451,7 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="13" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>833</v>
@@ -48625,7 +48480,7 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="13" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>833</v>
@@ -48654,7 +48509,7 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="13" t="s">
-        <v>2584</v>
+        <v>2577</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>833</v>
@@ -48683,7 +48538,7 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="13" t="s">
-        <v>2585</v>
+        <v>2578</v>
       </c>
       <c r="B160" s="13" t="s">
         <v>833</v>
@@ -48712,7 +48567,7 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="13" t="s">
-        <v>2587</v>
+        <v>2580</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>833</v>
@@ -48741,7 +48596,7 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="13" t="s">
-        <v>2588</v>
+        <v>2581</v>
       </c>
       <c r="B162" s="13" t="s">
         <v>833</v>
@@ -48770,7 +48625,7 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="13" t="s">
-        <v>2589</v>
+        <v>2582</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>833</v>
@@ -48799,7 +48654,7 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="13" t="s">
-        <v>2590</v>
+        <v>2583</v>
       </c>
       <c r="B164" s="13" t="s">
         <v>833</v>
@@ -48828,7 +48683,7 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="13" t="s">
-        <v>2591</v>
+        <v>2584</v>
       </c>
       <c r="B165" s="13" t="s">
         <v>833</v>
@@ -48857,7 +48712,7 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="13" t="s">
-        <v>2592</v>
+        <v>2585</v>
       </c>
       <c r="B166" s="13" t="s">
         <v>833</v>
@@ -48886,7 +48741,7 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="13" t="s">
-        <v>2593</v>
+        <v>2586</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>833</v>
@@ -48915,7 +48770,7 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="13" t="s">
-        <v>2594</v>
+        <v>2587</v>
       </c>
       <c r="B168" s="13" t="s">
         <v>833</v>
@@ -48944,7 +48799,7 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="13" t="s">
-        <v>2621</v>
+        <v>2614</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>833</v>
@@ -48973,7 +48828,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="13" t="s">
-        <v>2622</v>
+        <v>2615</v>
       </c>
       <c r="B170" s="13" t="s">
         <v>833</v>
@@ -49002,7 +48857,7 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="13" t="s">
-        <v>2623</v>
+        <v>2616</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>833</v>
@@ -49031,7 +48886,7 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="13" t="s">
-        <v>2624</v>
+        <v>2617</v>
       </c>
       <c r="B172" s="13" t="s">
         <v>833</v>
@@ -49060,7 +48915,7 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="13" t="s">
-        <v>2625</v>
+        <v>2618</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>833</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CB3997-1B21-4DAF-AE8A-1DD0AD287EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1019A797-5261-4C05-8041-012B7B4103AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8050" uniqueCount="2642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8042" uniqueCount="2635">
   <si>
     <t>항목</t>
   </si>
@@ -7445,10 +7445,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -17133,1259 +17129,6 @@
   </si>
   <si>
     <r>
-      <t>바뀐</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 2026-10-06</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 143</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식사</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개뿐이고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식사</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>속도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>도전</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>157개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있던</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>칸을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채웠다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>근거는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한당뇨병학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2023, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한고혈압학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2022, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한국지질</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>동맥경화학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2022, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한비만학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, WHO 2023 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지방</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식약처</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나트륨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저감</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. DIET-P-0239~0252. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>의학</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검수</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>노출조건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구세트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>수정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>오늘은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굽거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>찌기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늦은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카페인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>튀김</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굽거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>찌기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늦은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카페인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구세트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>국내외</t>
     </r>
     <r>
@@ -20285,206 +19028,6 @@
   </si>
   <si>
     <r>
-      <t>식품</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>말해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>무엇으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>바꾸라는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것인지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>알기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어려웠다</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>덜</t>
     </r>
     <r>
@@ -22153,364 +20696,6 @@
   </si>
   <si>
     <r>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> B</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>」</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>형태와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 172</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>됨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지정하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카놀라유는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. DIET-P-0253~0268(0261 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>주말도</t>
     </r>
     <r>
@@ -24918,6 +23103,522 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>내보냄</t>
+    </r>
+  </si>
+  <si>
+    <t>{지난 끼니}에 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · 2026-10-07</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{지난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{지난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-06 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
   </si>
 </sst>
@@ -25727,7 +24428,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -25744,10 +24445,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>2511</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>2512</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
@@ -25755,7 +24456,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
@@ -25771,7 +24472,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
@@ -25779,7 +24480,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1">
@@ -25819,7 +24520,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>2618</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -25851,17 +24552,17 @@
         <v>22</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="13" t="s">
-        <v>2546</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="13" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -25869,55 +24570,27 @@
         <v>0</v>
       </c>
       <c r="B19" s="13" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>2487</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>2488</v>
-      </c>
       <c r="D19" s="13" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
-        <v>2589</v>
+        <v>2631</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>2590</v>
+        <v>2632</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>2619</v>
+        <v>2633</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="13" t="s">
-        <v>2547</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>2548</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>2549</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="13" t="s">
-        <v>2551</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>2552</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>2553</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>2554</v>
+        <v>2634</v>
       </c>
     </row>
   </sheetData>
@@ -28085,7 +26758,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="15" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>1168</v>
@@ -28114,7 +26787,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="15" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>1168</v>
@@ -28143,7 +26816,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="15" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>1168</v>
@@ -28172,7 +26845,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="15" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>1168</v>
@@ -29229,7 +27902,7 @@
         <v>1319</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>1166</v>
@@ -29238,7 +27911,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="15" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>1315</v>
@@ -29722,10 +28395,10 @@
         <v>1382</v>
       </c>
       <c r="B58" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C58" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="D58" t="s">
         <v>1384</v>
@@ -29740,7 +28413,7 @@
         <v>1182</v>
       </c>
       <c r="J58" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="K58">
         <v>58</v>
@@ -29751,10 +28424,10 @@
         <v>1386</v>
       </c>
       <c r="B59" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C59" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="D59" t="s">
         <v>1387</v>
@@ -29769,7 +28442,7 @@
         <v>1182</v>
       </c>
       <c r="J59" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="K59">
         <v>59</v>
@@ -29780,10 +28453,10 @@
         <v>1388</v>
       </c>
       <c r="B60" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C60" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="D60" t="s">
         <v>1186</v>
@@ -29798,7 +28471,7 @@
         <v>1182</v>
       </c>
       <c r="J60" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="K60">
         <v>60</v>
@@ -29809,10 +28482,10 @@
         <v>1389</v>
       </c>
       <c r="B61" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C61" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="D61" t="s">
         <v>769</v>
@@ -29827,7 +28500,7 @@
         <v>1182</v>
       </c>
       <c r="J61" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="K61">
         <v>61</v>
@@ -29922,13 +28595,13 @@
         <v>2363</v>
       </c>
       <c r="B65" t="s">
+        <v>2437</v>
+      </c>
+      <c r="C65" t="s">
         <v>2438</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>2439</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2440</v>
       </c>
       <c r="E65" t="s">
         <v>1393</v>
@@ -29937,21 +28610,21 @@
         <v>1182</v>
       </c>
       <c r="J65" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="13" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C66" s="13" t="s">
+        <v>2462</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>2463</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>2464</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>1393</v>
@@ -29960,21 +28633,21 @@
         <v>1182</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="13" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>1393</v>
@@ -29983,7 +28656,7 @@
         <v>1182</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
   </sheetData>
@@ -30055,10 +28728,10 @@
         <v>1407</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>2500</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>2501</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>2502</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -30079,10 +28752,10 @@
         <v>1407</v>
       </c>
       <c r="G3" s="14" t="s">
+        <v>2500</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>2501</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>2502</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -30103,10 +28776,10 @@
         <v>1407</v>
       </c>
       <c r="G4" s="14" t="s">
+        <v>2500</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>2501</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>2502</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -30549,35 +29222,35 @@
         <v>1450</v>
       </c>
       <c r="H23" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="13" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>2458</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="E24" s="13" t="s">
         <v>2459</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="G24" s="13" t="s">
         <v>2460</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>2461</v>
-      </c>
       <c r="H24" s="13" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="13" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>1412</v>
@@ -30586,10 +29259,10 @@
         <v>1939</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -30597,19 +29270,19 @@
         <v>1318</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>1412</v>
       </c>
       <c r="E26" s="13" t="s">
+        <v>2476</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>2477</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>2478</v>
-      </c>
       <c r="H26" s="13" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -30617,7 +29290,7 @@
         <v>1162</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>1412</v>
@@ -30629,10 +29302,10 @@
         <v>1403</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -30640,7 +29313,7 @@
         <v>1162</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>1406</v>
@@ -30652,10 +29325,10 @@
         <v>1416</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -30663,7 +29336,7 @@
         <v>1169</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>1412</v>
@@ -30675,10 +29348,10 @@
         <v>1416</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -30686,7 +29359,7 @@
         <v>1169</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>1420</v>
@@ -30698,10 +29371,10 @@
         <v>1403</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -30709,7 +29382,7 @@
         <v>1172</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>1412</v>
@@ -30721,10 +29394,10 @@
         <v>1416</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -30732,7 +29405,7 @@
         <v>1172</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>1420</v>
@@ -30744,10 +29417,10 @@
         <v>1403</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -30755,7 +29428,7 @@
         <v>1175</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>1412</v>
@@ -30764,13 +29437,13 @@
         <v>704</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -30778,22 +29451,22 @@
         <v>1175</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>1412</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
   </sheetData>
@@ -37961,13 +36634,13 @@
         <v>1898</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C39" s="13" t="s">
+        <v>2494</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>2495</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>2496</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -38006,10 +36679,10 @@
         <v>1908</v>
       </c>
       <c r="C42" s="13" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D42" s="13" t="s">
         <v>2469</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>2470</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -38059,13 +36732,13 @@
         <v>2331</v>
       </c>
       <c r="B46" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C46" t="s">
         <v>2443</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>2444</v>
-      </c>
-      <c r="D46" t="s">
-        <v>2445</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -38073,13 +36746,13 @@
         <v>2361</v>
       </c>
       <c r="B47" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C47" t="s">
         <v>2446</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>2447</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2448</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -38087,13 +36760,13 @@
         <v>2362</v>
       </c>
       <c r="B48" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C48" t="s">
         <v>2449</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>2450</v>
-      </c>
-      <c r="D48" t="s">
-        <v>2451</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -38101,27 +36774,27 @@
         <v>2372</v>
       </c>
       <c r="B49" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C49" t="s">
         <v>2452</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>2453</v>
-      </c>
-      <c r="D49" t="s">
-        <v>2454</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="13" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>2497</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="D50" s="13" t="s">
         <v>2498</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>2499</v>
       </c>
     </row>
   </sheetData>
@@ -38958,10 +37631,10 @@
         <v>1945</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>2587</v>
+        <v>2577</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>2588</v>
+        <v>2578</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -39441,7 +38114,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="17" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>2006</v>
@@ -42549,7 +41222,7 @@
         <v>1945</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>2189</v>
@@ -43764,7 +42437,7 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="13" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B145" s="13" t="s">
         <v>832</v>
@@ -43782,19 +42455,19 @@
         <v>1939</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>2631</v>
+        <v>2618</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>2632</v>
+        <v>2619</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>941</v>
       </c>
       <c r="K145" s="13" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="L145" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M145" s="13">
         <v>173</v>
@@ -43802,7 +42475,7 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="13" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B146" s="13" t="s">
         <v>832</v>
@@ -43820,16 +42493,16 @@
         <v>1945</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>2633</v>
+        <v>2620</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>2634</v>
+        <v>2621</v>
       </c>
       <c r="K146" s="13" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L146" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M146" s="13">
         <v>174</v>
@@ -43837,7 +42510,7 @@
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="13" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B147" s="13" t="s">
         <v>832</v>
@@ -43855,16 +42528,16 @@
         <v>1945</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>2635</v>
+        <v>2622</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>2636</v>
+        <v>2623</v>
       </c>
       <c r="K147" s="13" t="s">
-        <v>2630</v>
+        <v>2617</v>
       </c>
       <c r="L147" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M147" s="13">
         <v>175</v>
@@ -43872,7 +42545,7 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="13" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B148" s="13" t="s">
         <v>832</v>
@@ -43890,16 +42563,16 @@
         <v>1945</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>2556</v>
+        <v>2546</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>2557</v>
+        <v>2547</v>
       </c>
       <c r="K148" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L148" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M148" s="13">
         <v>176</v>
@@ -43907,7 +42580,7 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="13" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>832</v>
@@ -43925,16 +42598,16 @@
         <v>1939</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>2558</v>
+        <v>2548</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>2559</v>
+        <v>2549</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="L149" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M149" s="13">
         <v>177</v>
@@ -43942,7 +42615,7 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="13" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>832</v>
@@ -43960,16 +42633,16 @@
         <v>1939</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>2560</v>
+        <v>2550</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>2561</v>
+        <v>2551</v>
       </c>
       <c r="K150" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L150" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M150" s="13">
         <v>178</v>
@@ -43977,7 +42650,7 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="13" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>832</v>
@@ -43995,16 +42668,16 @@
         <v>1939</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>2591</v>
+        <v>2579</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>2592</v>
+        <v>2580</v>
       </c>
       <c r="K151" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L151" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M151" s="13">
         <v>179</v>
@@ -44012,7 +42685,7 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B152" s="13" t="s">
         <v>832</v>
@@ -44030,16 +42703,16 @@
         <v>1939</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>2562</v>
+        <v>2552</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>2563</v>
+        <v>2553</v>
       </c>
       <c r="K152" s="13" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="L152" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M152" s="13">
         <v>180</v>
@@ -44047,7 +42720,7 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="13" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>832</v>
@@ -44065,16 +42738,16 @@
         <v>1939</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>2564</v>
+        <v>2554</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>2565</v>
+        <v>2555</v>
       </c>
       <c r="K153" s="13" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="L153" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M153" s="13">
         <v>181</v>
@@ -44082,7 +42755,7 @@
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="13" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B154" s="13" t="s">
         <v>832</v>
@@ -44100,16 +42773,16 @@
         <v>1934</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>2566</v>
+        <v>2556</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>2567</v>
+        <v>2557</v>
       </c>
       <c r="K154" s="13" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L154" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M154" s="13">
         <v>182</v>
@@ -44117,7 +42790,7 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="13" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>832</v>
@@ -44135,16 +42808,16 @@
         <v>1934</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>2568</v>
+        <v>2558</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>2569</v>
+        <v>2559</v>
       </c>
       <c r="K155" s="13" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="L155" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M155" s="13">
         <v>183</v>
@@ -44152,7 +42825,7 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="13" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B156" s="13" t="s">
         <v>832</v>
@@ -44170,16 +42843,16 @@
         <v>1939</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>2570</v>
+        <v>2560</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>2571</v>
+        <v>2561</v>
       </c>
       <c r="K156" s="13" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L156" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M156" s="13">
         <v>184</v>
@@ -44187,7 +42860,7 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="13" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>832</v>
@@ -44205,19 +42878,19 @@
         <v>1945</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>2572</v>
+        <v>2562</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>2573</v>
+        <v>2563</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>943</v>
       </c>
       <c r="K157" s="13" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="L157" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M157" s="13">
         <v>185</v>
@@ -44225,7 +42898,7 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="13" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>832</v>
@@ -44243,19 +42916,19 @@
         <v>1939</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>2574</v>
+        <v>2564</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>2575</v>
+        <v>2565</v>
       </c>
       <c r="I158" s="13" t="s">
         <v>941</v>
       </c>
       <c r="K158" s="13" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="L158" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M158" s="13">
         <v>186</v>
@@ -44263,7 +42936,7 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="13" t="s">
-        <v>2576</v>
+        <v>2566</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>832</v>
@@ -44281,16 +42954,16 @@
         <v>1945</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>2593</v>
+        <v>2581</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>2594</v>
+        <v>2582</v>
       </c>
       <c r="K159" s="13" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="L159" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M159" s="13">
         <v>187</v>
@@ -44298,7 +42971,7 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="13" t="s">
-        <v>2577</v>
+        <v>2567</v>
       </c>
       <c r="B160" s="13" t="s">
         <v>832</v>
@@ -44316,16 +42989,16 @@
         <v>1939</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>2595</v>
+        <v>2583</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>2596</v>
+        <v>2584</v>
       </c>
       <c r="K160" s="13" t="s">
-        <v>2578</v>
+        <v>2568</v>
       </c>
       <c r="L160" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M160" s="13">
         <v>188</v>
@@ -44333,7 +43006,7 @@
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="13" t="s">
-        <v>2579</v>
+        <v>2569</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>832</v>
@@ -44351,16 +43024,16 @@
         <v>1939</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>2597</v>
+        <v>2585</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>2598</v>
+        <v>2586</v>
       </c>
       <c r="K161" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L161" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M161" s="13">
         <v>189</v>
@@ -44368,7 +43041,7 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="13" t="s">
-        <v>2580</v>
+        <v>2570</v>
       </c>
       <c r="B162" s="13" t="s">
         <v>832</v>
@@ -44386,16 +43059,16 @@
         <v>1945</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>2599</v>
+        <v>2587</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>2600</v>
+        <v>2588</v>
       </c>
       <c r="K162" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L162" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M162" s="13">
         <v>190</v>
@@ -44403,7 +43076,7 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="13" t="s">
-        <v>2581</v>
+        <v>2571</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>832</v>
@@ -44421,16 +43094,16 @@
         <v>1934</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>2601</v>
+        <v>2589</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>2602</v>
+        <v>2590</v>
       </c>
       <c r="K163" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L163" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M163" s="13">
         <v>191</v>
@@ -44438,7 +43111,7 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="13" t="s">
-        <v>2582</v>
+        <v>2572</v>
       </c>
       <c r="B164" s="13" t="s">
         <v>832</v>
@@ -44456,16 +43129,16 @@
         <v>1939</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>2603</v>
+        <v>2591</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>2604</v>
+        <v>2592</v>
       </c>
       <c r="K164" s="13" t="s">
         <v>1936</v>
       </c>
       <c r="L164" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M164" s="13">
         <v>192</v>
@@ -44473,7 +43146,7 @@
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="13" t="s">
-        <v>2583</v>
+        <v>2573</v>
       </c>
       <c r="B165" s="13" t="s">
         <v>832</v>
@@ -44491,16 +43164,16 @@
         <v>1939</v>
       </c>
       <c r="G165" s="13" t="s">
-        <v>2605</v>
+        <v>2593</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>2606</v>
+        <v>2594</v>
       </c>
       <c r="K165" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L165" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M165" s="13">
         <v>193</v>
@@ -44508,7 +43181,7 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="13" t="s">
-        <v>2584</v>
+        <v>2574</v>
       </c>
       <c r="B166" s="13" t="s">
         <v>832</v>
@@ -44526,16 +43199,16 @@
         <v>1934</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>2607</v>
+        <v>2595</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>2608</v>
+        <v>2596</v>
       </c>
       <c r="K166" s="13" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="L166" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M166" s="13">
         <v>194</v>
@@ -44543,7 +43216,7 @@
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="13" t="s">
-        <v>2585</v>
+        <v>2575</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>832</v>
@@ -44561,16 +43234,16 @@
         <v>1939</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>2609</v>
+        <v>2597</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>2610</v>
+        <v>2598</v>
       </c>
       <c r="K167" s="13" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="L167" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M167" s="13">
         <v>196</v>
@@ -44578,7 +43251,7 @@
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="13" t="s">
-        <v>2586</v>
+        <v>2576</v>
       </c>
       <c r="B168" s="13" t="s">
         <v>832</v>
@@ -44596,16 +43269,16 @@
         <v>1939</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>2611</v>
+        <v>2599</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>2612</v>
+        <v>2600</v>
       </c>
       <c r="K168" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L168" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M168" s="13">
         <v>197</v>
@@ -44613,7 +43286,7 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="13" t="s">
-        <v>2613</v>
+        <v>2601</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>832</v>
@@ -44631,16 +43304,16 @@
         <v>1934</v>
       </c>
       <c r="G169" s="13" t="s">
-        <v>2620</v>
+        <v>2607</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>2621</v>
+        <v>2608</v>
       </c>
       <c r="K169" s="13" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="L169" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M169" s="13">
         <v>198</v>
@@ -44648,7 +43321,7 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="13" t="s">
-        <v>2614</v>
+        <v>2602</v>
       </c>
       <c r="B170" s="13" t="s">
         <v>832</v>
@@ -44666,16 +43339,16 @@
         <v>1939</v>
       </c>
       <c r="G170" s="13" t="s">
-        <v>2622</v>
+        <v>2609</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>2623</v>
+        <v>2610</v>
       </c>
       <c r="K170" s="13" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L170" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M170" s="13">
         <v>199</v>
@@ -44683,7 +43356,7 @@
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="13" t="s">
-        <v>2615</v>
+        <v>2603</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>832</v>
@@ -44701,19 +43374,19 @@
         <v>1939</v>
       </c>
       <c r="G171" s="13" t="s">
-        <v>2624</v>
+        <v>2611</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>2625</v>
+        <v>2612</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>941</v>
       </c>
       <c r="K171" s="13" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="L171" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M171" s="13">
         <v>200</v>
@@ -44721,7 +43394,7 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="13" t="s">
-        <v>2616</v>
+        <v>2604</v>
       </c>
       <c r="B172" s="13" t="s">
         <v>832</v>
@@ -44739,16 +43412,16 @@
         <v>1945</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>2626</v>
+        <v>2613</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>2627</v>
+        <v>2614</v>
       </c>
       <c r="K172" s="13" t="s">
         <v>1936</v>
       </c>
       <c r="L172" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M172" s="13">
         <v>201</v>
@@ -44756,7 +43429,7 @@
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="13" t="s">
-        <v>2617</v>
+        <v>2605</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>832</v>
@@ -44774,16 +43447,16 @@
         <v>1934</v>
       </c>
       <c r="G173" s="13" t="s">
-        <v>2628</v>
+        <v>2615</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>2629</v>
+        <v>2616</v>
       </c>
       <c r="K173" s="13" t="s">
         <v>1481</v>
       </c>
       <c r="L173" s="13" t="s">
-        <v>2555</v>
+        <v>2545</v>
       </c>
       <c r="M173" s="13">
         <v>202</v>
@@ -49239,7 +47912,7 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="13" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B145" s="13" t="s">
         <v>832</v>
@@ -49268,7 +47941,7 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="13" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B146" s="13" t="s">
         <v>832</v>
@@ -49297,7 +47970,7 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="13" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B147" s="13" t="s">
         <v>832</v>
@@ -49326,7 +47999,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="13" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B148" s="13" t="s">
         <v>832</v>
@@ -49355,7 +48028,7 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="13" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>832</v>
@@ -49384,7 +48057,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="13" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>832</v>
@@ -49413,7 +48086,7 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="13" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>832</v>
@@ -49442,7 +48115,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="13" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B152" s="13" t="s">
         <v>832</v>
@@ -49471,7 +48144,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="13" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>832</v>
@@ -49500,7 +48173,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="13" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="B154" s="13" t="s">
         <v>832</v>
@@ -49529,7 +48202,7 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="13" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>832</v>
@@ -49558,7 +48231,7 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="13" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B156" s="13" t="s">
         <v>832</v>
@@ -49587,7 +48260,7 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="13" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>832</v>
@@ -49616,7 +48289,7 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="13" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>832</v>
@@ -49645,7 +48318,7 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="13" t="s">
-        <v>2576</v>
+        <v>2566</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>832</v>
@@ -49674,7 +48347,7 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="13" t="s">
-        <v>2577</v>
+        <v>2567</v>
       </c>
       <c r="B160" s="13" t="s">
         <v>832</v>
@@ -49703,7 +48376,7 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="13" t="s">
-        <v>2579</v>
+        <v>2569</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>832</v>
@@ -49732,7 +48405,7 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="13" t="s">
-        <v>2580</v>
+        <v>2570</v>
       </c>
       <c r="B162" s="13" t="s">
         <v>832</v>
@@ -49761,7 +48434,7 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="13" t="s">
-        <v>2581</v>
+        <v>2571</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>832</v>
@@ -49790,7 +48463,7 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="13" t="s">
-        <v>2582</v>
+        <v>2572</v>
       </c>
       <c r="B164" s="13" t="s">
         <v>832</v>
@@ -49819,7 +48492,7 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="13" t="s">
-        <v>2583</v>
+        <v>2573</v>
       </c>
       <c r="B165" s="13" t="s">
         <v>832</v>
@@ -49848,7 +48521,7 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="13" t="s">
-        <v>2584</v>
+        <v>2574</v>
       </c>
       <c r="B166" s="13" t="s">
         <v>832</v>
@@ -49877,7 +48550,7 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="13" t="s">
-        <v>2585</v>
+        <v>2575</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>832</v>
@@ -49906,7 +48579,7 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="13" t="s">
-        <v>2586</v>
+        <v>2576</v>
       </c>
       <c r="B168" s="13" t="s">
         <v>832</v>
@@ -49935,7 +48608,7 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="13" t="s">
-        <v>2613</v>
+        <v>2601</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>832</v>
@@ -49964,7 +48637,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="13" t="s">
-        <v>2614</v>
+        <v>2602</v>
       </c>
       <c r="B170" s="13" t="s">
         <v>832</v>
@@ -49993,7 +48666,7 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="13" t="s">
-        <v>2615</v>
+        <v>2603</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>832</v>
@@ -50022,7 +48695,7 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="13" t="s">
-        <v>2616</v>
+        <v>2604</v>
       </c>
       <c r="B172" s="13" t="s">
         <v>832</v>
@@ -50051,7 +48724,7 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="13" t="s">
-        <v>2617</v>
+        <v>2605</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>832</v>
@@ -50622,7 +49295,7 @@
         <v>287</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>2637</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1">
@@ -52315,7 +50988,7 @@
         <v>444</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>2638</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="24" customHeight="1">
@@ -52820,7 +51493,7 @@
         <v>477</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>2639</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="24" customHeight="1">
@@ -52912,7 +51585,7 @@
         <v>287</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>2637</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="24" customHeight="1">
@@ -53213,7 +51886,7 @@
         <v>287</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>2640</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="24" customHeight="1">
@@ -53328,7 +52001,7 @@
         <v>513</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>2641</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="24" customHeight="1">
@@ -56798,19 +55471,19 @@
         <v>806</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>807</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E4" s="16" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>2493</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>2494</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>422</v>
@@ -56933,22 +55606,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>2479</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>2482</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>2480</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>2483</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>2484</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>2485</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>422</v>
@@ -57198,8 +55871,8 @@
       <c r="D8" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>2424</v>
+      <c r="E8" s="14" t="s">
+        <v>2629</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>841</v>
@@ -57251,22 +55924,22 @@
         <v>832</v>
       </c>
       <c r="C10" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="D10" t="s">
         <v>2325</v>
       </c>
       <c r="E10" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F10" t="s">
         <v>2431</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>2432</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>2433</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2434</v>
       </c>
     </row>
   </sheetData>
@@ -57877,7 +56550,7 @@
         <v>2326</v>
       </c>
       <c r="E26" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -57894,7 +56567,7 @@
         <v>2327</v>
       </c>
       <c r="E27" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -57911,7 +56584,7 @@
         <v>2328</v>
       </c>
       <c r="E28" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
   </sheetData>
@@ -58141,7 +56814,7 @@
         <v>904</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="K6" s="1">
         <v>6</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41867F9-B6C1-4CF1-8F11-1E0EE67A1198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676964F-810D-412E-AAD7-D4794ADE8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25313,6 +25313,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -25675,7 +25679,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배는</t>
+      <t>배부름은</t>
     </r>
     <r>
       <rPr>
@@ -25694,7 +25698,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>어땠나요</t>
+      <t>어느</t>
     </r>
     <r>
       <rPr>
@@ -25704,6 +25708,25 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정도였나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">? </t>
     </r>
     <r>
@@ -25927,11 +25950,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹거나 걸렀어요</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26976,7 +26995,7 @@
         <v>2658</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>2659</v>
@@ -58410,7 +58429,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58617,7 +58636,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -60373,18 +60392,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60406,18 +60425,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676964F-810D-412E-AAD7-D4794ADE8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D6B5C7-D1D2-4D2C-8D5E-88DA9FD01540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25317,6 +25317,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -25375,7 +25379,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>반찬을</t>
+      <t>반찬은</t>
     </r>
     <r>
       <rPr>
@@ -25413,7 +25417,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>가지</t>
+      <t>가지였나요</t>
     </r>
     <r>
       <rPr>
@@ -25423,7 +25427,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>? · {</t>
     </r>
     <r>
       <rPr>
@@ -25432,7 +25436,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드셨나요</t>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25442,6 +25446,120 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번이었나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t>? · {</t>
     </r>
     <r>
@@ -25470,7 +25588,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>전후로</t>
+      <t>후</t>
     </r>
     <r>
       <rPr>
@@ -25489,7 +25607,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>단</t>
+      <t>배부름은</t>
     </r>
     <r>
       <rPr>
@@ -25508,7 +25626,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>음료나</t>
+      <t>어땠나요</t>
     </r>
     <r>
       <rPr>
@@ -25518,7 +25636,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">? </t>
     </r>
     <r>
       <rPr>
@@ -25527,7 +25645,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>간식을</t>
+      <t>등</t>
     </r>
     <r>
       <rPr>
@@ -25537,7 +25655,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
@@ -25546,7 +25664,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>몇</t>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25565,7 +25683,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>번</t>
+      <t>이름</t>
     </r>
     <r>
       <rPr>
@@ -25584,7 +25702,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드셨나요</t>
+      <t>뒤</t>
     </r>
     <r>
       <rPr>
@@ -25594,7 +25712,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25603,7 +25721,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>끼니</t>
+      <t>조사를</t>
     </r>
     <r>
       <rPr>
@@ -25613,7 +25731,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>}</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25622,7 +25740,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>을</t>
+      <t>문장에</t>
     </r>
     <r>
       <rPr>
@@ -25641,7 +25759,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>드신</t>
+      <t>미리</t>
     </r>
     <r>
       <rPr>
@@ -25660,7 +25778,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>뒤</t>
+      <t>써</t>
     </r>
     <r>
       <rPr>
@@ -25679,7 +25797,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배부름은</t>
+      <t>두고</t>
     </r>
     <r>
       <rPr>
@@ -25689,7 +25807,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> 32</t>
     </r>
     <r>
       <rPr>
@@ -25698,7 +25816,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>어느</t>
+      <t>자</t>
     </r>
     <r>
       <rPr>
@@ -25717,7 +25835,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>정도였나요</t>
+      <t>이내를</t>
     </r>
     <r>
       <rPr>
@@ -25727,7 +25845,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">? </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -25736,221 +25854,8 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이름</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뒤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조사를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>써</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 32</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>지킴</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26995,7 +26900,7 @@
         <v>2658</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>2659</v>
@@ -58429,7 +58334,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -60392,18 +60297,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60425,18 +60330,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D6B5C7-D1D2-4D2C-8D5E-88DA9FD01540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C7934D-1326-44F3-B9C0-9A023F983539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="2669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2662">
   <si>
     <t>항목</t>
   </si>
@@ -10977,254 +10977,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단백질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>생선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달걀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-06 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>단계</t>
     </r>
     <r>
@@ -24167,1144 +23919,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다듬기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채소</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전후에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배불렀나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배부르게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>배부르게 먹었어요</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -25322,7 +23936,89 @@
   </si>
   <si>
     <r>
-      <t>{끼니</t>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다듬기</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -25341,6 +24037,1139 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배불렀나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상
+식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거름</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>엔</t>
     </r>
     <r>
@@ -25360,6 +25189,140 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>채소</t>
     </r>
     <r>
@@ -25370,6 +25333,63 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -25427,7 +25447,65 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -25560,7 +25638,27 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -25579,6 +25677,121 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">} </t>
     </r>
     <r>
@@ -25636,6 +25849,102 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">? </t>
     </r>
     <r>
@@ -25645,26 +25954,332 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요
+끼니</t>
     </r>
     <r>
       <rPr>
@@ -25807,6 +26422,44 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>치환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> 32</t>
     </r>
     <r>
@@ -25835,26 +26488,146 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지킴</t>
+      <t>이하로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞춤</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00~07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00, DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -25974,7 +26747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -26029,6 +26802,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -26713,7 +27489,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -26864,60 +27640,32 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>2534</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2535</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2652</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2536</v>
+    <row r="20" spans="1:4" ht="140">
+      <c r="A20" s="20" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>2661</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>2537</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>2538</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2539</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="12" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>2658</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>2668</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>2659</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="12" t="s">
-        <v>2660</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>2661</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>2663</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>2662</v>
       </c>
     </row>
   </sheetData>
@@ -30945,13 +31693,13 @@
         <v>1439</v>
       </c>
       <c r="B66" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C66" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="D66" t="s">
-        <v>2555</v>
+        <v>2552</v>
       </c>
       <c r="E66" t="s">
         <v>1421</v>
@@ -30960,7 +31708,7 @@
         <v>1205</v>
       </c>
       <c r="J66" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -30968,13 +31716,13 @@
         <v>1441</v>
       </c>
       <c r="B67" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C67" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="D67" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="E67" t="s">
         <v>1421</v>
@@ -30983,7 +31731,7 @@
         <v>1205</v>
       </c>
       <c r="J67" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -30994,10 +31742,10 @@
         <v>485</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1189</v>
@@ -31017,10 +31765,10 @@
         <v>485</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1189</v>
@@ -31615,7 +32363,7 @@
         <v>1500</v>
       </c>
       <c r="H24" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -31635,7 +32383,7 @@
         <v>1500</v>
       </c>
       <c r="H25" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -31655,7 +32403,7 @@
         <v>1505</v>
       </c>
       <c r="H26" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31678,7 +32426,7 @@
         <v>1507</v>
       </c>
       <c r="H27" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31701,7 +32449,7 @@
         <v>1507</v>
       </c>
       <c r="H28" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31724,7 +32472,7 @@
         <v>1507</v>
       </c>
       <c r="H29" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31747,7 +32495,7 @@
         <v>1507</v>
       </c>
       <c r="H30" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31770,7 +32518,7 @@
         <v>1507</v>
       </c>
       <c r="H31" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31793,7 +32541,7 @@
         <v>1507</v>
       </c>
       <c r="H32" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31816,7 +32564,7 @@
         <v>1507</v>
       </c>
       <c r="H33" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31839,7 +32587,7 @@
         <v>1507</v>
       </c>
       <c r="H34" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31862,7 +32610,7 @@
         <v>1500</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31885,7 +32633,7 @@
         <v>1500</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31908,7 +32656,7 @@
         <v>1500</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31931,7 +32679,7 @@
         <v>1500</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31954,7 +32702,7 @@
         <v>1500</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
     </row>
   </sheetData>
@@ -39122,13 +39870,13 @@
         <v>1958</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -39167,10 +39915,10 @@
         <v>1968</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -39276,13 +40024,13 @@
         <v>1997</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -44934,7 +45682,7 @@
         <v>840</v>
       </c>
       <c r="C145" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D145" t="s">
         <v>2010</v>
@@ -44946,10 +45694,10 @@
         <v>1502</v>
       </c>
       <c r="G145" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="H145" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="I145" t="s">
         <v>964</v>
@@ -44958,7 +45706,7 @@
         <v>2463</v>
       </c>
       <c r="L145" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -44972,7 +45720,7 @@
         <v>840</v>
       </c>
       <c r="C146" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D146" t="s">
         <v>2010</v>
@@ -44984,16 +45732,16 @@
         <v>2023</v>
       </c>
       <c r="G146" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="H146" t="s">
-        <v>2591</v>
+        <v>2588</v>
       </c>
       <c r="K146" t="s">
         <v>2465</v>
       </c>
       <c r="L146" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -45007,7 +45755,7 @@
         <v>840</v>
       </c>
       <c r="C147" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D147" t="s">
         <v>2010</v>
@@ -45019,16 +45767,16 @@
         <v>2023</v>
       </c>
       <c r="G147" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="H147" t="s">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="K147" t="s">
         <v>2467</v>
       </c>
       <c r="L147" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -45042,7 +45790,7 @@
         <v>840</v>
       </c>
       <c r="C148" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D148" t="s">
         <v>2010</v>
@@ -45054,16 +45802,16 @@
         <v>2023</v>
       </c>
       <c r="G148" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="H148" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="K148" t="s">
         <v>1541</v>
       </c>
       <c r="L148" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -45077,7 +45825,7 @@
         <v>840</v>
       </c>
       <c r="C149" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D149" t="s">
         <v>2010</v>
@@ -45089,16 +45837,16 @@
         <v>1502</v>
       </c>
       <c r="G149" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="H149" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="K149" t="s">
         <v>2470</v>
       </c>
       <c r="L149" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -45112,7 +45860,7 @@
         <v>840</v>
       </c>
       <c r="C150" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D150" t="s">
         <v>2010</v>
@@ -45124,16 +45872,16 @@
         <v>1502</v>
       </c>
       <c r="G150" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="H150" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="K150" t="s">
         <v>2472</v>
       </c>
       <c r="L150" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -45147,7 +45895,7 @@
         <v>840</v>
       </c>
       <c r="C151" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D151" t="s">
         <v>2010</v>
@@ -45159,16 +45907,16 @@
         <v>1502</v>
       </c>
       <c r="G151" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="H151" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="K151" t="s">
         <v>2472</v>
       </c>
       <c r="L151" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -45182,7 +45930,7 @@
         <v>840</v>
       </c>
       <c r="C152" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D152" t="s">
         <v>2010</v>
@@ -45194,16 +45942,16 @@
         <v>1502</v>
       </c>
       <c r="G152" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="H152" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="K152" t="s">
         <v>2475</v>
       </c>
       <c r="L152" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -45217,7 +45965,7 @@
         <v>840</v>
       </c>
       <c r="C153" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D153" t="s">
         <v>2010</v>
@@ -45229,16 +45977,16 @@
         <v>1502</v>
       </c>
       <c r="G153" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="H153" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="K153" t="s">
         <v>2477</v>
       </c>
       <c r="L153" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -45252,7 +46000,7 @@
         <v>840</v>
       </c>
       <c r="C154" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D154" t="s">
         <v>2010</v>
@@ -45264,16 +46012,16 @@
         <v>2011</v>
       </c>
       <c r="G154" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="H154" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="K154" t="s">
         <v>2465</v>
       </c>
       <c r="L154" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -45287,7 +46035,7 @@
         <v>840</v>
       </c>
       <c r="C155" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D155" t="s">
         <v>2010</v>
@@ -45299,16 +46047,16 @@
         <v>2011</v>
       </c>
       <c r="G155" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="H155" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="K155" t="s">
         <v>2463</v>
       </c>
       <c r="L155" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -45322,7 +46070,7 @@
         <v>840</v>
       </c>
       <c r="C156" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D156" t="s">
         <v>2010</v>
@@ -45334,16 +46082,16 @@
         <v>1502</v>
       </c>
       <c r="G156" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="H156" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="K156" t="s">
         <v>2465</v>
       </c>
       <c r="L156" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -45357,7 +46105,7 @@
         <v>840</v>
       </c>
       <c r="C157" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D157" t="s">
         <v>2010</v>
@@ -45369,10 +46117,10 @@
         <v>2023</v>
       </c>
       <c r="G157" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="H157" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="I157" t="s">
         <v>966</v>
@@ -45381,7 +46129,7 @@
         <v>2463</v>
       </c>
       <c r="L157" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -45395,7 +46143,7 @@
         <v>840</v>
       </c>
       <c r="C158" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D158" t="s">
         <v>2010</v>
@@ -45407,10 +46155,10 @@
         <v>1502</v>
       </c>
       <c r="G158" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="H158" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="I158" t="s">
         <v>964</v>
@@ -45419,7 +46167,7 @@
         <v>2463</v>
       </c>
       <c r="L158" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -45433,7 +46181,7 @@
         <v>840</v>
       </c>
       <c r="C159" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D159" t="s">
         <v>2010</v>
@@ -45445,16 +46193,16 @@
         <v>2023</v>
       </c>
       <c r="G159" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="H159" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="K159" t="s">
         <v>2470</v>
       </c>
       <c r="L159" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -45468,7 +46216,7 @@
         <v>840</v>
       </c>
       <c r="C160" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D160" t="s">
         <v>2010</v>
@@ -45480,16 +46228,16 @@
         <v>1502</v>
       </c>
       <c r="G160" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="H160" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="K160" t="s">
         <v>2485</v>
       </c>
       <c r="L160" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -45503,7 +46251,7 @@
         <v>840</v>
       </c>
       <c r="C161" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D161" t="s">
         <v>2010</v>
@@ -45515,16 +46263,16 @@
         <v>1502</v>
       </c>
       <c r="G161" t="s">
-        <v>2620</v>
+        <v>2617</v>
       </c>
       <c r="H161" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="K161" t="s">
         <v>1541</v>
       </c>
       <c r="L161" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -45538,7 +46286,7 @@
         <v>840</v>
       </c>
       <c r="C162" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D162" t="s">
         <v>2010</v>
@@ -45550,16 +46298,16 @@
         <v>2023</v>
       </c>
       <c r="G162" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="H162" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="K162" t="s">
         <v>1541</v>
       </c>
       <c r="L162" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -45573,7 +46321,7 @@
         <v>840</v>
       </c>
       <c r="C163" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D163" t="s">
         <v>2010</v>
@@ -45585,16 +46333,16 @@
         <v>2011</v>
       </c>
       <c r="G163" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="H163" t="s">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="K163" t="s">
         <v>1541</v>
       </c>
       <c r="L163" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -45608,7 +46356,7 @@
         <v>840</v>
       </c>
       <c r="C164" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D164" t="s">
         <v>2010</v>
@@ -45620,16 +46368,16 @@
         <v>1502</v>
       </c>
       <c r="G164" t="s">
-        <v>2626</v>
+        <v>2623</v>
       </c>
       <c r="H164" t="s">
-        <v>2627</v>
+        <v>2624</v>
       </c>
       <c r="K164" t="s">
         <v>2014</v>
       </c>
       <c r="L164" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -45643,7 +46391,7 @@
         <v>840</v>
       </c>
       <c r="C165" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D165" t="s">
         <v>2010</v>
@@ -45655,16 +46403,16 @@
         <v>1502</v>
       </c>
       <c r="G165" t="s">
-        <v>2628</v>
+        <v>2625</v>
       </c>
       <c r="H165" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="K165" t="s">
         <v>2472</v>
       </c>
       <c r="L165" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -45678,7 +46426,7 @@
         <v>840</v>
       </c>
       <c r="C166" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D166" t="s">
         <v>2010</v>
@@ -45690,16 +46438,16 @@
         <v>2011</v>
       </c>
       <c r="G166" t="s">
-        <v>2630</v>
+        <v>2627</v>
       </c>
       <c r="H166" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="K166" t="s">
         <v>2472</v>
       </c>
       <c r="L166" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -45713,7 +46461,7 @@
         <v>840</v>
       </c>
       <c r="C167" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D167" t="s">
         <v>2010</v>
@@ -45725,16 +46473,16 @@
         <v>1502</v>
       </c>
       <c r="G167" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="H167" t="s">
-        <v>2633</v>
+        <v>2630</v>
       </c>
       <c r="K167" t="s">
         <v>2477</v>
       </c>
       <c r="L167" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -45748,7 +46496,7 @@
         <v>840</v>
       </c>
       <c r="C168" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D168" t="s">
         <v>2010</v>
@@ -45760,16 +46508,16 @@
         <v>1502</v>
       </c>
       <c r="G168" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="H168" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="K168" t="s">
         <v>1541</v>
       </c>
       <c r="L168" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -45783,7 +46531,7 @@
         <v>840</v>
       </c>
       <c r="C169" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D169" t="s">
         <v>2010</v>
@@ -45795,16 +46543,16 @@
         <v>2011</v>
       </c>
       <c r="G169" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="H169" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="K169" t="s">
         <v>2463</v>
       </c>
       <c r="L169" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -45818,7 +46566,7 @@
         <v>840</v>
       </c>
       <c r="C170" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D170" t="s">
         <v>2010</v>
@@ -45830,16 +46578,16 @@
         <v>1502</v>
       </c>
       <c r="G170" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="H170" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="K170" t="s">
         <v>2465</v>
       </c>
       <c r="L170" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -45853,7 +46601,7 @@
         <v>840</v>
       </c>
       <c r="C171" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D171" t="s">
         <v>2010</v>
@@ -45865,10 +46613,10 @@
         <v>1502</v>
       </c>
       <c r="G171" t="s">
-        <v>2640</v>
+        <v>2637</v>
       </c>
       <c r="H171" t="s">
-        <v>2641</v>
+        <v>2638</v>
       </c>
       <c r="I171" t="s">
         <v>964</v>
@@ -45877,7 +46625,7 @@
         <v>2465</v>
       </c>
       <c r="L171" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -45891,7 +46639,7 @@
         <v>840</v>
       </c>
       <c r="C172" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D172" t="s">
         <v>2010</v>
@@ -45903,16 +46651,16 @@
         <v>2023</v>
       </c>
       <c r="G172" t="s">
-        <v>2642</v>
+        <v>2639</v>
       </c>
       <c r="H172" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="K172" t="s">
         <v>2014</v>
       </c>
       <c r="L172" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -45926,7 +46674,7 @@
         <v>840</v>
       </c>
       <c r="C173" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="D173" t="s">
         <v>2010</v>
@@ -45938,16 +46686,16 @@
         <v>2011</v>
       </c>
       <c r="G173" t="s">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="H173" t="s">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="K173" t="s">
         <v>1541</v>
       </c>
       <c r="L173" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="M173">
         <v>202</v>
@@ -50728,7 +51476,7 @@
         <v>840</v>
       </c>
       <c r="C156" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D156" t="s">
         <v>2515</v>
@@ -50757,7 +51505,7 @@
         <v>840</v>
       </c>
       <c r="C157" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D157" t="s">
         <v>2515</v>
@@ -51163,7 +51911,7 @@
         <v>840</v>
       </c>
       <c r="C171" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="D171" t="s">
         <v>2515</v>
@@ -51786,7 +52534,7 @@
         <v>292</v>
       </c>
       <c r="I23" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1">
@@ -53479,7 +54227,7 @@
         <v>449</v>
       </c>
       <c r="I100" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="24" customHeight="1">
@@ -53984,7 +54732,7 @@
         <v>482</v>
       </c>
       <c r="I123" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="24" customHeight="1">
@@ -54076,7 +54824,7 @@
         <v>292</v>
       </c>
       <c r="I127" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="24" customHeight="1">
@@ -54377,7 +55125,7 @@
         <v>292</v>
       </c>
       <c r="I141" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="24" customHeight="1">
@@ -54492,7 +55240,7 @@
         <v>518</v>
       </c>
       <c r="I146" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="24" customHeight="1">
@@ -57962,7 +58710,7 @@
         <v>811</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>812</v>
@@ -57971,10 +58719,10 @@
         <v>813</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>427</v>
@@ -58100,19 +58848,19 @@
         <v>837</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>838</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>427</v>
@@ -58218,7 +58966,7 @@
         <v>849</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>850</v>
@@ -58247,7 +58995,7 @@
         <v>849</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>850</v>
@@ -58276,7 +59024,7 @@
         <v>849</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2649</v>
+        <v>2646</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>850</v>
@@ -58305,16 +59053,16 @@
         <v>849</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2650</v>
+        <v>2647</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2665</v>
+        <v>2655</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2651</v>
+        <v>2648</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -58334,7 +59082,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2667</v>
+        <v>2657</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58363,7 +59111,7 @@
         <v>849</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2652</v>
+        <v>2649</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>850</v>
@@ -58392,7 +59140,7 @@
         <v>849</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>850</v>
@@ -58541,7 +59289,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2666</v>
+        <v>2656</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -58789,10 +59537,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2654</v>
+        <v>2651</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2655</v>
+        <v>2652</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58810,10 +59558,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2656</v>
+        <v>2653</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2664</v>
+        <v>2654</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -60297,18 +61045,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60330,18 +61078,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A67D2E-C255-4044-AD74-4EA092D00BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35EC53-D6C4-4B8B-9B76-4BDA60A1BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24909,457 +24909,457 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>거의 못 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹었어요</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>7자 (5~7자)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>option_label은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>띄어쓰기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>포함</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(5~7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>여야</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>폭이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>길면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>높이가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>혼자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>늘어난다</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7자를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적재하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬은 몇 가지였나요?
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 많이 먹었어요 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 많이). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>많이 먹었어요</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>7자 (5~7자)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>option_label은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>띄어쓰기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>포함</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(5~7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>여야</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>버튼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>폭이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고정이라</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>길면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>버튼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>높이가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>혼자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늘어난다</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>7자를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넘는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적재하면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
+    <t>배부르게 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26379,7 +26379,7 @@
         <v>2649</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>2651</v>
+        <v>2659</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>2650</v>
@@ -29414,7 +29414,7 @@
         <v>1301</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1189</v>
@@ -38744,10 +38744,10 @@
         <v>1993</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -57697,7 +57697,7 @@
         <v>849</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>850</v>
@@ -57726,7 +57726,7 @@
         <v>849</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>850</v>
@@ -57790,7 +57790,7 @@
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2654</v>
+        <v>2660</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>2643</v>
@@ -57813,7 +57813,7 @@
         <v>849</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>850</v>
@@ -58020,7 +58020,7 @@
         <v>887</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -58271,7 +58271,7 @@
         <v>2646</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58292,7 +58292,7 @@
         <v>2647</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -59776,18 +59776,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59809,18 +59809,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35EC53-D6C4-4B8B-9B76-4BDA60A1BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36ECD95-7E7F-4530-A8F5-5CE59F168781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8090" uniqueCount="2663">
   <si>
     <t>항목</t>
   </si>
@@ -24922,10 +24922,6 @@
   </si>
   <si>
     <t>거의 못 먹음</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -25349,17 +25345,25 @@
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배불리). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>배부르게 먹음</t>
+    <t>먹지 않음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>배불리 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -26379,7 +26383,7 @@
         <v>2649</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>2650</v>
@@ -29414,7 +29418,7 @@
         <v>1301</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1189</v>
@@ -38744,10 +38748,10 @@
         <v>1993</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2657</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2658</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -57790,7 +57794,7 @@
         <v>863</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>2643</v>
@@ -58249,8 +58253,8 @@
       <c r="D14" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>899</v>
+      <c r="E14" s="13" t="s">
+        <v>2660</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -58271,7 +58275,7 @@
         <v>2646</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2655</v>
+        <v>2661</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -58292,7 +58296,7 @@
         <v>2647</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -59776,18 +59780,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59809,18 +59813,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA5FC95-D328-4A34-B38C-9E2CAA01AC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0C1ED4-E5C4-4AEF-A4E4-2993C381802B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -14233,106 +14233,6 @@
   </si>
   <si>
     <r>
-      <t>56일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Carlito"/>
@@ -26851,32 +26751,342 @@
       </rPr>
       <t>행</t>
     </r>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>충분히 먹음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>56일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬을 얼마나 드셨나요? 답 충분히 먹음 · 조금 먹음 · 먹지 않음
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
-국물: {끼니}엔 국물을 얼마나 드셨나요?
+국물: {끼니}엔 국물을 얼마나 드셨나요? 답 먹지 않음 · 절반 이하 · 절반 넘게
 배부름: {끼니} 후 배부름은 어땠나요?
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>충분히 먹음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -27888,18 +28098,18 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="140">
+    <row r="20" spans="1:4" ht="154">
       <c r="A20" s="20" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>2635</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="20" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>2636</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>2660</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>2637</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -27918,16 +28128,16 @@
     </row>
     <row r="22" spans="1:4" ht="56">
       <c r="A22" s="20" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>2656</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>2657</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>2658</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>2659</v>
       </c>
     </row>
   </sheetData>
@@ -30667,7 +30877,7 @@
         <v>1193</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="K21" s="1">
         <v>21</v>
@@ -30945,7 +31155,7 @@
         <v>1288</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1177</v>
@@ -32030,7 +32240,7 @@
         <v>2542</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2543</v>
+        <v>2663</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1177</v>
@@ -32625,7 +32835,7 @@
         <v>1486</v>
       </c>
       <c r="H24" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -32645,7 +32855,7 @@
         <v>1486</v>
       </c>
       <c r="H25" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -32665,7 +32875,7 @@
         <v>1491</v>
       </c>
       <c r="H26" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -32688,7 +32898,7 @@
         <v>1493</v>
       </c>
       <c r="H27" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -32711,7 +32921,7 @@
         <v>1493</v>
       </c>
       <c r="H28" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -32734,7 +32944,7 @@
         <v>1493</v>
       </c>
       <c r="H29" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -32757,7 +32967,7 @@
         <v>1493</v>
       </c>
       <c r="H30" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -32780,7 +32990,7 @@
         <v>1493</v>
       </c>
       <c r="H31" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -32803,7 +33013,7 @@
         <v>1493</v>
       </c>
       <c r="H32" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -32826,7 +33036,7 @@
         <v>1493</v>
       </c>
       <c r="H33" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -32849,7 +33059,7 @@
         <v>1493</v>
       </c>
       <c r="H34" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -32872,7 +33082,7 @@
         <v>1486</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -32895,7 +33105,7 @@
         <v>1486</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -32918,7 +33128,7 @@
         <v>1486</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -32941,7 +33151,7 @@
         <v>1486</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -32964,7 +33174,7 @@
         <v>1486</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
     </row>
   </sheetData>
@@ -40135,10 +40345,10 @@
         <v>2527</v>
       </c>
       <c r="C39" s="16" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>2560</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>2561</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -40177,10 +40387,10 @@
         <v>1954</v>
       </c>
       <c r="C42" s="17" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D42" s="17" t="s">
         <v>2562</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>2563</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -40275,10 +40485,10 @@
         <v>1980</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2642</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2643</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -40286,13 +40496,13 @@
         <v>1981</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C50" s="16" t="s">
         <v>2564</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="D50" s="16" t="s">
         <v>2565</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>2566</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -45944,7 +46154,7 @@
         <v>839</v>
       </c>
       <c r="C145" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D145" t="s">
         <v>1994</v>
@@ -45956,10 +46166,10 @@
         <v>1488</v>
       </c>
       <c r="G145" t="s">
+        <v>2567</v>
+      </c>
+      <c r="H145" t="s">
         <v>2568</v>
-      </c>
-      <c r="H145" t="s">
-        <v>2569</v>
       </c>
       <c r="I145" t="s">
         <v>952</v>
@@ -45968,7 +46178,7 @@
         <v>2447</v>
       </c>
       <c r="L145" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -45982,7 +46192,7 @@
         <v>839</v>
       </c>
       <c r="C146" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D146" t="s">
         <v>1994</v>
@@ -45994,16 +46204,16 @@
         <v>2007</v>
       </c>
       <c r="G146" t="s">
+        <v>2570</v>
+      </c>
+      <c r="H146" t="s">
         <v>2571</v>
-      </c>
-      <c r="H146" t="s">
-        <v>2572</v>
       </c>
       <c r="K146" t="s">
         <v>2449</v>
       </c>
       <c r="L146" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -46017,7 +46227,7 @@
         <v>839</v>
       </c>
       <c r="C147" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D147" t="s">
         <v>1994</v>
@@ -46029,16 +46239,16 @@
         <v>2007</v>
       </c>
       <c r="G147" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H147" t="s">
         <v>2573</v>
-      </c>
-      <c r="H147" t="s">
-        <v>2574</v>
       </c>
       <c r="K147" t="s">
         <v>2451</v>
       </c>
       <c r="L147" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -46052,7 +46262,7 @@
         <v>839</v>
       </c>
       <c r="C148" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D148" t="s">
         <v>1994</v>
@@ -46064,16 +46274,16 @@
         <v>2007</v>
       </c>
       <c r="G148" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H148" t="s">
         <v>2575</v>
-      </c>
-      <c r="H148" t="s">
-        <v>2576</v>
       </c>
       <c r="K148" t="s">
         <v>1527</v>
       </c>
       <c r="L148" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -46087,7 +46297,7 @@
         <v>839</v>
       </c>
       <c r="C149" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D149" t="s">
         <v>1994</v>
@@ -46099,16 +46309,16 @@
         <v>1488</v>
       </c>
       <c r="G149" t="s">
+        <v>2576</v>
+      </c>
+      <c r="H149" t="s">
         <v>2577</v>
-      </c>
-      <c r="H149" t="s">
-        <v>2578</v>
       </c>
       <c r="K149" t="s">
         <v>2454</v>
       </c>
       <c r="L149" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -46122,7 +46332,7 @@
         <v>839</v>
       </c>
       <c r="C150" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D150" t="s">
         <v>1994</v>
@@ -46134,16 +46344,16 @@
         <v>1488</v>
       </c>
       <c r="G150" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H150" t="s">
         <v>2579</v>
-      </c>
-      <c r="H150" t="s">
-        <v>2580</v>
       </c>
       <c r="K150" t="s">
         <v>2456</v>
       </c>
       <c r="L150" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -46157,7 +46367,7 @@
         <v>839</v>
       </c>
       <c r="C151" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D151" t="s">
         <v>1994</v>
@@ -46169,16 +46379,16 @@
         <v>1488</v>
       </c>
       <c r="G151" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H151" t="s">
         <v>2581</v>
-      </c>
-      <c r="H151" t="s">
-        <v>2582</v>
       </c>
       <c r="K151" t="s">
         <v>2456</v>
       </c>
       <c r="L151" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -46192,7 +46402,7 @@
         <v>839</v>
       </c>
       <c r="C152" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D152" t="s">
         <v>1994</v>
@@ -46204,16 +46414,16 @@
         <v>1488</v>
       </c>
       <c r="G152" t="s">
+        <v>2582</v>
+      </c>
+      <c r="H152" t="s">
         <v>2583</v>
-      </c>
-      <c r="H152" t="s">
-        <v>2584</v>
       </c>
       <c r="K152" t="s">
         <v>2459</v>
       </c>
       <c r="L152" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -46227,7 +46437,7 @@
         <v>839</v>
       </c>
       <c r="C153" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D153" t="s">
         <v>1994</v>
@@ -46239,16 +46449,16 @@
         <v>1488</v>
       </c>
       <c r="G153" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H153" t="s">
         <v>2585</v>
-      </c>
-      <c r="H153" t="s">
-        <v>2586</v>
       </c>
       <c r="K153" t="s">
         <v>2461</v>
       </c>
       <c r="L153" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -46262,7 +46472,7 @@
         <v>839</v>
       </c>
       <c r="C154" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D154" t="s">
         <v>1994</v>
@@ -46274,16 +46484,16 @@
         <v>1995</v>
       </c>
       <c r="G154" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H154" t="s">
         <v>2587</v>
-      </c>
-      <c r="H154" t="s">
-        <v>2588</v>
       </c>
       <c r="K154" t="s">
         <v>2449</v>
       </c>
       <c r="L154" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -46297,7 +46507,7 @@
         <v>839</v>
       </c>
       <c r="C155" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D155" t="s">
         <v>1994</v>
@@ -46309,16 +46519,16 @@
         <v>1995</v>
       </c>
       <c r="G155" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H155" t="s">
         <v>2589</v>
-      </c>
-      <c r="H155" t="s">
-        <v>2590</v>
       </c>
       <c r="K155" t="s">
         <v>2447</v>
       </c>
       <c r="L155" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -46332,7 +46542,7 @@
         <v>839</v>
       </c>
       <c r="C156" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D156" t="s">
         <v>1994</v>
@@ -46344,16 +46554,16 @@
         <v>1488</v>
       </c>
       <c r="G156" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H156" t="s">
         <v>2591</v>
-      </c>
-      <c r="H156" t="s">
-        <v>2592</v>
       </c>
       <c r="K156" t="s">
         <v>2449</v>
       </c>
       <c r="L156" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -46367,7 +46577,7 @@
         <v>839</v>
       </c>
       <c r="C157" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D157" t="s">
         <v>1994</v>
@@ -46379,10 +46589,10 @@
         <v>2007</v>
       </c>
       <c r="G157" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H157" t="s">
         <v>2593</v>
-      </c>
-      <c r="H157" t="s">
-        <v>2594</v>
       </c>
       <c r="I157" t="s">
         <v>954</v>
@@ -46391,7 +46601,7 @@
         <v>2447</v>
       </c>
       <c r="L157" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -46405,7 +46615,7 @@
         <v>839</v>
       </c>
       <c r="C158" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D158" t="s">
         <v>1994</v>
@@ -46417,10 +46627,10 @@
         <v>1488</v>
       </c>
       <c r="G158" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H158" t="s">
         <v>2595</v>
-      </c>
-      <c r="H158" t="s">
-        <v>2596</v>
       </c>
       <c r="I158" t="s">
         <v>952</v>
@@ -46429,7 +46639,7 @@
         <v>2447</v>
       </c>
       <c r="L158" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -46443,7 +46653,7 @@
         <v>839</v>
       </c>
       <c r="C159" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D159" t="s">
         <v>1994</v>
@@ -46455,16 +46665,16 @@
         <v>2007</v>
       </c>
       <c r="G159" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H159" t="s">
         <v>2597</v>
-      </c>
-      <c r="H159" t="s">
-        <v>2598</v>
       </c>
       <c r="K159" t="s">
         <v>2454</v>
       </c>
       <c r="L159" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -46478,7 +46688,7 @@
         <v>839</v>
       </c>
       <c r="C160" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D160" t="s">
         <v>1994</v>
@@ -46490,16 +46700,16 @@
         <v>1488</v>
       </c>
       <c r="G160" t="s">
+        <v>2598</v>
+      </c>
+      <c r="H160" t="s">
         <v>2599</v>
-      </c>
-      <c r="H160" t="s">
-        <v>2600</v>
       </c>
       <c r="K160" t="s">
         <v>2469</v>
       </c>
       <c r="L160" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -46513,7 +46723,7 @@
         <v>839</v>
       </c>
       <c r="C161" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D161" t="s">
         <v>1994</v>
@@ -46525,16 +46735,16 @@
         <v>1488</v>
       </c>
       <c r="G161" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H161" t="s">
         <v>2601</v>
-      </c>
-      <c r="H161" t="s">
-        <v>2602</v>
       </c>
       <c r="K161" t="s">
         <v>1527</v>
       </c>
       <c r="L161" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -46548,7 +46758,7 @@
         <v>839</v>
       </c>
       <c r="C162" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D162" t="s">
         <v>1994</v>
@@ -46560,16 +46770,16 @@
         <v>2007</v>
       </c>
       <c r="G162" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H162" t="s">
         <v>2603</v>
-      </c>
-      <c r="H162" t="s">
-        <v>2604</v>
       </c>
       <c r="K162" t="s">
         <v>1527</v>
       </c>
       <c r="L162" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -46583,7 +46793,7 @@
         <v>839</v>
       </c>
       <c r="C163" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D163" t="s">
         <v>1994</v>
@@ -46595,16 +46805,16 @@
         <v>1995</v>
       </c>
       <c r="G163" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H163" t="s">
         <v>2605</v>
-      </c>
-      <c r="H163" t="s">
-        <v>2606</v>
       </c>
       <c r="K163" t="s">
         <v>1527</v>
       </c>
       <c r="L163" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -46618,7 +46828,7 @@
         <v>839</v>
       </c>
       <c r="C164" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D164" t="s">
         <v>1994</v>
@@ -46630,16 +46840,16 @@
         <v>1488</v>
       </c>
       <c r="G164" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H164" t="s">
         <v>2607</v>
-      </c>
-      <c r="H164" t="s">
-        <v>2608</v>
       </c>
       <c r="K164" t="s">
         <v>1998</v>
       </c>
       <c r="L164" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -46653,7 +46863,7 @@
         <v>839</v>
       </c>
       <c r="C165" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D165" t="s">
         <v>1994</v>
@@ -46665,16 +46875,16 @@
         <v>1488</v>
       </c>
       <c r="G165" t="s">
+        <v>2608</v>
+      </c>
+      <c r="H165" t="s">
         <v>2609</v>
-      </c>
-      <c r="H165" t="s">
-        <v>2610</v>
       </c>
       <c r="K165" t="s">
         <v>2456</v>
       </c>
       <c r="L165" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -46688,7 +46898,7 @@
         <v>839</v>
       </c>
       <c r="C166" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D166" t="s">
         <v>1994</v>
@@ -46700,16 +46910,16 @@
         <v>1995</v>
       </c>
       <c r="G166" t="s">
+        <v>2610</v>
+      </c>
+      <c r="H166" t="s">
         <v>2611</v>
-      </c>
-      <c r="H166" t="s">
-        <v>2612</v>
       </c>
       <c r="K166" t="s">
         <v>2456</v>
       </c>
       <c r="L166" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -46723,7 +46933,7 @@
         <v>839</v>
       </c>
       <c r="C167" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D167" t="s">
         <v>1994</v>
@@ -46735,16 +46945,16 @@
         <v>1488</v>
       </c>
       <c r="G167" t="s">
+        <v>2612</v>
+      </c>
+      <c r="H167" t="s">
         <v>2613</v>
-      </c>
-      <c r="H167" t="s">
-        <v>2614</v>
       </c>
       <c r="K167" t="s">
         <v>2461</v>
       </c>
       <c r="L167" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -46758,7 +46968,7 @@
         <v>839</v>
       </c>
       <c r="C168" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D168" t="s">
         <v>1994</v>
@@ -46770,16 +46980,16 @@
         <v>1488</v>
       </c>
       <c r="G168" t="s">
+        <v>2614</v>
+      </c>
+      <c r="H168" t="s">
         <v>2615</v>
-      </c>
-      <c r="H168" t="s">
-        <v>2616</v>
       </c>
       <c r="K168" t="s">
         <v>1527</v>
       </c>
       <c r="L168" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -46793,7 +47003,7 @@
         <v>839</v>
       </c>
       <c r="C169" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D169" t="s">
         <v>1994</v>
@@ -46805,16 +47015,16 @@
         <v>1995</v>
       </c>
       <c r="G169" t="s">
+        <v>2616</v>
+      </c>
+      <c r="H169" t="s">
         <v>2617</v>
-      </c>
-      <c r="H169" t="s">
-        <v>2618</v>
       </c>
       <c r="K169" t="s">
         <v>2447</v>
       </c>
       <c r="L169" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -46828,7 +47038,7 @@
         <v>839</v>
       </c>
       <c r="C170" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D170" t="s">
         <v>1994</v>
@@ -46840,16 +47050,16 @@
         <v>1488</v>
       </c>
       <c r="G170" t="s">
+        <v>2618</v>
+      </c>
+      <c r="H170" t="s">
         <v>2619</v>
-      </c>
-      <c r="H170" t="s">
-        <v>2620</v>
       </c>
       <c r="K170" t="s">
         <v>2449</v>
       </c>
       <c r="L170" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -46863,7 +47073,7 @@
         <v>839</v>
       </c>
       <c r="C171" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D171" t="s">
         <v>1994</v>
@@ -46875,10 +47085,10 @@
         <v>1488</v>
       </c>
       <c r="G171" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H171" t="s">
         <v>2621</v>
-      </c>
-      <c r="H171" t="s">
-        <v>2622</v>
       </c>
       <c r="I171" t="s">
         <v>952</v>
@@ -46887,7 +47097,7 @@
         <v>2449</v>
       </c>
       <c r="L171" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -46901,7 +47111,7 @@
         <v>839</v>
       </c>
       <c r="C172" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D172" t="s">
         <v>1994</v>
@@ -46913,16 +47123,16 @@
         <v>2007</v>
       </c>
       <c r="G172" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H172" t="s">
         <v>2623</v>
-      </c>
-      <c r="H172" t="s">
-        <v>2624</v>
       </c>
       <c r="K172" t="s">
         <v>1998</v>
       </c>
       <c r="L172" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -46936,7 +47146,7 @@
         <v>839</v>
       </c>
       <c r="C173" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="D173" t="s">
         <v>1994</v>
@@ -46948,16 +47158,16 @@
         <v>1995</v>
       </c>
       <c r="G173" t="s">
+        <v>2624</v>
+      </c>
+      <c r="H173" t="s">
         <v>2625</v>
-      </c>
-      <c r="H173" t="s">
-        <v>2626</v>
       </c>
       <c r="K173" t="s">
         <v>1527</v>
       </c>
       <c r="L173" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="M173">
         <v>202</v>
@@ -51738,7 +51948,7 @@
         <v>839</v>
       </c>
       <c r="C156" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D156" t="s">
         <v>2499</v>
@@ -51767,7 +51977,7 @@
         <v>839</v>
       </c>
       <c r="C157" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D157" t="s">
         <v>2499</v>
@@ -52173,7 +52383,7 @@
         <v>839</v>
       </c>
       <c r="C171" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="D171" t="s">
         <v>2499</v>
@@ -58935,7 +59145,7 @@
         <v>802</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>803</v>
@@ -59202,7 +59412,7 @@
         <v>842</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>843</v>
@@ -59228,16 +59438,16 @@
         <v>847</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>848</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="I3" s="1">
         <v>3</v>
@@ -59257,7 +59467,7 @@
         <v>847</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>848</v>
@@ -59286,7 +59496,7 @@
         <v>847</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>848</v>
@@ -59315,16 +59525,16 @@
         <v>847</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>859</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -59344,7 +59554,7 @@
         <v>847</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>848</v>
@@ -59373,7 +59583,7 @@
         <v>847</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>848</v>
@@ -59402,7 +59612,7 @@
         <v>847</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>848</v>
@@ -59431,16 +59641,16 @@
         <v>874</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="F10" t="s">
         <v>875</v>
       </c>
       <c r="G10" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>2651</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>2652</v>
       </c>
     </row>
   </sheetData>
@@ -59551,7 +59761,7 @@
         <v>880</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -59574,7 +59784,7 @@
         <v>881</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -59597,7 +59807,7 @@
         <v>882</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -59620,7 +59830,7 @@
         <v>883</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="F7" s="1">
         <v>-1</v>
@@ -59711,8 +59921,8 @@
       <c r="D11" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>889</v>
+      <c r="E11" s="13" t="s">
+        <v>2644</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -59781,7 +59991,7 @@
         <v>883</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -59799,10 +60009,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -59820,10 +60030,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -60051,7 +60261,7 @@
         <v>905</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -60085,7 +60295,7 @@
         <v>908</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
     </row>
   </sheetData>
@@ -61307,18 +61517,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61340,18 +61550,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED1096B-27FC-4BA8-9DB2-400C9AD2B375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41202F-5DD0-493D-BDA6-41618649F4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8102" uniqueCount="2673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8106" uniqueCount="2684">
   <si>
     <t>항목</t>
   </si>
@@ -29176,6 +29176,1953 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>선택</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-Q-04</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTRO</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 끼니 규칙 축은 목표 축이 되지 않아 나올 수 없고 「주말도 아침 챙기기」와 겹침</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 식사 시각 질문은 아침에만 묻고 이 문구는 저녁 전용·식후 불가라 나올 수 없음. 식후 가능으로 바꿀지 정한 뒤 되살린다</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKEND</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이유로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>월요일에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전용이고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>불가라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>옮김</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>겹침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>되지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0088 E·F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, DIET-P-0043·0157 source_status · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0264 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
   </si>
 </sst>
@@ -29294,7 +31241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -29352,6 +31299,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -30036,7 +31986,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -30241,6 +32191,20 @@
       </c>
       <c r="D23" s="20" t="s">
         <v>2672</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="98">
+      <c r="A24" s="20" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>2683</v>
       </c>
     </row>
   </sheetData>
@@ -44147,8 +46111,8 @@
       <c r="B36" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1990</v>
+      <c r="C36" s="21" t="s">
+        <v>2675</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1991</v>
@@ -44172,8 +46136,8 @@
       <c r="K36" s="8" t="s">
         <v>1995</v>
       </c>
-      <c r="L36" s="8" t="s">
-        <v>1996</v>
+      <c r="L36" s="21" t="s">
+        <v>2676</v>
       </c>
       <c r="M36" s="8">
         <v>36</v>
@@ -45295,11 +47259,11 @@
       <c r="D66" s="8" t="s">
         <v>1991</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>837</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>2004</v>
+      <c r="E66" s="21" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>2674</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>2199</v>
@@ -46513,8 +48477,8 @@
       <c r="B98" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>1990</v>
+      <c r="C98" s="21" t="s">
+        <v>2675</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1991</v>
@@ -46536,8 +48500,8 @@
       <c r="K98" s="8" t="s">
         <v>2051</v>
       </c>
-      <c r="L98" s="8" t="s">
-        <v>1996</v>
+      <c r="L98" s="21" t="s">
+        <v>2677</v>
       </c>
       <c r="M98" s="8">
         <v>123</v>
@@ -54441,14 +56405,14 @@
       <c r="B169" t="s">
         <v>838</v>
       </c>
-      <c r="C169" t="s">
-        <v>2486</v>
+      <c r="C169" s="12" t="s">
+        <v>2679</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
       </c>
-      <c r="E169" t="s">
-        <v>326</v>
+      <c r="E169" s="12" t="s">
+        <v>2678</v>
       </c>
       <c r="F169" t="s">
         <v>326</v>
@@ -63634,18 +65598,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -63667,18 +65631,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41202F-5DD0-493D-BDA6-41618649F4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D83BE-DC1F-4D17-A145-17307EF39B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8106" uniqueCount="2684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="2703">
   <si>
     <t>항목</t>
   </si>
@@ -9737,10 +9737,6 @@
   </si>
   <si>
     <t>PRE_MIDNIGHT</t>
-  </si>
-  <si>
-    <t>질문 9, 선택지 27, 목표문구 172, 노출조건 172, 질환규칙 14, 상병코드조건 61, 설정 68</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>동일 축의 축 목표가 완료되지 않은 채 끝난 것 연속 2건</t>
@@ -24422,383 +24418,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>17~24시와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> READY</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이면서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> after_dinner_eligible=true</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 확정된 축 목표가 3건 미만이면 판단하지 않음</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -31123,6 +30742,3801 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>시트</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0269</t>
+  </si>
+  <si>
+    <r>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>허기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>소화가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>편한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10-07 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0270</t>
+  </si>
+  <si>
+    <r>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>속을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달래며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부족한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신하지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않아요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0271</t>
+  </si>
+  <si>
+    <r>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침거리를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둬요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17~24시와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> READY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이면서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> after_dinner_eligible=true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 9, 선택지 27, 목표문구 175, 노출조건 175, 질환규칙 14, 상병코드조건 61, 설정 68</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>V-52</t>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이때는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(after_dinner_eligible=true)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>했는데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는데도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-05 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-52 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
     </r>
   </si>
 </sst>
@@ -31241,7 +34655,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -31302,6 +34716,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -31611,7 +35033,7 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D51" totalsRowShown="0" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="DietValidationRules" displayName="DietValidationRules" ref="A1:D52" totalsRowShown="0" dataDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1600-000001000000}" name="규칙 ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1600-000002000000}" name="대상" dataDxfId="2"/>
@@ -31637,7 +35059,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M173" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M176" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="phrase_version"/>
@@ -31658,8 +35080,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K173" totalsRowShown="0">
-  <autoFilter ref="A1:K173" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K176" totalsRowShown="0">
+  <autoFilter ref="A1:K176" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
     <filterColumn colId="6">
       <filters>
         <filter val="TRUE"/>
@@ -31986,7 +35408,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -32003,10 +35425,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D1" t="s">
         <v>2506</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2507</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
@@ -32078,7 +35500,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2497</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -32115,96 +35537,110 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B19" t="s">
         <v>2510</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>2511</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>2512</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2513</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="154">
       <c r="A20" s="20" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>2623</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="20" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>2624</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>2653</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>2625</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>2514</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>2515</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>2654</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>2516</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="56">
       <c r="A22" s="20" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>2644</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="20" t="s">
         <v>2645</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>2646</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>2647</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="42">
       <c r="A23" s="20" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>2669</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="D23" s="20" t="s">
         <v>2670</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>2671</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>2672</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="98">
       <c r="A24" s="20" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>2680</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="D24" s="20" t="s">
         <v>2681</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>2682</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>2683</v>
+    </row>
+    <row r="25" spans="1:4" ht="56">
+      <c r="A25" s="20" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -34603,7 +38039,7 @@
         <v>1204</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>1176</v>
@@ -34632,7 +38068,7 @@
         <v>1208</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>1176</v>
@@ -34845,7 +38281,7 @@
         <v>1238</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>1176</v>
@@ -34944,7 +38380,7 @@
         <v>1192</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K21" s="1">
         <v>21</v>
@@ -35222,7 +38658,7 @@
         <v>1286</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>1176</v>
@@ -36232,13 +39668,13 @@
         <v>1423</v>
       </c>
       <c r="B66" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C66" t="s">
         <v>2529</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>2530</v>
-      </c>
-      <c r="D66" t="s">
-        <v>2531</v>
       </c>
       <c r="E66" t="s">
         <v>1405</v>
@@ -36247,7 +39683,7 @@
         <v>1192</v>
       </c>
       <c r="J66" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -36255,13 +39691,13 @@
         <v>1425</v>
       </c>
       <c r="B67" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C67" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D67" t="s">
         <v>2533</v>
-      </c>
-      <c r="D67" t="s">
-        <v>2534</v>
       </c>
       <c r="E67" t="s">
         <v>1405</v>
@@ -36270,21 +39706,21 @@
         <v>1192</v>
       </c>
       <c r="J67" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="12" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>485</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1176</v>
@@ -36298,16 +39734,16 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>485</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1176</v>
@@ -36463,7 +39899,7 @@
         <v>1435</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
@@ -36902,7 +40338,7 @@
         <v>1483</v>
       </c>
       <c r="H24" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -36922,7 +40358,7 @@
         <v>1483</v>
       </c>
       <c r="H25" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -36942,7 +40378,7 @@
         <v>1488</v>
       </c>
       <c r="H26" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -36965,7 +40401,7 @@
         <v>1490</v>
       </c>
       <c r="H27" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -36988,7 +40424,7 @@
         <v>1490</v>
       </c>
       <c r="H28" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -37011,7 +40447,7 @@
         <v>1490</v>
       </c>
       <c r="H29" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -37034,7 +40470,7 @@
         <v>1490</v>
       </c>
       <c r="H30" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -37057,7 +40493,7 @@
         <v>1490</v>
       </c>
       <c r="H31" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -37080,7 +40516,7 @@
         <v>1490</v>
       </c>
       <c r="H32" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -37103,7 +40539,7 @@
         <v>1490</v>
       </c>
       <c r="H33" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -37126,7 +40562,7 @@
         <v>1490</v>
       </c>
       <c r="H34" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -37134,7 +40570,7 @@
         <v>1203</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>1434</v>
@@ -37149,7 +40585,7 @@
         <v>1483</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -37157,7 +40593,7 @@
         <v>1203</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>1427</v>
@@ -37172,7 +40608,7 @@
         <v>1483</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -37180,7 +40616,7 @@
         <v>1203</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1427</v>
@@ -37195,7 +40631,7 @@
         <v>1483</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -37203,7 +40639,7 @@
         <v>1207</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>1434</v>
@@ -37218,15 +40654,15 @@
         <v>1483</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="12" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>1441</v>
@@ -37241,7 +40677,7 @@
         <v>1483</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
   </sheetData>
@@ -44409,13 +47845,13 @@
         <v>1941</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C39" s="16" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>2550</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>2551</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -44454,10 +47890,10 @@
         <v>1951</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28">
@@ -44552,10 +47988,10 @@
         <v>1977</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>2630</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2631</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="28">
@@ -44563,27 +47999,41 @@
         <v>1978</v>
       </c>
       <c r="B50" s="16" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C50" s="16" t="s">
         <v>2552</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="D50" s="16" t="s">
         <v>2553</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>2554</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28">
       <c r="A51" s="17" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>2665</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="D51" s="17" t="s">
         <v>2666</v>
       </c>
-      <c r="C51" s="17" t="s">
-        <v>2667</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>2668</v>
+    </row>
+    <row r="52" spans="1:4" ht="42">
+      <c r="A52" s="17" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>2698</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -44770,7 +48220,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -46112,7 +49562,7 @@
         <v>838</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1991</v>
@@ -46137,7 +49587,7 @@
         <v>1995</v>
       </c>
       <c r="L36" s="21" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="M36" s="8">
         <v>36</v>
@@ -47260,10 +50710,10 @@
         <v>1991</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="G66" s="11" t="s">
         <v>2199</v>
@@ -48478,7 +51928,7 @@
         <v>838</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1991</v>
@@ -48501,7 +51951,7 @@
         <v>2051</v>
       </c>
       <c r="L98" s="21" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="M98" s="8">
         <v>123</v>
@@ -50235,7 +53685,7 @@
         <v>838</v>
       </c>
       <c r="C145" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D145" t="s">
         <v>1991</v>
@@ -50247,10 +53697,10 @@
         <v>1485</v>
       </c>
       <c r="G145" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H145" t="s">
         <v>2556</v>
-      </c>
-      <c r="H145" t="s">
-        <v>2557</v>
       </c>
       <c r="I145" t="s">
         <v>951</v>
@@ -50259,7 +53709,7 @@
         <v>2444</v>
       </c>
       <c r="L145" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M145">
         <v>173</v>
@@ -50273,7 +53723,7 @@
         <v>838</v>
       </c>
       <c r="C146" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D146" t="s">
         <v>1991</v>
@@ -50285,16 +53735,16 @@
         <v>2004</v>
       </c>
       <c r="G146" t="s">
+        <v>2558</v>
+      </c>
+      <c r="H146" t="s">
         <v>2559</v>
-      </c>
-      <c r="H146" t="s">
-        <v>2560</v>
       </c>
       <c r="K146" t="s">
         <v>2446</v>
       </c>
       <c r="L146" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M146">
         <v>174</v>
@@ -50308,7 +53758,7 @@
         <v>838</v>
       </c>
       <c r="C147" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D147" t="s">
         <v>1991</v>
@@ -50320,16 +53770,16 @@
         <v>2004</v>
       </c>
       <c r="G147" t="s">
+        <v>2560</v>
+      </c>
+      <c r="H147" t="s">
         <v>2561</v>
-      </c>
-      <c r="H147" t="s">
-        <v>2562</v>
       </c>
       <c r="K147" t="s">
         <v>2448</v>
       </c>
       <c r="L147" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M147">
         <v>175</v>
@@ -50343,7 +53793,7 @@
         <v>838</v>
       </c>
       <c r="C148" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D148" t="s">
         <v>1991</v>
@@ -50355,16 +53805,16 @@
         <v>2004</v>
       </c>
       <c r="G148" t="s">
+        <v>2562</v>
+      </c>
+      <c r="H148" t="s">
         <v>2563</v>
-      </c>
-      <c r="H148" t="s">
-        <v>2564</v>
       </c>
       <c r="K148" t="s">
         <v>1524</v>
       </c>
       <c r="L148" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M148">
         <v>176</v>
@@ -50378,7 +53828,7 @@
         <v>838</v>
       </c>
       <c r="C149" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D149" t="s">
         <v>1991</v>
@@ -50390,16 +53840,16 @@
         <v>1485</v>
       </c>
       <c r="G149" t="s">
+        <v>2564</v>
+      </c>
+      <c r="H149" t="s">
         <v>2565</v>
-      </c>
-      <c r="H149" t="s">
-        <v>2566</v>
       </c>
       <c r="K149" t="s">
         <v>2451</v>
       </c>
       <c r="L149" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M149">
         <v>177</v>
@@ -50413,7 +53863,7 @@
         <v>838</v>
       </c>
       <c r="C150" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D150" t="s">
         <v>1991</v>
@@ -50425,16 +53875,16 @@
         <v>1485</v>
       </c>
       <c r="G150" t="s">
+        <v>2566</v>
+      </c>
+      <c r="H150" t="s">
         <v>2567</v>
-      </c>
-      <c r="H150" t="s">
-        <v>2568</v>
       </c>
       <c r="K150" t="s">
         <v>2453</v>
       </c>
       <c r="L150" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M150">
         <v>178</v>
@@ -50448,7 +53898,7 @@
         <v>838</v>
       </c>
       <c r="C151" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D151" t="s">
         <v>1991</v>
@@ -50460,16 +53910,16 @@
         <v>1485</v>
       </c>
       <c r="G151" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H151" t="s">
         <v>2569</v>
-      </c>
-      <c r="H151" t="s">
-        <v>2570</v>
       </c>
       <c r="K151" t="s">
         <v>2453</v>
       </c>
       <c r="L151" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -50483,7 +53933,7 @@
         <v>838</v>
       </c>
       <c r="C152" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D152" t="s">
         <v>1991</v>
@@ -50495,16 +53945,16 @@
         <v>1485</v>
       </c>
       <c r="G152" t="s">
+        <v>2570</v>
+      </c>
+      <c r="H152" t="s">
         <v>2571</v>
-      </c>
-      <c r="H152" t="s">
-        <v>2572</v>
       </c>
       <c r="K152" t="s">
         <v>2456</v>
       </c>
       <c r="L152" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M152">
         <v>180</v>
@@ -50518,7 +53968,7 @@
         <v>838</v>
       </c>
       <c r="C153" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D153" t="s">
         <v>1991</v>
@@ -50530,16 +53980,16 @@
         <v>1485</v>
       </c>
       <c r="G153" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H153" t="s">
         <v>2573</v>
-      </c>
-      <c r="H153" t="s">
-        <v>2574</v>
       </c>
       <c r="K153" t="s">
         <v>2458</v>
       </c>
       <c r="L153" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M153">
         <v>181</v>
@@ -50553,7 +54003,7 @@
         <v>838</v>
       </c>
       <c r="C154" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D154" t="s">
         <v>1991</v>
@@ -50565,16 +54015,16 @@
         <v>1992</v>
       </c>
       <c r="G154" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H154" t="s">
         <v>2575</v>
-      </c>
-      <c r="H154" t="s">
-        <v>2576</v>
       </c>
       <c r="K154" t="s">
         <v>2446</v>
       </c>
       <c r="L154" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M154">
         <v>182</v>
@@ -50588,7 +54038,7 @@
         <v>838</v>
       </c>
       <c r="C155" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D155" t="s">
         <v>1991</v>
@@ -50600,16 +54050,16 @@
         <v>1992</v>
       </c>
       <c r="G155" t="s">
+        <v>2576</v>
+      </c>
+      <c r="H155" t="s">
         <v>2577</v>
-      </c>
-      <c r="H155" t="s">
-        <v>2578</v>
       </c>
       <c r="K155" t="s">
         <v>2444</v>
       </c>
       <c r="L155" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M155">
         <v>183</v>
@@ -50623,7 +54073,7 @@
         <v>838</v>
       </c>
       <c r="C156" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D156" t="s">
         <v>1991</v>
@@ -50635,16 +54085,16 @@
         <v>1485</v>
       </c>
       <c r="G156" t="s">
+        <v>2578</v>
+      </c>
+      <c r="H156" t="s">
         <v>2579</v>
-      </c>
-      <c r="H156" t="s">
-        <v>2580</v>
       </c>
       <c r="K156" t="s">
         <v>2446</v>
       </c>
       <c r="L156" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M156">
         <v>184</v>
@@ -50658,7 +54108,7 @@
         <v>838</v>
       </c>
       <c r="C157" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D157" t="s">
         <v>1991</v>
@@ -50670,10 +54120,10 @@
         <v>2004</v>
       </c>
       <c r="G157" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H157" t="s">
         <v>2581</v>
-      </c>
-      <c r="H157" t="s">
-        <v>2582</v>
       </c>
       <c r="I157" t="s">
         <v>953</v>
@@ -50682,7 +54132,7 @@
         <v>2444</v>
       </c>
       <c r="L157" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M157">
         <v>185</v>
@@ -50696,7 +54146,7 @@
         <v>838</v>
       </c>
       <c r="C158" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D158" t="s">
         <v>1991</v>
@@ -50708,10 +54158,10 @@
         <v>1485</v>
       </c>
       <c r="G158" t="s">
+        <v>2582</v>
+      </c>
+      <c r="H158" t="s">
         <v>2583</v>
-      </c>
-      <c r="H158" t="s">
-        <v>2584</v>
       </c>
       <c r="I158" t="s">
         <v>951</v>
@@ -50720,7 +54170,7 @@
         <v>2444</v>
       </c>
       <c r="L158" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M158">
         <v>186</v>
@@ -50734,7 +54184,7 @@
         <v>838</v>
       </c>
       <c r="C159" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D159" t="s">
         <v>1991</v>
@@ -50746,16 +54196,16 @@
         <v>2004</v>
       </c>
       <c r="G159" t="s">
+        <v>2584</v>
+      </c>
+      <c r="H159" t="s">
         <v>2585</v>
-      </c>
-      <c r="H159" t="s">
-        <v>2586</v>
       </c>
       <c r="K159" t="s">
         <v>2451</v>
       </c>
       <c r="L159" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M159">
         <v>187</v>
@@ -50769,7 +54219,7 @@
         <v>838</v>
       </c>
       <c r="C160" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D160" t="s">
         <v>1991</v>
@@ -50781,16 +54231,16 @@
         <v>1485</v>
       </c>
       <c r="G160" t="s">
+        <v>2586</v>
+      </c>
+      <c r="H160" t="s">
         <v>2587</v>
-      </c>
-      <c r="H160" t="s">
-        <v>2588</v>
       </c>
       <c r="K160" t="s">
         <v>2466</v>
       </c>
       <c r="L160" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M160">
         <v>188</v>
@@ -50804,7 +54254,7 @@
         <v>838</v>
       </c>
       <c r="C161" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D161" t="s">
         <v>1991</v>
@@ -50816,16 +54266,16 @@
         <v>1485</v>
       </c>
       <c r="G161" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H161" t="s">
         <v>2589</v>
-      </c>
-      <c r="H161" t="s">
-        <v>2590</v>
       </c>
       <c r="K161" t="s">
         <v>1524</v>
       </c>
       <c r="L161" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M161">
         <v>189</v>
@@ -50839,7 +54289,7 @@
         <v>838</v>
       </c>
       <c r="C162" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D162" t="s">
         <v>1991</v>
@@ -50851,16 +54301,16 @@
         <v>2004</v>
       </c>
       <c r="G162" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H162" t="s">
         <v>2591</v>
-      </c>
-      <c r="H162" t="s">
-        <v>2592</v>
       </c>
       <c r="K162" t="s">
         <v>1524</v>
       </c>
       <c r="L162" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M162">
         <v>190</v>
@@ -50874,7 +54324,7 @@
         <v>838</v>
       </c>
       <c r="C163" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D163" t="s">
         <v>1991</v>
@@ -50886,16 +54336,16 @@
         <v>1992</v>
       </c>
       <c r="G163" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H163" t="s">
         <v>2593</v>
-      </c>
-      <c r="H163" t="s">
-        <v>2594</v>
       </c>
       <c r="K163" t="s">
         <v>1524</v>
       </c>
       <c r="L163" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M163">
         <v>191</v>
@@ -50909,7 +54359,7 @@
         <v>838</v>
       </c>
       <c r="C164" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D164" t="s">
         <v>1991</v>
@@ -50921,16 +54371,16 @@
         <v>1485</v>
       </c>
       <c r="G164" t="s">
+        <v>2594</v>
+      </c>
+      <c r="H164" t="s">
         <v>2595</v>
-      </c>
-      <c r="H164" t="s">
-        <v>2596</v>
       </c>
       <c r="K164" t="s">
         <v>1995</v>
       </c>
       <c r="L164" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M164">
         <v>192</v>
@@ -50944,7 +54394,7 @@
         <v>838</v>
       </c>
       <c r="C165" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D165" t="s">
         <v>1991</v>
@@ -50956,16 +54406,16 @@
         <v>1485</v>
       </c>
       <c r="G165" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H165" t="s">
         <v>2597</v>
-      </c>
-      <c r="H165" t="s">
-        <v>2598</v>
       </c>
       <c r="K165" t="s">
         <v>2453</v>
       </c>
       <c r="L165" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M165">
         <v>193</v>
@@ -50979,7 +54429,7 @@
         <v>838</v>
       </c>
       <c r="C166" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D166" t="s">
         <v>1991</v>
@@ -50991,16 +54441,16 @@
         <v>1992</v>
       </c>
       <c r="G166" t="s">
+        <v>2598</v>
+      </c>
+      <c r="H166" t="s">
         <v>2599</v>
-      </c>
-      <c r="H166" t="s">
-        <v>2600</v>
       </c>
       <c r="K166" t="s">
         <v>2453</v>
       </c>
       <c r="L166" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M166">
         <v>194</v>
@@ -51014,7 +54464,7 @@
         <v>838</v>
       </c>
       <c r="C167" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D167" t="s">
         <v>1991</v>
@@ -51026,16 +54476,16 @@
         <v>1485</v>
       </c>
       <c r="G167" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H167" t="s">
         <v>2601</v>
-      </c>
-      <c r="H167" t="s">
-        <v>2602</v>
       </c>
       <c r="K167" t="s">
         <v>2458</v>
       </c>
       <c r="L167" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M167">
         <v>196</v>
@@ -51049,7 +54499,7 @@
         <v>838</v>
       </c>
       <c r="C168" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D168" t="s">
         <v>1991</v>
@@ -51061,16 +54511,16 @@
         <v>1485</v>
       </c>
       <c r="G168" t="s">
+        <v>2602</v>
+      </c>
+      <c r="H168" t="s">
         <v>2603</v>
-      </c>
-      <c r="H168" t="s">
-        <v>2604</v>
       </c>
       <c r="K168" t="s">
         <v>1524</v>
       </c>
       <c r="L168" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -51084,7 +54534,7 @@
         <v>838</v>
       </c>
       <c r="C169" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D169" t="s">
         <v>1991</v>
@@ -51096,16 +54546,16 @@
         <v>1992</v>
       </c>
       <c r="G169" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H169" t="s">
         <v>2605</v>
-      </c>
-      <c r="H169" t="s">
-        <v>2606</v>
       </c>
       <c r="K169" t="s">
         <v>2444</v>
       </c>
       <c r="L169" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M169">
         <v>198</v>
@@ -51119,7 +54569,7 @@
         <v>838</v>
       </c>
       <c r="C170" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D170" t="s">
         <v>1991</v>
@@ -51131,16 +54581,16 @@
         <v>1485</v>
       </c>
       <c r="G170" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H170" t="s">
         <v>2607</v>
-      </c>
-      <c r="H170" t="s">
-        <v>2608</v>
       </c>
       <c r="K170" t="s">
         <v>2446</v>
       </c>
       <c r="L170" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M170">
         <v>199</v>
@@ -51154,7 +54604,7 @@
         <v>838</v>
       </c>
       <c r="C171" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D171" t="s">
         <v>1991</v>
@@ -51166,10 +54616,10 @@
         <v>1485</v>
       </c>
       <c r="G171" t="s">
+        <v>2608</v>
+      </c>
+      <c r="H171" t="s">
         <v>2609</v>
-      </c>
-      <c r="H171" t="s">
-        <v>2610</v>
       </c>
       <c r="I171" t="s">
         <v>951</v>
@@ -51178,7 +54628,7 @@
         <v>2446</v>
       </c>
       <c r="L171" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -51192,7 +54642,7 @@
         <v>838</v>
       </c>
       <c r="C172" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D172" t="s">
         <v>1991</v>
@@ -51204,16 +54654,16 @@
         <v>2004</v>
       </c>
       <c r="G172" t="s">
+        <v>2610</v>
+      </c>
+      <c r="H172" t="s">
         <v>2611</v>
-      </c>
-      <c r="H172" t="s">
-        <v>2612</v>
       </c>
       <c r="K172" t="s">
         <v>1995</v>
       </c>
       <c r="L172" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M172">
         <v>201</v>
@@ -51227,7 +54677,7 @@
         <v>838</v>
       </c>
       <c r="C173" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="D173" t="s">
         <v>1991</v>
@@ -51239,19 +54689,124 @@
         <v>1992</v>
       </c>
       <c r="G173" t="s">
+        <v>2612</v>
+      </c>
+      <c r="H173" t="s">
         <v>2613</v>
-      </c>
-      <c r="H173" t="s">
-        <v>2614</v>
       </c>
       <c r="K173" t="s">
         <v>1524</v>
       </c>
       <c r="L173" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="M173">
         <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="12" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12" t="s">
+        <v>2683</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>2684</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J174" s="12"/>
+      <c r="K174" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L174" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M174" s="12">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="12" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12" t="s">
+        <v>2688</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>2689</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J175" s="12"/>
+      <c r="K175" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L175" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M175" s="12">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="12" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12" t="s">
+        <v>2691</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="J176" s="12"/>
+      <c r="K176" s="12" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L176" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="M176" s="12">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -51265,7 +54820,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -52067,8 +55622,8 @@
       <c r="F27" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="G27" s="9" t="b">
-        <v>0</v>
+      <c r="G27" s="22" t="b">
+        <v>1</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>334</v>
@@ -56029,7 +59584,7 @@
         <v>838</v>
       </c>
       <c r="C156" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D156" t="s">
         <v>2496</v>
@@ -56058,7 +59613,7 @@
         <v>838</v>
       </c>
       <c r="C157" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D157" t="s">
         <v>2496</v>
@@ -56406,13 +59961,13 @@
         <v>838</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="D169" t="s">
         <v>326</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="F169" t="s">
         <v>326</v>
@@ -56464,7 +60019,7 @@
         <v>838</v>
       </c>
       <c r="C171" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="D171" t="s">
         <v>2496</v>
@@ -56541,6 +60096,99 @@
       </c>
       <c r="K173">
         <v>202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" s="12" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G174" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I174" s="12"/>
+      <c r="J174" s="12"/>
+      <c r="K174" s="12">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" s="12" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G175" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I175" s="12"/>
+      <c r="J175" s="12"/>
+      <c r="K175" s="12">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" s="12" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G176" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I176" s="12"/>
+      <c r="J176" s="12"/>
+      <c r="K176" s="12">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -57087,7 +60735,7 @@
         <v>292</v>
       </c>
       <c r="I23" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="24" customHeight="1">
@@ -58780,7 +62428,7 @@
         <v>449</v>
       </c>
       <c r="I100" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="24" customHeight="1">
@@ -59285,7 +62933,7 @@
         <v>482</v>
       </c>
       <c r="I123" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="24" customHeight="1">
@@ -59377,7 +63025,7 @@
         <v>292</v>
       </c>
       <c r="I127" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="24" customHeight="1">
@@ -59678,7 +63326,7 @@
         <v>292</v>
       </c>
       <c r="I141" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="24" customHeight="1">
@@ -59793,7 +63441,7 @@
         <v>518</v>
       </c>
       <c r="I146" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="24" customHeight="1">
@@ -63226,7 +66874,7 @@
         <v>802</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>803</v>
@@ -63263,7 +66911,7 @@
         <v>810</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>811</v>
@@ -63272,10 +66920,10 @@
         <v>812</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>2523</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2524</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>427</v>
@@ -63318,7 +66966,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2655</v>
+        <v>2693</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -63401,19 +67049,19 @@
         <v>835</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>836</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>2526</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>2527</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>2528</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>427</v>
@@ -63493,7 +67141,7 @@
         <v>841</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>842</v>
@@ -63519,16 +67167,16 @@
         <v>846</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>847</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>2649</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>2650</v>
       </c>
       <c r="I3" s="1">
         <v>3</v>
@@ -63548,7 +67196,7 @@
         <v>846</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>847</v>
@@ -63577,7 +67225,7 @@
         <v>846</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>847</v>
@@ -63606,16 +67254,16 @@
         <v>846</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>858</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -63635,7 +67283,7 @@
         <v>846</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>847</v>
@@ -63664,7 +67312,7 @@
         <v>846</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>847</v>
@@ -63693,7 +67341,7 @@
         <v>846</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>847</v>
@@ -63722,16 +67370,16 @@
         <v>873</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="F10" t="s">
         <v>874</v>
       </c>
       <c r="G10" s="12" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>2639</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>2640</v>
       </c>
     </row>
   </sheetData>
@@ -63842,7 +67490,7 @@
         <v>879</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F4" s="1">
         <v>-1</v>
@@ -63865,7 +67513,7 @@
         <v>880</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -63888,7 +67536,7 @@
         <v>881</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -63911,7 +67559,7 @@
         <v>882</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F7" s="1">
         <v>-1</v>
@@ -64003,7 +67651,7 @@
         <v>882</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
@@ -64072,7 +67720,7 @@
         <v>882</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
@@ -64090,10 +67738,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
@@ -64111,10 +67759,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
@@ -64342,7 +67990,7 @@
         <v>904</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -64376,7 +68024,7 @@
         <v>907</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
   </sheetData>
@@ -65598,18 +69246,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -65631,18 +69279,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486D83BE-DC1F-4D17-A145-17307EF39B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52BCFB-9C40-425D-B39A-20AAEA82796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8162" uniqueCount="2703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8195" uniqueCount="2714">
   <si>
     <t>항목</t>
   </si>
@@ -31698,6 +31698,3107 @@
     </r>
   </si>
   <si>
+    <t>V-52</t>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>17시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이때는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(after_dinner_eligible=true)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>금지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넘어간다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>했는데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는데도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거부</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때문에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나오지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출출하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요기하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우유나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙길</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>준비하기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-05 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-52 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0272</t>
+  </si>
+  <si>
+    <r>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>식욕이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>떨어지는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쉬워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10-07 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바꾸지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표로도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓸</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+  </si>
+  <si>
+    <t>DIET-P-0273</t>
+  </si>
+  <si>
+    <r>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시간이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일정하면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>놓치기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어려워요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>17~24시와</t>
     </r>
@@ -31804,6 +34905,1309 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING) 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(ANY) 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 9, 선택지 27, 목표문구 177, 노출조건 177, 질환규칙 14, 상병코드조건 61, 설정 68</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>신장질환도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>증량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>성격이라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「조금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적게」「거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요」를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답해도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>증량이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아닌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입맛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신장질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용자도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번갈아</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>받음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> 17</t>
     </r>
     <r>
@@ -31832,74 +36236,17 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
     </r>
     <r>
       <rPr>
@@ -31918,6 +36265,44 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
+      <t>(17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
       <t>, 00~04</t>
     </r>
     <r>
@@ -31927,700 +36312,41 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맞는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>질문 9, 선택지 27, 목표문구 175, 노출조건 175, 질환규칙 14, 상병코드조건 61, 설정 68</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>V-52</t>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>17시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적게」「거의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸렀어요」이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>풀을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓴다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이때는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(after_dinner_eligible=true)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그날</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>금지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>성격</t>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
     </r>
     <r>
       <rPr>
@@ -32639,1808 +36365,6 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달력</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>남지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넘어간다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>했는데</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는데도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나오지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>거부</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때문에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 0</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개라</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적게」「거의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸렀어요」를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답해도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나오지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>다음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>챙기기를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가능으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>바꾸고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>출출하면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가볍게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>요기하기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>따뜻한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우유나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두유</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>챙길</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>준비하기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번갈아</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나옴</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>노출조건</t>
     </r>
     <r>
@@ -34470,7 +36394,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> DIET-P-0033, 0269~0271 · </t>
+      <t xml:space="preserve"> DIET-P-0272·0273 · </t>
     </r>
     <r>
       <rPr>
@@ -34490,25 +36414,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> R-05 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검증규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> V-52 · </t>
     </r>
     <r>
       <rPr>
@@ -35059,7 +36964,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M176" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="58" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="DietGoalPhrasesClean" displayName="DietGoalPhrasesClean" ref="A1:M178" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="phrase_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="phrase_version"/>
@@ -35080,8 +36985,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K176" totalsRowShown="0">
-  <autoFilter ref="A1:K176" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="59" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="DietPhraseApplicabilityClean" displayName="DietPhraseApplicabilityClean" ref="A1:K178" totalsRowShown="0">
+  <autoFilter ref="A1:K178" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}">
     <filterColumn colId="6">
       <filters>
         <filter val="TRUE"/>
@@ -35408,7 +37313,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -35500,7 +37405,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2694</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -35631,16 +37536,30 @@
     </row>
     <row r="25" spans="1:4" ht="56">
       <c r="A25" s="20" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>2699</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="D25" s="20" t="s">
         <v>2700</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>2701</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>2702</v>
+    </row>
+    <row r="26" spans="1:4" ht="42">
+      <c r="A26" s="20" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>2712</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>2713</v>
       </c>
     </row>
   </sheetData>
@@ -48024,16 +49943,16 @@
     </row>
     <row r="52" spans="1:4" ht="42">
       <c r="A52" s="17" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>2695</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="D52" s="17" t="s">
         <v>2696</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>2698</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -48220,7 +50139,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -54809,6 +56728,70 @@
         <v>205</v>
       </c>
     </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="12" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12" t="s">
+        <v>2702</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I177" s="12"/>
+      <c r="J177" s="12"/>
+      <c r="K177" s="12"/>
+      <c r="L177" s="12" t="s">
+        <v>2704</v>
+      </c>
+      <c r="M177" s="12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12" t="s">
+        <v>2706</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
+      <c r="K178" s="12" t="s">
+        <v>2444</v>
+      </c>
+      <c r="L178" s="12" t="s">
+        <v>2704</v>
+      </c>
+      <c r="M178" s="12">
+        <v>207</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54820,7 +56803,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K178"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -60189,6 +62172,68 @@
       <c r="J176" s="12"/>
       <c r="K176" s="12">
         <v>205</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" s="12" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G177" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I177" s="12"/>
+      <c r="J177" s="12"/>
+      <c r="K177" s="12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G178" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
+      <c r="K178" s="12">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -66966,7 +69011,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2693</v>
+        <v>2708</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -69246,18 +71291,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69279,18 +71324,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52BCFB-9C40-425D-B39A-20AAEA82796F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3DAD4E-5840-42AA-B62E-ED2D52703A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34799,459 +34799,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>17~24시와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> READY</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이면서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> after_dinner_eligible=true</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 19</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후보로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 17~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 19</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>, 00~04</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간대</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(EVENING) 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제한이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(ANY) 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>질문 9, 선택지 27, 목표문구 177, 노출조건 177, 질환규칙 14, 상병코드조건 61, 설정 68</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -36443,6 +35990,744 @@
       </rPr>
       <t>문구세트</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>17~24시와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> READY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이면서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> after_dinner_eligible=true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후보로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 17~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 00~04</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제한이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(ANY) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간대</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(EVENING)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓴다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>늘거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄어도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개수는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -37405,7 +37690,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
@@ -37550,16 +37835,16 @@
     </row>
     <row r="26" spans="1:4" ht="42">
       <c r="A26" s="20" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>2710</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="C26" s="20" t="s">
         <v>2711</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>2712</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>2713</v>
       </c>
     </row>
   </sheetData>
@@ -69011,7 +69296,7 @@
         <v>820</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2708</v>
+        <v>2713</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>821</v>
@@ -71291,18 +71576,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -71324,18 +71609,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95292DC-7039-49BB-A977-B818C01AA149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652C313C-F5F7-45B7-BB44-74442E7FBC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56315,10 +56315,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>자동 노출 조건은 시간대, 평일·주말, 명절·연휴만 사용한다. 명절·연휴는 달력일자 시트의 날짜(calendar_code HOLIDAY)로 판정한다. 배달·편의점·회식·카페·사무실·급식·마트·야근·여행처럼 앱이 확인하지 않는 상황 조건은 사용하지 않는다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>목표 축은 그날 회전 질문으로 고른 축과 같다. 그 축에 금지·시간·상황 필터를 통과한 문구가 없을 때만 다음 축으로 내려가며, 그 순서는 직접 선택 → 사용자 확인 진료정보 → 3개월 이내 건강검진 신호 → 일반이다. 끼니 규칙 축도 일반 축에 포함한다. 같은 질환은 직접 선택 출처로 한 번만 반영. 금지 성격은 모든 출처를 합산</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -56334,11 +56330,16 @@
 끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
   </si>
   <si>
-    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+  </si>
+  <si>
+    <t>자동 노출 조건은 시간대, 평일·주말, 명절·연휴만 사용한다. 명절·연휴는 달력일자 시트의 날짜(calendar_code HOLIDAY)로 판정한다. 그 날짜에는 그날 목표 축에서 현재 단계 이하의 명절·연휴 문구가 통과하면 다른 문구보다 먼저 쓴다. 배달·편의점·회식·카페·사무실·급식·마트·야근·여행처럼 앱이 확인하지 않는 상황 조건은 사용하지 않는다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나오고, 그 날짜에는 다른 문구보다 먼저 쓴다
 끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
-  </si>
-  <si>
-    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -61093,18 +61094,18 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="52">
+    <row r="22" spans="1:4" ht="65">
       <c r="A22" s="8" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>2732</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="8" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>2733</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>2734</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>2735</v>
       </c>
     </row>
   </sheetData>
@@ -73382,7 +73383,7 @@
         <v>2452</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>2562</v>
@@ -73536,7 +73537,7 @@
         <v>2588</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>2589</v>
@@ -93647,7 +93648,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="37.5">
+    <row r="9" spans="1:7" ht="62.5">
       <c r="A9" s="6" t="s">
         <v>390</v>
       </c>
@@ -93661,7 +93662,7 @@
         <v>2469</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>2729</v>
+        <v>2734</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>2470</v>
@@ -95767,6 +95768,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010011BABF6A94C35643897AD108A63C3FA9" ma:contentTypeVersion="3" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="0dd8771f9317307737e3c0a6afa68b4c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="47def904-0df1-4aa1-ae40-c4bd318a6de7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8ccd85fd4a825fc66f8c3b5a4ab7306b" ns2:_="">
     <xsd:import namespace="47def904-0df1-4aa1-ae40-c4bd318a6de7"/>
@@ -95904,15 +95914,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA5F7BAD-F7AB-4266-8370-535EF14A9159}">
   <ds:schemaRefs>
@@ -95923,6 +95924,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE6123CC-E6A1-4739-AA75-207000A0601B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -95938,12 +95947,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91418F39-4898-4011-9115-620418630BB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>